--- a/Excel/TaskCountryConfig.xlsx
+++ b/Excel/TaskCountryConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A58C67-1AD1-4A49-A777-7DF87AF02B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FDD28C-44C2-419F-ACFE-883AE595C126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -89,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="P4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="389">
   <si>
     <t>Id</t>
   </si>
@@ -1075,18 +1075,6 @@
     <t>1;200000@31;40@10000159;10</t>
   </si>
   <si>
-    <t>随机2个</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>随机3个</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>随机5个</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>合成1只战力达到6000点的宠物</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -1109,6 +1097,479 @@
   <si>
     <t>大师洗练</t>
     <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskName_EN</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log in to the game</t>
+  </si>
+  <si>
+    <t>Monster Trial</t>
+  </si>
+  <si>
+    <t>Lord's Trial</t>
+  </si>
+  <si>
+    <t>Trial of the Dungeon</t>
+  </si>
+  <si>
+    <t>Costing Gold Coins</t>
+  </si>
+  <si>
+    <t>Gold Reward Expert</t>
+  </si>
+  <si>
+    <t>Manufacturing equipment</t>
+  </si>
+  <si>
+    <t>Equipment Identification</t>
+  </si>
+  <si>
+    <t>Pet Refinement</t>
+  </si>
+  <si>
+    <t>Get pet</t>
+  </si>
+  <si>
+    <t>Equipment Refinement</t>
+  </si>
+  <si>
+    <t>Online time</t>
+  </si>
+  <si>
+    <t>Equipment Recycling</t>
+  </si>
+  <si>
+    <t>Gnome Merchant</t>
+  </si>
+  <si>
+    <t>Cooking Master</t>
+  </si>
+  <si>
+    <t>Trial Grounds</t>
+  </si>
+  <si>
+    <t>Challenging Land</t>
+  </si>
+  <si>
+    <t>Battlefield Victory</t>
+  </si>
+  <si>
+    <t>Forward without hesitation</t>
+  </si>
+  <si>
+    <t>Face the challenge head-on</t>
+  </si>
+  <si>
+    <t>Unflinching</t>
+  </si>
+  <si>
+    <t>Unstoppable</t>
+  </si>
+  <si>
+    <t>Overwhelming</t>
+  </si>
+  <si>
+    <t>Unstoppable Hero</t>
+  </si>
+  <si>
+    <t>Resilient Body</t>
+  </si>
+  <si>
+    <t>Unyielding Soul</t>
+  </si>
+  <si>
+    <t>Show Your Skill</t>
+  </si>
+  <si>
+    <t>Hunt 100 monsters.</t>
+  </si>
+  <si>
+    <t>Hunt 200 monsters</t>
+  </si>
+  <si>
+    <t>Hunt 300 monsters</t>
+  </si>
+  <si>
+    <t>Hunt 500 monsters</t>
+  </si>
+  <si>
+    <t>Defeat 5 enemy characters</t>
+  </si>
+  <si>
+    <t>Defeat 10 enemy parties</t>
+  </si>
+  <si>
+    <t>Defeated 20 enemy soldiers</t>
+  </si>
+  <si>
+    <t>Defeat 30 enemy players</t>
+  </si>
+  <si>
+    <t>Defeat 50 enemy units</t>
+  </si>
+  <si>
+    <t>Capture a gold mine</t>
+  </si>
+  <si>
+    <t>Capture a silver mine</t>
+  </si>
+  <si>
+    <t>Capture a copper mine</t>
+  </si>
+  <si>
+    <t>Number of times to challenge other mines</t>
+  </si>
+  <si>
+    <t>Ten consecutive strikes broken</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>Exploration Expert</t>
+  </si>
+  <si>
+    <t>Seal Challenge</t>
+  </si>
+  <si>
+    <t>Pet acquisition</t>
+  </si>
+  <si>
+    <t>Equipment enchantment</t>
+  </si>
+  <si>
+    <t>Appraiser</t>
+  </si>
+  <si>
+    <t>Pet fusion</t>
+  </si>
+  <si>
+    <t>Pet Minor Achievement</t>
+  </si>
+  <si>
+    <t>Pet Baptism</t>
+  </si>
+  <si>
+    <t>Pet Battle</t>
+  </si>
+  <si>
+    <t>Life Crafting</t>
+  </si>
+  <si>
+    <t>Pet hatching</t>
+  </si>
+  <si>
+    <t>Dungeon Challenge</t>
+  </si>
+  <si>
+    <t>Pet Becomes Fully Developed</t>
+  </si>
+  <si>
+    <t>Master's refinement</t>
+  </si>
+  <si>
+    <t>Present a treasure</t>
+  </si>
+  <si>
+    <t>Take over the mine</t>
+  </si>
+  <si>
+    <t>Rare pet hatching</t>
+  </si>
+  <si>
+    <t>Pet Achievement</t>
+  </si>
+  <si>
+    <t>Strength indicator</t>
+  </si>
+  <si>
+    <t>Pet Challenge</t>
+  </si>
+  <si>
+    <t>Combat Challenge</t>
+  </si>
+  <si>
+    <t>Offer the Divine Companion</t>
+  </si>
+  <si>
+    <t>Lucky One</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskDes_EN</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log in to the game once</t>
+  </si>
+  <si>
+    <t>Defeat 30 random monsters</t>
+  </si>
+  <si>
+    <t>Defeat 3 any Lord-level monsters</t>
+  </si>
+  <si>
+    <t>Complete any group-picked dungeon once</t>
+  </si>
+  <si>
+    <t>Cost 100,000 gold coins</t>
+  </si>
+  <si>
+    <t>Complete 3 bounty quests at the main city mission messenger.</t>
+  </si>
+  <si>
+    <t>Create 1 random equipment or item</t>
+  </si>
+  <si>
+    <t>Use the identification symbol to identify 1 piece of equipment</t>
+  </si>
+  <si>
+    <t>In the pet modification interface, use the item once on the pet.</t>
+  </si>
+  <si>
+    <t>Obtain a brand new pet</t>
+  </si>
+  <si>
+    <t>At the main city's Refining Master's location, refine the equipment once.</t>
+  </si>
+  <si>
+    <t>Online time over 15 minutes</t>
+  </si>
+  <si>
+    <t>Online time exceeds 20 minutes</t>
+  </si>
+  <si>
+    <t>Recycle 5 pieces of equipment.</t>
+  </si>
+  <si>
+    <t>List an item for sale on the auction house</t>
+  </si>
+  <si>
+    <t>Create a cooking item at the home cooking place</t>
+  </si>
+  <si>
+    <t>Enter the Trial Land from the main city for exploration</t>
+  </si>
+  <si>
+    <t>Enter the challenge area from the main city to embark on an exploration adventure.</t>
+  </si>
+  <si>
+    <t>Win the battle</t>
+  </si>
+  <si>
+    <t>Defeating an enemy faction player on the battlefield</t>
+  </si>
+  <si>
+    <t>Defeat 3 players from the opposing faction in the battlefield</t>
+  </si>
+  <si>
+    <t>Defeat 5 enemy camp players on the battlefield</t>
+  </si>
+  <si>
+    <t>Defeat 10 enemy players from the opposing team in the battlefield</t>
+  </si>
+  <si>
+    <t>Defeat 15 players from the opposing faction in the battlefield.</t>
+  </si>
+  <si>
+    <t>Defeat 20 enemy camp players in battle</t>
+  </si>
+  <si>
+    <t>Defeated 30 players from the opposing faction on the battlefield</t>
+  </si>
+  <si>
+    <t>The player persisted in the battle despite being defeated by other players three times on the battlefield.</t>
+  </si>
+  <si>
+    <t>The battle is still fought even if defeated by other players 10 times in the arena.</t>
+  </si>
+  <si>
+    <t>Participate in battlefield activities and survive in the battlefield for more than 5 minutes.</t>
+  </si>
+  <si>
+    <t>Hunt 100 monsters</t>
+  </si>
+  <si>
+    <t>Hunting 200 monsters</t>
+  </si>
+  <si>
+    <t>Kill 300 monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt 500 monsters.  </t>
+  </si>
+  <si>
+    <t>Defeat 5 enemy players in the clan championship</t>
+  </si>
+  <si>
+    <t>Defeated 10 enemy players in the clan rivalry match</t>
+  </si>
+  <si>
+    <t>Defeat 20 enemy players in the clan competition</t>
+  </si>
+  <si>
+    <t>In the clan championship, defeat 30 enemy players.</t>
+  </si>
+  <si>
+    <t>Defeat 50 enemy players in the clan competition</t>
+  </si>
+  <si>
+    <t>Capture a gold mine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture a silver mine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Occupy a Bronze Mine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture any core mine of any level</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Challenge other players 3 times in the mining gameplay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 10 enemy players in the wild and receive 5 experience boxes as a reward</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the ordinary treasure map 10 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the advanced treasure map 3 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 10 hell-level lord monsters</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Completed the Tower of Sealing 10 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gained 3 brand new pets</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use enchanting items to enchant one's equipment 5 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the identification item to appraise the equipment 5 times.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Synthesis 5 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combine with 1 pet with a combat power of 6000 points</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>The pet has used the Pet Crystal to refine 5 times.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>The pet has won 10 times in the ladder battle</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip refinement reaches 10 times.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Life skill: Produces 20 items</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Successfully hatched 5 pets</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Challenge 5 abyss-type dungeons</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet synthesis 10 times,</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synthesize a pet with a combat power of 7000 points.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use 90 or more runes to identify 2 pieces of equipment</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment Refining reaches 20 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submit an orange piece of equipment</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture 1 gold mine</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip refinement completed 30 times</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Successfully hatch two pets using a precious pet egg.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synthesize a pet with a combat power of 8000 points</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>The trial land's output has entered the top 10 of the ranking.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>The pet ladder has entered the top 10 of the ranking list.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enter the top 10 of the battle ranking</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture 1 core mine</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submit a pet with more than 6 skills.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft a piece of equipment with hidden skills</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submit a piece of equipment with a level above 5 and 3 attributes</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11267,7 +11728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -11327,7 +11788,6 @@
     <xf numFmtId="49" fontId="19" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11351,6 +11811,16 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="51" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="51" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3226">
@@ -14945,24 +15415,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:T87"/>
+  <dimension ref="C2:U87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="11.875" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="13.125" customWidth="1"/>
-    <col min="12" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="20.875" customWidth="1"/>
-    <col min="15" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="17.5" customWidth="1"/>
-    <col min="18" max="18" width="36" style="4" customWidth="1"/>
+    <col min="4" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="20.875" customWidth="1"/>
+    <col min="16" max="17" width="14.875" customWidth="1"/>
+    <col min="18" max="18" width="17.5" customWidth="1"/>
+    <col min="19" max="19" width="36" style="4" customWidth="1"/>
+    <col min="20" max="20" width="76.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="3:20" x14ac:dyDescent="0.15">
+      <c r="E2" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="T2" s="32" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -14970,49 +15449,55 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="S3" s="17" t="s">
         <v>15</v>
       </c>
+      <c r="T3" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="3:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -15020,49 +15505,55 @@
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="S4" s="18" t="s">
         <v>30</v>
       </c>
+      <c r="T4" s="7" t="s">
+        <v>312</v>
+      </c>
     </row>
-    <row r="5" spans="3:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
@@ -15070,7 +15561,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>31</v>
@@ -15082,10 +15573,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>31</v>
@@ -15097,4129 +15588,4620 @@
         <v>31</v>
       </c>
       <c r="N5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="Q5" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="S5" s="17" t="s">
         <v>32</v>
       </c>
+      <c r="T5" s="6" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" spans="3:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="8">
         <v>100011</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="8">
         <v>100001</v>
       </c>
-      <c r="G6" s="8">
+      <c r="H6" s="8">
         <v>1</v>
       </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
         <v>1</v>
       </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
       <c r="K6" s="8">
         <v>0</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
         <v>5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>3000</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="14">
+      <c r="P6" s="14">
         <v>1001</v>
       </c>
-      <c r="P6" s="14">
-        <v>0</v>
-      </c>
       <c r="Q6" s="14">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
         <v>1</v>
       </c>
-      <c r="R6" s="19" t="s">
+      <c r="S6" s="19" t="s">
         <v>36</v>
       </c>
+      <c r="T6" s="19" t="s">
+        <v>313</v>
+      </c>
     </row>
-    <row r="7" spans="3:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="8">
         <v>100021</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" s="8">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="8">
         <v>100002</v>
       </c>
-      <c r="G7" s="8">
+      <c r="H7" s="8">
         <v>1</v>
       </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
         <v>1</v>
       </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
       <c r="K7" s="8">
         <v>0</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
         <v>10</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>4500</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="O7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="14">
+      <c r="P7" s="14">
         <v>1002</v>
       </c>
-      <c r="P7" s="14">
-        <v>0</v>
-      </c>
       <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
         <v>30</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="S7" s="19" t="s">
         <v>38</v>
       </c>
+      <c r="T7" s="19" t="s">
+        <v>314</v>
+      </c>
     </row>
-    <row r="8" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="8">
         <v>100031</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F8" s="8">
         <v>1</v>
       </c>
-      <c r="F8" s="8">
+      <c r="G8" s="8">
         <v>100003</v>
       </c>
-      <c r="G8" s="8">
+      <c r="H8" s="8">
         <v>1</v>
       </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8">
         <v>1</v>
       </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
       <c r="K8" s="8">
         <v>0</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
         <v>10</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>15000</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="O8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="15">
+      <c r="P8" s="15">
         <v>1003</v>
       </c>
-      <c r="P8" s="15">
-        <v>0</v>
-      </c>
       <c r="Q8" s="15">
+        <v>0</v>
+      </c>
+      <c r="R8" s="15">
         <v>3</v>
       </c>
-      <c r="R8" s="19" t="s">
+      <c r="S8" s="19" t="s">
         <v>40</v>
       </c>
+      <c r="T8" s="19" t="s">
+        <v>315</v>
+      </c>
     </row>
-    <row r="9" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="8">
         <v>100041</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="8">
+      <c r="H9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="10">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
         <v>1</v>
       </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
       <c r="K9" s="8">
         <v>0</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
         <v>10</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <v>15000</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="O9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="15">
+      <c r="P9" s="15">
         <v>1004</v>
       </c>
-      <c r="P9" s="15">
-        <v>0</v>
-      </c>
       <c r="Q9" s="15">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15">
         <v>1</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="S9" s="19" t="s">
         <v>43</v>
       </c>
+      <c r="T9" s="19" t="s">
+        <v>316</v>
+      </c>
     </row>
-    <row r="10" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="8">
         <v>100051</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" s="8">
         <v>1</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="8">
         <v>100005</v>
       </c>
-      <c r="G10" s="8">
+      <c r="H10" s="8">
         <v>1</v>
       </c>
-      <c r="H10" s="8">
+      <c r="I10" s="8">
         <v>100052</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="8">
         <v>0.5</v>
       </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
       <c r="K10" s="8">
         <v>0</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
         <v>10</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <v>6000</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="O10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="14">
+      <c r="P10" s="14">
         <v>1005</v>
       </c>
-      <c r="P10" s="14">
-        <v>0</v>
-      </c>
       <c r="Q10" s="14">
+        <v>0</v>
+      </c>
+      <c r="R10" s="14">
         <v>100000</v>
       </c>
-      <c r="R10" s="19" t="s">
+      <c r="S10" s="19" t="s">
         <v>45</v>
       </c>
+      <c r="T10" s="19" t="s">
+        <v>317</v>
+      </c>
     </row>
-    <row r="11" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="8">
         <v>100052</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" s="8">
         <v>1</v>
       </c>
-      <c r="F11" s="8">
+      <c r="G11" s="8">
         <v>100052</v>
       </c>
-      <c r="G11" s="8">
+      <c r="H11" s="8">
         <v>1</v>
       </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="I11" s="10">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
         <v>1</v>
       </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
       <c r="K11" s="8">
         <v>0</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
         <v>10</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>6000</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="O11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="14">
+      <c r="P11" s="14">
         <v>1014</v>
       </c>
-      <c r="P11" s="14">
-        <v>0</v>
-      </c>
       <c r="Q11" s="14">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
         <v>3</v>
       </c>
-      <c r="R11" s="19" t="s">
+      <c r="S11" s="19" t="s">
         <v>47</v>
       </c>
+      <c r="T11" s="19" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="12" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="8">
         <v>100061</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F12" s="8">
         <v>1</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="8">
+      <c r="H12" s="8">
         <v>1</v>
       </c>
-      <c r="H12" s="8">
+      <c r="I12" s="8">
         <v>100062</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="8">
         <v>0.7</v>
       </c>
-      <c r="J12" s="8">
-        <v>0</v>
-      </c>
       <c r="K12" s="8">
         <v>0</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
         <v>10</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <v>6000</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="O12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O12" s="15">
+      <c r="P12" s="15">
         <v>1006</v>
       </c>
-      <c r="P12" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="16">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15">
         <v>1</v>
       </c>
-      <c r="R12" s="19" t="s">
+      <c r="S12" s="19" t="s">
         <v>50</v>
       </c>
+      <c r="T12" s="19" t="s">
+        <v>319</v>
+      </c>
     </row>
-    <row r="13" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="8">
         <v>100062</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="8">
         <v>1</v>
       </c>
-      <c r="F13" s="8">
+      <c r="G13" s="8">
         <v>100062</v>
       </c>
-      <c r="G13" s="8">
+      <c r="H13" s="8">
         <v>1</v>
       </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
         <v>1</v>
       </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
       <c r="K13" s="8">
         <v>0</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
         <v>10</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <v>6000</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="O13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O13" s="15">
+      <c r="P13" s="15">
         <v>1017</v>
       </c>
-      <c r="P13" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="16">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15">
         <v>1</v>
       </c>
-      <c r="R13" s="19" t="s">
+      <c r="S13" s="19" t="s">
         <v>52</v>
       </c>
+      <c r="T13" s="19" t="s">
+        <v>320</v>
+      </c>
     </row>
-    <row r="14" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="8">
         <v>100071</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="8">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="8">
         <v>1</v>
       </c>
-      <c r="H14" s="10">
+      <c r="I14" s="10">
         <v>100072</v>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="8">
         <v>0.5</v>
       </c>
-      <c r="J14" s="8">
+      <c r="K14" s="8">
         <v>1</v>
       </c>
-      <c r="K14" s="8">
+      <c r="L14" s="8">
         <v>30</v>
       </c>
-      <c r="L14" s="12">
+      <c r="M14" s="12">
         <v>10</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <v>6000</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="O14" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O14" s="14">
+      <c r="P14" s="14">
         <v>1007</v>
       </c>
-      <c r="P14" s="14">
-        <v>0</v>
-      </c>
       <c r="Q14" s="14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
         <v>1</v>
       </c>
-      <c r="R14" s="19" t="s">
+      <c r="S14" s="19" t="s">
         <v>55</v>
       </c>
+      <c r="T14" s="19" t="s">
+        <v>321</v>
+      </c>
     </row>
-    <row r="15" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="8">
         <v>100072</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F15" s="8">
         <v>1</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="8">
         <v>1</v>
       </c>
-      <c r="H15" s="10">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="I15" s="10">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
         <v>1</v>
       </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
       <c r="K15" s="8">
         <v>0</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
         <v>10</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <v>6000</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="O15" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="14">
+      <c r="P15" s="14">
         <v>1008</v>
       </c>
-      <c r="P15" s="14">
-        <v>0</v>
-      </c>
       <c r="Q15" s="14">
+        <v>0</v>
+      </c>
+      <c r="R15" s="14">
         <v>1</v>
       </c>
-      <c r="R15" s="19" t="s">
+      <c r="S15" s="19" t="s">
         <v>57</v>
       </c>
+      <c r="T15" s="19" t="s">
+        <v>322</v>
+      </c>
     </row>
-    <row r="16" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="8">
         <v>100081</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F16" s="8">
         <v>1</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="8">
+      <c r="H16" s="8">
         <v>1</v>
       </c>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="I16" s="10">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
         <v>1</v>
       </c>
-      <c r="J16" s="8">
-        <v>0</v>
-      </c>
       <c r="K16" s="8">
         <v>0</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="8">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
         <v>10</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <v>6000</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="O16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O16" s="14">
+      <c r="P16" s="14">
         <v>1009</v>
       </c>
-      <c r="P16" s="14">
-        <v>0</v>
-      </c>
       <c r="Q16" s="14">
+        <v>0</v>
+      </c>
+      <c r="R16" s="14">
         <v>1</v>
       </c>
-      <c r="R16" s="19" t="s">
+      <c r="S16" s="19" t="s">
         <v>60</v>
       </c>
+      <c r="T16" s="19" t="s">
+        <v>323</v>
+      </c>
     </row>
-    <row r="17" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="8">
         <v>100091</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="8">
         <v>1</v>
       </c>
-      <c r="H17" s="10">
+      <c r="I17" s="10">
         <v>100092</v>
       </c>
-      <c r="I17" s="8">
+      <c r="J17" s="8">
         <v>0.5</v>
       </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
       <c r="K17" s="8">
         <v>0</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
         <v>10</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <v>30000</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="O17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O17" s="15">
+      <c r="P17" s="15">
         <v>1010</v>
       </c>
-      <c r="P17" s="15">
-        <v>0</v>
-      </c>
       <c r="Q17" s="15">
+        <v>0</v>
+      </c>
+      <c r="R17" s="15">
         <v>15</v>
       </c>
-      <c r="R17" s="19" t="s">
+      <c r="S17" s="19" t="s">
         <v>63</v>
       </c>
+      <c r="T17" s="19" t="s">
+        <v>324</v>
+      </c>
     </row>
-    <row r="18" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="8">
         <v>100092</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F18" s="8">
         <v>1</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="8">
         <v>1</v>
       </c>
-      <c r="H18" s="10">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8">
+      <c r="I18" s="10">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
         <v>1</v>
       </c>
-      <c r="J18" s="8">
-        <v>0</v>
-      </c>
       <c r="K18" s="8">
         <v>0</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
         <v>10</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <v>30000</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="O18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O18" s="15">
+      <c r="P18" s="15">
         <v>1010</v>
       </c>
-      <c r="P18" s="15">
-        <v>0</v>
-      </c>
       <c r="Q18" s="15">
+        <v>0</v>
+      </c>
+      <c r="R18" s="15">
         <v>20</v>
       </c>
-      <c r="R18" s="19" t="s">
+      <c r="S18" s="19" t="s">
         <v>64</v>
       </c>
+      <c r="T18" s="19" t="s">
+        <v>325</v>
+      </c>
     </row>
-    <row r="19" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="8">
         <v>100101</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F19" s="8">
         <v>1</v>
       </c>
-      <c r="F19" s="8">
+      <c r="G19" s="8">
         <v>100010</v>
       </c>
-      <c r="G19" s="8">
+      <c r="H19" s="8">
         <v>1</v>
       </c>
-      <c r="H19" s="8">
+      <c r="I19" s="8">
         <v>100102</v>
       </c>
-      <c r="I19" s="8">
+      <c r="J19" s="8">
         <v>0.5</v>
       </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
       <c r="K19" s="8">
         <v>0</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
         <v>10</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <v>15000</v>
       </c>
-      <c r="N19" s="13" t="s">
+      <c r="O19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O19" s="14">
+      <c r="P19" s="14">
         <v>1011</v>
       </c>
-      <c r="P19" s="14">
-        <v>0</v>
-      </c>
       <c r="Q19" s="14">
+        <v>0</v>
+      </c>
+      <c r="R19" s="14">
         <v>5</v>
       </c>
-      <c r="R19" s="19" t="s">
+      <c r="S19" s="19" t="s">
         <v>66</v>
       </c>
+      <c r="T19" s="19" t="s">
+        <v>326</v>
+      </c>
     </row>
-    <row r="20" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="8">
         <v>100102</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F20" s="8">
         <v>1</v>
       </c>
-      <c r="F20" s="8">
+      <c r="G20" s="8">
         <v>100102</v>
       </c>
-      <c r="G20" s="8">
+      <c r="H20" s="8">
         <v>1</v>
       </c>
-      <c r="H20" s="10">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8">
+      <c r="I20" s="10">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
         <v>1</v>
       </c>
-      <c r="J20" s="8">
-        <v>0</v>
-      </c>
       <c r="K20" s="8">
         <v>0</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="8">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
         <v>10</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <v>15000</v>
       </c>
-      <c r="N20" s="13" t="s">
+      <c r="O20" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O20" s="14">
+      <c r="P20" s="14">
         <v>1015</v>
       </c>
-      <c r="P20" s="14">
-        <v>0</v>
-      </c>
       <c r="Q20" s="14">
+        <v>0</v>
+      </c>
+      <c r="R20" s="14">
         <v>1</v>
       </c>
-      <c r="R20" s="19" t="s">
+      <c r="S20" s="19" t="s">
         <v>68</v>
       </c>
+      <c r="T20" s="19" t="s">
+        <v>327</v>
+      </c>
     </row>
-    <row r="21" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="8">
         <v>100103</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="8">
         <v>1</v>
       </c>
-      <c r="F21" s="8">
+      <c r="G21" s="8">
         <v>100103</v>
       </c>
-      <c r="G21" s="8">
+      <c r="H21" s="8">
         <v>1</v>
       </c>
-      <c r="H21" s="10">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8">
-        <v>1</v>
+      <c r="I21" s="10">
+        <v>0</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
       </c>
       <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
         <v>25</v>
       </c>
-      <c r="L21" s="12">
+      <c r="M21" s="12">
         <v>10</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <v>15000</v>
       </c>
-      <c r="N21" s="13" t="s">
+      <c r="O21" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O21" s="14">
+      <c r="P21" s="14">
         <v>1018</v>
       </c>
-      <c r="P21" s="14">
-        <v>0</v>
-      </c>
       <c r="Q21" s="14">
+        <v>0</v>
+      </c>
+      <c r="R21" s="14">
         <v>1</v>
       </c>
-      <c r="R21" s="19" t="s">
+      <c r="S21" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="T21" s="19" t="s">
+        <v>328</v>
+      </c>
     </row>
-    <row r="22" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="8">
         <v>100111</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" s="8">
         <v>1</v>
       </c>
-      <c r="F22" s="8">
+      <c r="G22" s="8">
         <v>100111</v>
       </c>
-      <c r="G22" s="8">
+      <c r="H22" s="8">
         <v>1</v>
       </c>
-      <c r="H22" s="8">
-        <v>0</v>
-      </c>
       <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
         <v>1</v>
       </c>
-      <c r="J22" s="8">
-        <v>0</v>
-      </c>
       <c r="K22" s="8">
         <v>0</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="8">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
         <v>5</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <v>15000</v>
       </c>
-      <c r="N22" s="13" t="s">
+      <c r="O22" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O22" s="14">
+      <c r="P22" s="14">
         <v>1012</v>
       </c>
-      <c r="P22" s="14">
-        <v>0</v>
-      </c>
       <c r="Q22" s="14">
+        <v>0</v>
+      </c>
+      <c r="R22" s="14">
         <v>1</v>
       </c>
-      <c r="R22" s="19" t="s">
+      <c r="S22" s="19" t="s">
         <v>72</v>
       </c>
+      <c r="T22" s="19" t="s">
+        <v>329</v>
+      </c>
     </row>
-    <row r="23" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="8">
         <v>100121</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" s="8">
         <v>1</v>
       </c>
-      <c r="F23" s="8">
+      <c r="G23" s="8">
         <v>100121</v>
       </c>
-      <c r="G23" s="8">
+      <c r="H23" s="8">
         <v>1</v>
       </c>
-      <c r="H23" s="10">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="I23" s="10">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
         <v>1</v>
       </c>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
       <c r="K23" s="8">
         <v>0</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
         <v>5</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <v>15000</v>
       </c>
-      <c r="N23" s="13" t="s">
+      <c r="O23" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O23" s="14">
+      <c r="P23" s="14">
         <v>1013</v>
       </c>
-      <c r="P23" s="14">
-        <v>0</v>
-      </c>
       <c r="Q23" s="14">
+        <v>0</v>
+      </c>
+      <c r="R23" s="14">
         <v>1</v>
       </c>
-      <c r="R23" s="19" t="s">
+      <c r="S23" s="19" t="s">
         <v>74</v>
       </c>
+      <c r="T23" s="19" t="s">
+        <v>330</v>
+      </c>
     </row>
-    <row r="24" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="8">
         <v>200001</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="F24" s="8">
+      <c r="G24" s="8">
         <v>100011</v>
       </c>
-      <c r="G24" s="8">
+      <c r="H24" s="8">
         <v>1</v>
       </c>
-      <c r="H24" s="8">
-        <v>0</v>
-      </c>
       <c r="I24" s="8">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8">
         <v>1</v>
       </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
       <c r="K24" s="8">
         <v>0</v>
       </c>
-      <c r="L24" s="12">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2">
+      <c r="L24" s="8">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
         <v>30000</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="O24" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O24" s="14">
+      <c r="P24" s="14">
         <v>1101</v>
       </c>
-      <c r="P24" s="14">
-        <v>0</v>
-      </c>
       <c r="Q24" s="14">
+        <v>0</v>
+      </c>
+      <c r="R24" s="14">
         <v>1</v>
       </c>
-      <c r="R24" s="19" t="s">
+      <c r="S24" s="19" t="s">
         <v>77</v>
       </c>
+      <c r="T24" s="19" t="s">
+        <v>331</v>
+      </c>
     </row>
-    <row r="25" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="8">
         <v>200002</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F25" s="8">
         <v>2</v>
       </c>
-      <c r="F25" s="8">
+      <c r="G25" s="8">
         <v>100014</v>
       </c>
-      <c r="G25" s="8">
+      <c r="H25" s="8">
         <v>1</v>
       </c>
-      <c r="H25" s="10">
-        <v>0</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="I25" s="10">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
         <v>1</v>
       </c>
-      <c r="J25" s="8">
-        <v>0</v>
-      </c>
       <c r="K25" s="8">
         <v>0</v>
       </c>
-      <c r="L25" s="12">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
         <v>30000</v>
       </c>
-      <c r="N25" s="13" t="s">
+      <c r="O25" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O25" s="14">
+      <c r="P25" s="14">
         <v>1102</v>
       </c>
-      <c r="P25" s="14">
-        <v>0</v>
-      </c>
       <c r="Q25" s="14">
+        <v>0</v>
+      </c>
+      <c r="R25" s="14">
         <v>1</v>
       </c>
-      <c r="R25" s="19" t="s">
+      <c r="S25" s="19" t="s">
         <v>80</v>
       </c>
+      <c r="T25" s="19" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="26" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="8">
         <v>200003</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F26" s="8">
         <v>2</v>
       </c>
-      <c r="F26" s="8">
+      <c r="G26" s="8">
         <v>100014</v>
       </c>
-      <c r="G26" s="8">
+      <c r="H26" s="8">
         <v>1</v>
       </c>
-      <c r="H26" s="10">
-        <v>0</v>
-      </c>
-      <c r="I26" s="8">
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
         <v>1</v>
       </c>
-      <c r="J26" s="8">
-        <v>0</v>
-      </c>
       <c r="K26" s="8">
         <v>0</v>
       </c>
-      <c r="L26" s="12">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
+      <c r="L26" s="8">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
         <v>30000</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="O26" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O26" s="14">
+      <c r="P26" s="14">
         <v>1102</v>
       </c>
-      <c r="P26" s="14">
-        <v>0</v>
-      </c>
       <c r="Q26" s="14">
+        <v>0</v>
+      </c>
+      <c r="R26" s="14">
         <v>3</v>
       </c>
-      <c r="R26" s="19" t="s">
+      <c r="S26" s="19" t="s">
         <v>82</v>
       </c>
+      <c r="T26" s="19" t="s">
+        <v>333</v>
+      </c>
     </row>
-    <row r="27" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="8">
         <v>200004</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" s="8">
         <v>2</v>
       </c>
-      <c r="F27" s="8">
+      <c r="G27" s="8">
         <v>100015</v>
       </c>
-      <c r="G27" s="8">
+      <c r="H27" s="8">
         <v>1</v>
       </c>
-      <c r="H27" s="10">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="I27" s="10">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
         <v>1</v>
       </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
       <c r="K27" s="8">
         <v>0</v>
       </c>
-      <c r="L27" s="12">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2">
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
         <v>30000</v>
       </c>
-      <c r="N27" s="13" t="s">
+      <c r="O27" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O27" s="14">
+      <c r="P27" s="14">
         <v>1102</v>
       </c>
-      <c r="P27" s="14">
-        <v>0</v>
-      </c>
       <c r="Q27" s="14">
+        <v>0</v>
+      </c>
+      <c r="R27" s="14">
         <v>5</v>
       </c>
-      <c r="R27" s="19" t="s">
+      <c r="S27" s="19" t="s">
         <v>84</v>
       </c>
+      <c r="T27" s="19" t="s">
+        <v>334</v>
+      </c>
     </row>
-    <row r="28" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="8">
         <v>200005</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F28" s="8">
         <v>2</v>
       </c>
-      <c r="F28" s="8">
+      <c r="G28" s="8">
         <v>100015</v>
       </c>
-      <c r="G28" s="8">
+      <c r="H28" s="8">
         <v>1</v>
       </c>
-      <c r="H28" s="10">
-        <v>0</v>
-      </c>
-      <c r="I28" s="8">
+      <c r="I28" s="10">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
         <v>1</v>
       </c>
-      <c r="J28" s="8">
-        <v>0</v>
-      </c>
       <c r="K28" s="8">
         <v>0</v>
       </c>
-      <c r="L28" s="12">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
         <v>30000</v>
       </c>
-      <c r="N28" s="13" t="s">
+      <c r="O28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O28" s="14">
+      <c r="P28" s="14">
         <v>1102</v>
       </c>
-      <c r="P28" s="14">
-        <v>0</v>
-      </c>
       <c r="Q28" s="14">
+        <v>0</v>
+      </c>
+      <c r="R28" s="14">
         <v>10</v>
       </c>
-      <c r="R28" s="19" t="s">
+      <c r="S28" s="19" t="s">
         <v>86</v>
       </c>
+      <c r="T28" s="19" t="s">
+        <v>335</v>
+      </c>
     </row>
-    <row r="29" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="8">
         <v>200006</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F29" s="8">
         <v>2</v>
       </c>
-      <c r="F29" s="8">
+      <c r="G29" s="8">
         <v>100016</v>
       </c>
-      <c r="G29" s="8">
+      <c r="H29" s="8">
         <v>1</v>
       </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
         <v>1</v>
       </c>
-      <c r="J29" s="8">
-        <v>0</v>
-      </c>
       <c r="K29" s="8">
         <v>0</v>
       </c>
-      <c r="L29" s="12">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
         <v>30000</v>
       </c>
-      <c r="N29" s="13" t="s">
+      <c r="O29" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O29" s="14">
+      <c r="P29" s="14">
         <v>1102</v>
       </c>
-      <c r="P29" s="14">
-        <v>0</v>
-      </c>
       <c r="Q29" s="14">
+        <v>0</v>
+      </c>
+      <c r="R29" s="14">
         <v>15</v>
       </c>
-      <c r="R29" s="19" t="s">
+      <c r="S29" s="19" t="s">
         <v>88</v>
       </c>
+      <c r="T29" s="19" t="s">
+        <v>336</v>
+      </c>
     </row>
-    <row r="30" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="8">
         <v>200007</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F30" s="8">
         <v>2</v>
       </c>
-      <c r="F30" s="8">
+      <c r="G30" s="8">
         <v>100016</v>
       </c>
-      <c r="G30" s="8">
+      <c r="H30" s="8">
         <v>1</v>
       </c>
-      <c r="H30" s="10">
-        <v>0</v>
-      </c>
-      <c r="I30" s="8">
+      <c r="I30" s="10">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
         <v>1</v>
       </c>
-      <c r="J30" s="8">
-        <v>0</v>
-      </c>
       <c r="K30" s="8">
         <v>0</v>
       </c>
-      <c r="L30" s="12">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2">
+      <c r="L30" s="8">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
         <v>30000</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="O30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O30" s="14">
+      <c r="P30" s="14">
         <v>1102</v>
       </c>
-      <c r="P30" s="14">
-        <v>0</v>
-      </c>
       <c r="Q30" s="14">
+        <v>0</v>
+      </c>
+      <c r="R30" s="14">
         <v>20</v>
       </c>
-      <c r="R30" s="19" t="s">
+      <c r="S30" s="19" t="s">
         <v>90</v>
       </c>
+      <c r="T30" s="19" t="s">
+        <v>337</v>
+      </c>
     </row>
-    <row r="31" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="8">
         <v>200008</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F31" s="8">
         <v>2</v>
       </c>
-      <c r="F31" s="8">
+      <c r="G31" s="8">
         <v>100016</v>
       </c>
-      <c r="G31" s="8">
+      <c r="H31" s="8">
         <v>1</v>
       </c>
-      <c r="H31" s="10">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="I31" s="10">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
         <v>1</v>
       </c>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
       <c r="K31" s="8">
         <v>0</v>
       </c>
-      <c r="L31" s="12">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2">
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
         <v>30000</v>
       </c>
-      <c r="N31" s="13" t="s">
+      <c r="O31" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="O31" s="14">
+      <c r="P31" s="14">
         <v>1102</v>
       </c>
-      <c r="P31" s="14">
-        <v>0</v>
-      </c>
       <c r="Q31" s="14">
+        <v>0</v>
+      </c>
+      <c r="R31" s="14">
         <v>30</v>
       </c>
-      <c r="R31" s="19" t="s">
+      <c r="S31" s="19" t="s">
         <v>93</v>
       </c>
+      <c r="T31" s="19" t="s">
+        <v>338</v>
+      </c>
     </row>
-    <row r="32" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="8">
         <v>200009</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F32" s="8">
         <v>2</v>
       </c>
-      <c r="F32" s="8">
+      <c r="G32" s="8">
         <v>100111</v>
       </c>
-      <c r="G32" s="8">
+      <c r="H32" s="8">
         <v>1</v>
       </c>
-      <c r="H32" s="10">
-        <v>0</v>
-      </c>
-      <c r="I32" s="8">
+      <c r="I32" s="10">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
         <v>1</v>
       </c>
-      <c r="J32" s="8">
-        <v>0</v>
-      </c>
       <c r="K32" s="8">
         <v>0</v>
       </c>
-      <c r="L32" s="12">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2">
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2">
         <v>30000</v>
       </c>
-      <c r="N32" s="13" t="s">
+      <c r="O32" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O32" s="14">
+      <c r="P32" s="14">
         <v>1102</v>
       </c>
-      <c r="P32" s="14">
-        <v>0</v>
-      </c>
       <c r="Q32" s="14">
+        <v>0</v>
+      </c>
+      <c r="R32" s="14">
         <v>3</v>
       </c>
-      <c r="R32" s="19" t="s">
+      <c r="S32" s="19" t="s">
         <v>95</v>
       </c>
+      <c r="T32" s="19" t="s">
+        <v>339</v>
+      </c>
     </row>
-    <row r="33" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="8">
         <v>200010</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F33" s="8">
         <v>2</v>
       </c>
-      <c r="F33" s="8">
+      <c r="G33" s="8">
         <v>100121</v>
       </c>
-      <c r="G33" s="8">
+      <c r="H33" s="8">
         <v>1</v>
       </c>
-      <c r="H33" s="10">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8">
+      <c r="I33" s="10">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
         <v>1</v>
       </c>
-      <c r="J33" s="8">
-        <v>0</v>
-      </c>
       <c r="K33" s="8">
         <v>0</v>
       </c>
-      <c r="L33" s="12">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2">
         <v>30000</v>
       </c>
-      <c r="N33" s="13" t="s">
+      <c r="O33" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O33" s="14">
+      <c r="P33" s="14">
         <v>1102</v>
       </c>
-      <c r="P33" s="14">
-        <v>0</v>
-      </c>
       <c r="Q33" s="14">
+        <v>0</v>
+      </c>
+      <c r="R33" s="14">
         <v>10</v>
       </c>
-      <c r="R33" s="19" t="s">
+      <c r="S33" s="19" t="s">
         <v>97</v>
       </c>
+      <c r="T33" s="19" t="s">
+        <v>340</v>
+      </c>
     </row>
-    <row r="34" spans="3:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:20" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="8">
         <v>200011</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F34" s="8">
         <v>2</v>
       </c>
-      <c r="F34" s="8">
+      <c r="G34" s="8">
         <v>100006</v>
       </c>
-      <c r="G34" s="8">
+      <c r="H34" s="8">
         <v>1</v>
       </c>
-      <c r="H34" s="10">
-        <v>0</v>
-      </c>
-      <c r="I34" s="8">
+      <c r="I34" s="10">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
         <v>1</v>
       </c>
-      <c r="J34" s="8">
-        <v>0</v>
-      </c>
       <c r="K34" s="8">
         <v>0</v>
       </c>
-      <c r="L34" s="12">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
+      <c r="L34" s="8">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2">
         <v>50000</v>
       </c>
-      <c r="N34" s="13" t="s">
+      <c r="O34" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O34" s="15">
+      <c r="P34" s="15">
         <v>1103</v>
       </c>
-      <c r="P34" s="15">
-        <v>0</v>
-      </c>
       <c r="Q34" s="15">
+        <v>0</v>
+      </c>
+      <c r="R34" s="15">
         <v>5</v>
       </c>
-      <c r="R34" s="19" t="s">
+      <c r="S34" s="19" t="s">
         <v>99</v>
       </c>
+      <c r="T34" s="19" t="s">
+        <v>341</v>
+      </c>
     </row>
-    <row r="35" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="8">
         <v>300001</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="F35" s="8">
+      <c r="G35" s="8">
         <v>100014</v>
       </c>
-      <c r="G35" s="8">
+      <c r="H35" s="8">
         <v>1</v>
       </c>
-      <c r="H35" s="10">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8">
+      <c r="I35" s="10">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
         <v>1</v>
       </c>
-      <c r="J35" s="8">
-        <v>0</v>
-      </c>
       <c r="K35" s="8">
         <v>0</v>
       </c>
-      <c r="L35" s="12">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2">
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2">
         <v>50000</v>
       </c>
-      <c r="N35" s="13" t="s">
+      <c r="O35" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O35" s="14">
+      <c r="P35" s="14">
         <v>1201</v>
       </c>
-      <c r="P35" s="14">
-        <v>0</v>
-      </c>
       <c r="Q35" s="14">
+        <v>0</v>
+      </c>
+      <c r="R35" s="14">
         <v>100</v>
       </c>
-      <c r="R35" s="19" t="s">
+      <c r="S35" s="19" t="s">
         <v>102</v>
       </c>
+      <c r="T35" s="19" t="s">
+        <v>342</v>
+      </c>
     </row>
-    <row r="36" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="8">
         <v>300002</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F36" s="8">
         <v>3</v>
       </c>
-      <c r="F36" s="8">
+      <c r="G36" s="8">
         <v>100014</v>
       </c>
-      <c r="G36" s="8">
+      <c r="H36" s="8">
         <v>1</v>
       </c>
-      <c r="H36" s="10">
-        <v>0</v>
-      </c>
-      <c r="I36" s="8">
+      <c r="I36" s="10">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8">
         <v>1</v>
       </c>
-      <c r="J36" s="8">
-        <v>0</v>
-      </c>
       <c r="K36" s="8">
         <v>0</v>
       </c>
-      <c r="L36" s="12">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2">
+      <c r="L36" s="8">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2">
         <v>50000</v>
       </c>
-      <c r="N36" s="13" t="s">
+      <c r="O36" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O36" s="14">
+      <c r="P36" s="14">
         <v>1201</v>
       </c>
-      <c r="P36" s="14">
-        <v>0</v>
-      </c>
       <c r="Q36" s="14">
+        <v>0</v>
+      </c>
+      <c r="R36" s="14">
         <v>200</v>
       </c>
-      <c r="R36" s="19" t="s">
+      <c r="S36" s="19" t="s">
         <v>104</v>
       </c>
+      <c r="T36" s="19" t="s">
+        <v>343</v>
+      </c>
     </row>
-    <row r="37" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="8">
         <v>300003</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F37" s="8">
         <v>3</v>
       </c>
-      <c r="F37" s="8">
+      <c r="G37" s="8">
         <v>100014</v>
       </c>
-      <c r="G37" s="8">
+      <c r="H37" s="8">
         <v>1</v>
       </c>
-      <c r="H37" s="10">
-        <v>0</v>
-      </c>
-      <c r="I37" s="8">
+      <c r="I37" s="10">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
         <v>1</v>
       </c>
-      <c r="J37" s="8">
-        <v>0</v>
-      </c>
       <c r="K37" s="8">
         <v>0</v>
       </c>
-      <c r="L37" s="12">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2">
+      <c r="L37" s="8">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2">
         <v>100000</v>
       </c>
-      <c r="N37" s="13" t="s">
+      <c r="O37" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O37" s="14">
+      <c r="P37" s="14">
         <v>1201</v>
       </c>
-      <c r="P37" s="14">
-        <v>0</v>
-      </c>
       <c r="Q37" s="14">
+        <v>0</v>
+      </c>
+      <c r="R37" s="14">
         <v>300</v>
       </c>
-      <c r="R37" s="19" t="s">
+      <c r="S37" s="19" t="s">
         <v>106</v>
       </c>
+      <c r="T37" s="19" t="s">
+        <v>344</v>
+      </c>
     </row>
-    <row r="38" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="8">
         <v>300004</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" s="8">
         <v>3</v>
       </c>
-      <c r="F38" s="8">
+      <c r="G38" s="8">
         <v>100014</v>
       </c>
-      <c r="G38" s="8">
+      <c r="H38" s="8">
         <v>1</v>
       </c>
-      <c r="H38" s="10">
-        <v>0</v>
-      </c>
-      <c r="I38" s="8">
+      <c r="I38" s="10">
+        <v>0</v>
+      </c>
+      <c r="J38" s="8">
         <v>1</v>
       </c>
-      <c r="J38" s="8">
-        <v>0</v>
-      </c>
       <c r="K38" s="8">
         <v>0</v>
       </c>
-      <c r="L38" s="12">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="L38" s="8">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
         <v>100000</v>
       </c>
-      <c r="N38" s="13" t="s">
+      <c r="O38" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O38" s="14">
+      <c r="P38" s="14">
         <v>1201</v>
       </c>
-      <c r="P38" s="14">
-        <v>0</v>
-      </c>
       <c r="Q38" s="14">
+        <v>0</v>
+      </c>
+      <c r="R38" s="14">
         <v>500</v>
       </c>
-      <c r="R38" s="19" t="s">
+      <c r="S38" s="19" t="s">
         <v>108</v>
       </c>
+      <c r="T38" s="19" t="s">
+        <v>345</v>
+      </c>
     </row>
-    <row r="39" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="8">
         <v>400001</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F39" s="8">
         <v>4</v>
       </c>
-      <c r="F39" s="8">
+      <c r="G39" s="8">
         <v>100014</v>
       </c>
-      <c r="G39" s="8">
+      <c r="H39" s="8">
         <v>1</v>
       </c>
-      <c r="H39" s="10">
-        <v>0</v>
-      </c>
-      <c r="I39" s="8">
+      <c r="I39" s="10">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8">
         <v>1</v>
       </c>
-      <c r="J39" s="8">
-        <v>0</v>
-      </c>
       <c r="K39" s="8">
         <v>0</v>
       </c>
-      <c r="L39" s="12">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2">
+      <c r="L39" s="8">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2">
         <v>30000</v>
       </c>
-      <c r="N39" s="13" t="s">
+      <c r="O39" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="O39" s="14">
+      <c r="P39" s="14">
         <v>1301</v>
       </c>
-      <c r="P39" s="14">
-        <v>0</v>
-      </c>
       <c r="Q39" s="14">
+        <v>0</v>
+      </c>
+      <c r="R39" s="14">
         <v>5</v>
       </c>
-      <c r="R39" s="19" t="s">
+      <c r="S39" s="19" t="s">
         <v>111</v>
       </c>
+      <c r="T39" s="19" t="s">
+        <v>346</v>
+      </c>
     </row>
-    <row r="40" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="8">
         <v>400002</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F40" s="8">
         <v>4</v>
       </c>
-      <c r="F40" s="8">
+      <c r="G40" s="8">
         <v>100014</v>
       </c>
-      <c r="G40" s="8">
+      <c r="H40" s="8">
         <v>1</v>
       </c>
-      <c r="H40" s="10">
-        <v>0</v>
-      </c>
-      <c r="I40" s="8">
+      <c r="I40" s="10">
+        <v>0</v>
+      </c>
+      <c r="J40" s="8">
         <v>1</v>
       </c>
-      <c r="J40" s="8">
-        <v>0</v>
-      </c>
       <c r="K40" s="8">
         <v>0</v>
       </c>
-      <c r="L40" s="12">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
+      <c r="L40" s="8">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2">
         <v>50000</v>
       </c>
-      <c r="N40" s="13" t="s">
+      <c r="O40" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O40" s="14">
+      <c r="P40" s="14">
         <v>1301</v>
       </c>
-      <c r="P40" s="14">
-        <v>0</v>
-      </c>
       <c r="Q40" s="14">
+        <v>0</v>
+      </c>
+      <c r="R40" s="14">
         <v>10</v>
       </c>
-      <c r="R40" s="19" t="s">
+      <c r="S40" s="19" t="s">
         <v>113</v>
       </c>
+      <c r="T40" s="19" t="s">
+        <v>347</v>
+      </c>
     </row>
-    <row r="41" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="8">
         <v>400003</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F41" s="8">
         <v>4</v>
       </c>
-      <c r="F41" s="8">
+      <c r="G41" s="8">
         <v>100015</v>
       </c>
-      <c r="G41" s="8">
+      <c r="H41" s="8">
         <v>1</v>
       </c>
-      <c r="H41" s="10">
-        <v>0</v>
-      </c>
-      <c r="I41" s="8">
+      <c r="I41" s="10">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8">
         <v>1</v>
       </c>
-      <c r="J41" s="8">
-        <v>0</v>
-      </c>
       <c r="K41" s="8">
         <v>0</v>
       </c>
-      <c r="L41" s="12">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2">
+      <c r="L41" s="8">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2">
         <v>50000</v>
       </c>
-      <c r="N41" s="13" t="s">
+      <c r="O41" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="O41" s="14">
+      <c r="P41" s="14">
         <v>1301</v>
       </c>
-      <c r="P41" s="14">
-        <v>0</v>
-      </c>
       <c r="Q41" s="14">
+        <v>0</v>
+      </c>
+      <c r="R41" s="14">
         <v>20</v>
       </c>
-      <c r="R41" s="19" t="s">
+      <c r="S41" s="19" t="s">
         <v>116</v>
       </c>
+      <c r="T41" s="19" t="s">
+        <v>348</v>
+      </c>
     </row>
-    <row r="42" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="8">
         <v>400004</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F42" s="8">
         <v>4</v>
       </c>
-      <c r="F42" s="8">
+      <c r="G42" s="8">
         <v>100016</v>
       </c>
-      <c r="G42" s="8">
+      <c r="H42" s="8">
         <v>1</v>
       </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-      <c r="I42" s="8">
+      <c r="I42" s="10">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8">
         <v>1</v>
       </c>
-      <c r="J42" s="8">
-        <v>0</v>
-      </c>
       <c r="K42" s="8">
         <v>0</v>
       </c>
-      <c r="L42" s="12">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
+      <c r="L42" s="8">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2">
         <v>100000</v>
       </c>
-      <c r="N42" s="13" t="s">
+      <c r="O42" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="O42" s="14">
+      <c r="P42" s="14">
         <v>1301</v>
       </c>
-      <c r="P42" s="14">
-        <v>0</v>
-      </c>
       <c r="Q42" s="14">
+        <v>0</v>
+      </c>
+      <c r="R42" s="14">
         <v>30</v>
       </c>
-      <c r="R42" s="19" t="s">
+      <c r="S42" s="19" t="s">
         <v>119</v>
       </c>
+      <c r="T42" s="19" t="s">
+        <v>349</v>
+      </c>
     </row>
-    <row r="43" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="8">
         <v>400005</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F43" s="8">
         <v>4</v>
       </c>
-      <c r="F43" s="8">
+      <c r="G43" s="8">
         <v>100016</v>
       </c>
-      <c r="G43" s="8">
+      <c r="H43" s="8">
         <v>1</v>
       </c>
-      <c r="H43" s="10">
-        <v>0</v>
-      </c>
-      <c r="I43" s="8">
+      <c r="I43" s="10">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8">
         <v>1</v>
       </c>
-      <c r="J43" s="8">
-        <v>0</v>
-      </c>
       <c r="K43" s="8">
         <v>0</v>
       </c>
-      <c r="L43" s="12">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2">
+      <c r="L43" s="8">
+        <v>0</v>
+      </c>
+      <c r="M43" s="12">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2">
         <v>100000</v>
       </c>
-      <c r="N43" s="13" t="s">
+      <c r="O43" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="O43" s="14">
+      <c r="P43" s="14">
         <v>1301</v>
       </c>
-      <c r="P43" s="14">
-        <v>0</v>
-      </c>
       <c r="Q43" s="14">
+        <v>0</v>
+      </c>
+      <c r="R43" s="14">
         <v>50</v>
       </c>
-      <c r="R43" s="19" t="s">
+      <c r="S43" s="19" t="s">
         <v>122</v>
       </c>
+      <c r="T43" s="19" t="s">
+        <v>350</v>
+      </c>
     </row>
-    <row r="44" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="8">
         <v>500001</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F44" s="8">
         <v>5</v>
       </c>
-      <c r="F44" s="8">
+      <c r="G44" s="8">
         <v>100016</v>
       </c>
-      <c r="G44" s="8">
+      <c r="H44" s="8">
         <v>1</v>
       </c>
-      <c r="H44" s="10">
-        <v>0</v>
-      </c>
-      <c r="I44" s="8">
+      <c r="I44" s="10">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8">
         <v>1</v>
       </c>
-      <c r="J44" s="8">
-        <v>0</v>
-      </c>
       <c r="K44" s="8">
         <v>0</v>
       </c>
-      <c r="L44" s="12">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>0</v>
-      </c>
-      <c r="N44" s="13" t="s">
+      <c r="L44" s="8">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0</v>
+      </c>
+      <c r="O44" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="O44" s="14">
+      <c r="P44" s="14">
         <v>401</v>
       </c>
-      <c r="P44" s="14">
+      <c r="Q44" s="14">
         <v>10001</v>
       </c>
-      <c r="Q44" s="14">
+      <c r="R44" s="14">
         <v>1</v>
       </c>
-      <c r="R44" s="19" t="s">
+      <c r="S44" s="19" t="s">
         <v>130</v>
       </c>
+      <c r="T44" s="19" t="s">
+        <v>351</v>
+      </c>
     </row>
-    <row r="45" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="8">
         <v>500002</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="F45" s="8">
         <v>5</v>
       </c>
-      <c r="F45" s="8">
+      <c r="G45" s="8">
         <v>100016</v>
       </c>
-      <c r="G45" s="8">
+      <c r="H45" s="8">
         <v>1</v>
       </c>
-      <c r="H45" s="10">
-        <v>0</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="I45" s="10">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8">
         <v>1</v>
       </c>
-      <c r="J45" s="8">
-        <v>0</v>
-      </c>
       <c r="K45" s="8">
         <v>0</v>
       </c>
-      <c r="L45" s="12">
-        <v>0</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" s="13" t="s">
+      <c r="L45" s="8">
+        <v>0</v>
+      </c>
+      <c r="M45" s="12">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0</v>
+      </c>
+      <c r="O45" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="O45" s="14">
+      <c r="P45" s="14">
         <v>401</v>
       </c>
-      <c r="P45" s="14">
+      <c r="Q45" s="14">
         <v>10002</v>
       </c>
-      <c r="Q45" s="14">
+      <c r="R45" s="14">
         <v>1</v>
       </c>
-      <c r="R45" s="19" t="s">
+      <c r="S45" s="19" t="s">
         <v>131</v>
       </c>
+      <c r="T45" s="19" t="s">
+        <v>352</v>
+      </c>
     </row>
-    <row r="46" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="8">
         <v>500003</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F46" s="8">
         <v>5</v>
       </c>
-      <c r="F46" s="8">
+      <c r="G46" s="8">
         <v>100016</v>
       </c>
-      <c r="G46" s="8">
+      <c r="H46" s="8">
         <v>1</v>
       </c>
-      <c r="H46" s="10">
-        <v>0</v>
-      </c>
-      <c r="I46" s="8">
+      <c r="I46" s="10">
+        <v>0</v>
+      </c>
+      <c r="J46" s="8">
         <v>1</v>
       </c>
-      <c r="J46" s="8">
-        <v>0</v>
-      </c>
       <c r="K46" s="8">
         <v>0</v>
       </c>
-      <c r="L46" s="12">
-        <v>0</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-      <c r="N46" s="13" t="s">
+      <c r="L46" s="8">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0</v>
+      </c>
+      <c r="O46" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="O46" s="14">
+      <c r="P46" s="14">
         <v>401</v>
       </c>
-      <c r="P46" s="14">
+      <c r="Q46" s="14">
         <v>10003</v>
       </c>
-      <c r="Q46" s="14">
+      <c r="R46" s="14">
         <v>1</v>
       </c>
-      <c r="R46" s="19" t="s">
+      <c r="S46" s="19" t="s">
         <v>132</v>
       </c>
+      <c r="T46" s="19" t="s">
+        <v>353</v>
+      </c>
     </row>
-    <row r="47" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="8">
         <v>500004</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F47" s="8">
         <v>5</v>
       </c>
-      <c r="F47" s="8">
+      <c r="G47" s="8">
         <v>100016</v>
       </c>
-      <c r="G47" s="8">
+      <c r="H47" s="8">
         <v>1</v>
       </c>
-      <c r="H47" s="10">
-        <v>0</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="I47" s="10">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
         <v>1</v>
       </c>
-      <c r="J47" s="8">
-        <v>0</v>
-      </c>
       <c r="K47" s="8">
         <v>0</v>
       </c>
-      <c r="L47" s="12">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-      <c r="N47" s="13" t="s">
+      <c r="L47" s="8">
+        <v>0</v>
+      </c>
+      <c r="M47" s="12">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2">
+        <v>0</v>
+      </c>
+      <c r="O47" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="O47" s="14">
+      <c r="P47" s="14">
         <v>401</v>
       </c>
-      <c r="P47" s="14">
-        <v>0</v>
-      </c>
       <c r="Q47" s="14">
+        <v>0</v>
+      </c>
+      <c r="R47" s="14">
         <v>1</v>
       </c>
-      <c r="R47" s="19" t="s">
+      <c r="S47" s="19" t="s">
         <v>133</v>
       </c>
+      <c r="T47" s="19" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="48" spans="3:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="8">
         <v>500005</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="F48" s="8">
         <v>5</v>
       </c>
-      <c r="F48" s="8">
+      <c r="G48" s="8">
         <v>100016</v>
       </c>
-      <c r="G48" s="8">
+      <c r="H48" s="8">
         <v>1</v>
       </c>
-      <c r="H48" s="10">
-        <v>0</v>
-      </c>
-      <c r="I48" s="8">
+      <c r="I48" s="10">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8">
         <v>1</v>
       </c>
-      <c r="J48" s="8">
-        <v>0</v>
-      </c>
       <c r="K48" s="8">
         <v>0</v>
       </c>
-      <c r="L48" s="12">
-        <v>0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0</v>
-      </c>
-      <c r="N48" s="13" t="s">
+      <c r="L48" s="8">
+        <v>0</v>
+      </c>
+      <c r="M48" s="12">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0</v>
+      </c>
+      <c r="O48" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="O48" s="14">
+      <c r="P48" s="14">
         <v>402</v>
       </c>
-      <c r="P48" s="14">
-        <v>0</v>
-      </c>
       <c r="Q48" s="14">
+        <v>0</v>
+      </c>
+      <c r="R48" s="14">
         <v>3</v>
       </c>
-      <c r="R48" s="19" t="s">
+      <c r="S48" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="S48" s="21"/>
+      <c r="T48" s="19" t="s">
+        <v>355</v>
+      </c>
     </row>
-    <row r="49" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="8">
         <v>600101</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" s="8">
         <v>6</v>
       </c>
-      <c r="F49" s="8">
+      <c r="G49" s="8">
         <v>100014</v>
       </c>
-      <c r="G49" s="8">
+      <c r="H49" s="8">
         <v>1</v>
       </c>
-      <c r="H49" s="10">
-        <v>0</v>
-      </c>
-      <c r="I49" s="8">
+      <c r="I49" s="10">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
         <v>1</v>
       </c>
-      <c r="J49" s="8">
-        <v>0</v>
-      </c>
       <c r="K49" s="8">
         <v>0</v>
       </c>
-      <c r="L49" s="12">
-        <v>0</v>
-      </c>
-      <c r="M49" s="24" t="s">
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="12">
+        <v>0</v>
+      </c>
+      <c r="N49" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N49" s="26" t="s">
+      <c r="O49" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O49" s="22" t="s">
+      <c r="P49" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="P49" s="22" t="s">
+      <c r="Q49" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="Q49" s="22" t="s">
+      <c r="R49" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R49" s="27" t="s">
+      <c r="S49" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="T49" s="29" t="s">
-        <v>241</v>
-      </c>
+      <c r="T49" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="U49" s="28"/>
     </row>
-    <row r="50" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="8">
         <v>600102</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="F50" s="8">
         <v>6</v>
       </c>
-      <c r="F50" s="8">
+      <c r="G50" s="8">
         <v>100014</v>
       </c>
-      <c r="G50" s="8">
+      <c r="H50" s="8">
         <v>1</v>
       </c>
-      <c r="H50" s="10">
-        <v>0</v>
-      </c>
-      <c r="I50" s="8">
+      <c r="I50" s="10">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8">
         <v>1</v>
       </c>
-      <c r="J50" s="8">
-        <v>0</v>
-      </c>
       <c r="K50" s="8">
         <v>0</v>
       </c>
-      <c r="L50" s="12">
-        <v>0</v>
-      </c>
-      <c r="M50" s="24" t="s">
+      <c r="L50" s="8">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0</v>
+      </c>
+      <c r="N50" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N50" s="26" t="s">
+      <c r="O50" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O50" s="22" t="s">
+      <c r="P50" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="P50" s="22" t="s">
+      <c r="Q50" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q50" s="22" t="s">
+      <c r="R50" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R50" s="27" t="s">
+      <c r="S50" s="26" t="s">
         <v>205</v>
       </c>
+      <c r="T50" s="26" t="s">
+        <v>357</v>
+      </c>
     </row>
-    <row r="51" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="8">
         <v>600103</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F51" s="8">
         <v>6</v>
       </c>
-      <c r="F51" s="8">
+      <c r="G51" s="8">
         <v>100014</v>
       </c>
-      <c r="G51" s="8">
+      <c r="H51" s="8">
         <v>1</v>
       </c>
-      <c r="H51" s="10">
-        <v>0</v>
-      </c>
-      <c r="I51" s="8">
+      <c r="I51" s="10">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8">
         <v>1</v>
       </c>
-      <c r="J51" s="8">
-        <v>0</v>
-      </c>
       <c r="K51" s="8">
         <v>0</v>
       </c>
-      <c r="L51" s="12">
-        <v>0</v>
-      </c>
-      <c r="M51" s="24" t="s">
+      <c r="L51" s="8">
+        <v>0</v>
+      </c>
+      <c r="M51" s="12">
+        <v>0</v>
+      </c>
+      <c r="N51" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N51" s="26" t="s">
+      <c r="O51" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O51" s="22" t="s">
+      <c r="P51" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="P51" s="22" t="s">
+      <c r="Q51" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q51" s="22" t="s">
+      <c r="R51" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="R51" s="27" t="s">
+      <c r="S51" s="26" t="s">
         <v>206</v>
       </c>
+      <c r="T51" s="26" t="s">
+        <v>358</v>
+      </c>
     </row>
-    <row r="52" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="8">
         <v>600104</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="F52" s="8">
         <v>6</v>
       </c>
-      <c r="F52" s="8">
+      <c r="G52" s="8">
         <v>100014</v>
       </c>
-      <c r="G52" s="8">
+      <c r="H52" s="8">
         <v>1</v>
       </c>
-      <c r="H52" s="10">
-        <v>0</v>
-      </c>
-      <c r="I52" s="8">
+      <c r="I52" s="10">
+        <v>0</v>
+      </c>
+      <c r="J52" s="8">
         <v>1</v>
       </c>
-      <c r="J52" s="8">
-        <v>0</v>
-      </c>
       <c r="K52" s="8">
         <v>0</v>
       </c>
-      <c r="L52" s="12">
-        <v>0</v>
-      </c>
-      <c r="M52" s="24" t="s">
+      <c r="L52" s="8">
+        <v>0</v>
+      </c>
+      <c r="M52" s="12">
+        <v>0</v>
+      </c>
+      <c r="N52" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N52" s="26" t="s">
+      <c r="O52" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O52" s="22" t="s">
+      <c r="P52" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="P52" s="22" t="s">
+      <c r="Q52" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q52" s="22" t="s">
+      <c r="R52" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R52" s="27" t="s">
+      <c r="S52" s="26" t="s">
         <v>207</v>
       </c>
+      <c r="T52" s="26" t="s">
+        <v>359</v>
+      </c>
     </row>
-    <row r="53" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="8">
         <v>600105</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="F53" s="8">
         <v>6</v>
       </c>
-      <c r="F53" s="8">
+      <c r="G53" s="8">
         <v>100014</v>
       </c>
-      <c r="G53" s="8">
+      <c r="H53" s="8">
         <v>1</v>
       </c>
-      <c r="H53" s="10">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8">
+      <c r="I53" s="10">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
         <v>1</v>
       </c>
-      <c r="J53" s="8">
-        <v>0</v>
-      </c>
       <c r="K53" s="8">
         <v>0</v>
       </c>
-      <c r="L53" s="12">
-        <v>0</v>
-      </c>
-      <c r="M53" s="24" t="s">
+      <c r="L53" s="8">
+        <v>0</v>
+      </c>
+      <c r="M53" s="12">
+        <v>0</v>
+      </c>
+      <c r="N53" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N53" s="26" t="s">
+      <c r="O53" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O53" s="22" t="s">
+      <c r="P53" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="P53" s="22" t="s">
+      <c r="Q53" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q53" s="22" t="s">
+      <c r="R53" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R53" s="27" t="s">
+      <c r="S53" s="26" t="s">
         <v>208</v>
       </c>
+      <c r="T53" s="26" t="s">
+        <v>360</v>
+      </c>
     </row>
-    <row r="54" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="8">
         <v>600106</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="F54" s="8">
         <v>6</v>
       </c>
-      <c r="F54" s="8">
+      <c r="G54" s="8">
         <v>100014</v>
       </c>
-      <c r="G54" s="8">
+      <c r="H54" s="8">
         <v>1</v>
       </c>
-      <c r="H54" s="10">
-        <v>0</v>
-      </c>
-      <c r="I54" s="8">
+      <c r="I54" s="10">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8">
         <v>1</v>
       </c>
-      <c r="J54" s="8">
-        <v>0</v>
-      </c>
       <c r="K54" s="8">
         <v>0</v>
       </c>
-      <c r="L54" s="12">
-        <v>0</v>
-      </c>
-      <c r="M54" s="24" t="s">
+      <c r="L54" s="8">
+        <v>0</v>
+      </c>
+      <c r="M54" s="12">
+        <v>0</v>
+      </c>
+      <c r="N54" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N54" s="26" t="s">
+      <c r="O54" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O54" s="22" t="s">
+      <c r="P54" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="P54" s="22" t="s">
+      <c r="Q54" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q54" s="22" t="s">
+      <c r="R54" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="R54" s="27" t="s">
+      <c r="S54" s="26" t="s">
         <v>209</v>
       </c>
+      <c r="T54" s="26" t="s">
+        <v>361</v>
+      </c>
     </row>
-    <row r="55" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="8">
         <v>600107</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="F55" s="8">
         <v>6</v>
       </c>
-      <c r="F55" s="8">
+      <c r="G55" s="8">
         <v>100014</v>
       </c>
-      <c r="G55" s="8">
+      <c r="H55" s="8">
         <v>1</v>
       </c>
-      <c r="H55" s="10">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8">
+      <c r="I55" s="10">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
         <v>1</v>
       </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
       <c r="K55" s="8">
         <v>0</v>
       </c>
-      <c r="L55" s="12">
-        <v>0</v>
-      </c>
-      <c r="M55" s="24" t="s">
+      <c r="L55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="12">
+        <v>0</v>
+      </c>
+      <c r="N55" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N55" s="26" t="s">
+      <c r="O55" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O55" s="22" t="s">
+      <c r="P55" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="P55" s="22" t="s">
+      <c r="Q55" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="Q55" s="22" t="s">
+      <c r="R55" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R55" s="27" t="s">
+      <c r="S55" s="26" t="s">
         <v>210</v>
       </c>
+      <c r="T55" s="26" t="s">
+        <v>362</v>
+      </c>
     </row>
-    <row r="56" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="8">
         <v>600108</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="F56" s="8">
         <v>6</v>
       </c>
-      <c r="F56" s="8">
+      <c r="G56" s="8">
         <v>100014</v>
       </c>
-      <c r="G56" s="8">
+      <c r="H56" s="8">
         <v>1</v>
       </c>
-      <c r="H56" s="10">
-        <v>0</v>
-      </c>
-      <c r="I56" s="8">
+      <c r="I56" s="10">
+        <v>0</v>
+      </c>
+      <c r="J56" s="8">
         <v>1</v>
       </c>
-      <c r="J56" s="8">
-        <v>0</v>
-      </c>
       <c r="K56" s="8">
         <v>0</v>
       </c>
-      <c r="L56" s="12">
-        <v>0</v>
-      </c>
-      <c r="M56" s="24" t="s">
+      <c r="L56" s="8">
+        <v>0</v>
+      </c>
+      <c r="M56" s="12">
+        <v>0</v>
+      </c>
+      <c r="N56" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N56" s="26" t="s">
+      <c r="O56" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O56" s="22" t="s">
+      <c r="P56" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="P56" s="22" t="s">
+      <c r="Q56" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="Q56" s="22" t="s">
+      <c r="R56" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R56" s="27" t="s">
+      <c r="S56" s="26" t="s">
         <v>211</v>
       </c>
+      <c r="T56" s="26" t="s">
+        <v>363</v>
+      </c>
     </row>
-    <row r="57" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="8">
         <v>600109</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="F57" s="8">
         <v>6</v>
       </c>
-      <c r="F57" s="8">
+      <c r="G57" s="8">
         <v>100014</v>
       </c>
-      <c r="G57" s="8">
+      <c r="H57" s="8">
         <v>1</v>
       </c>
-      <c r="H57" s="10">
-        <v>0</v>
-      </c>
-      <c r="I57" s="8">
+      <c r="I57" s="10">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8">
         <v>1</v>
       </c>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
       <c r="K57" s="8">
         <v>0</v>
       </c>
-      <c r="L57" s="12">
-        <v>0</v>
-      </c>
-      <c r="M57" s="24" t="s">
+      <c r="L57" s="8">
+        <v>0</v>
+      </c>
+      <c r="M57" s="12">
+        <v>0</v>
+      </c>
+      <c r="N57" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N57" s="26" t="s">
+      <c r="O57" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O57" s="22" t="s">
+      <c r="P57" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="P57" s="22" t="s">
+      <c r="Q57" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q57" s="22" t="s">
+      <c r="R57" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R57" s="27" t="s">
+      <c r="S57" s="26" t="s">
         <v>212</v>
       </c>
+      <c r="T57" s="26" t="s">
+        <v>364</v>
+      </c>
     </row>
-    <row r="58" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="8">
         <v>600110</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="F58" s="8">
         <v>6</v>
       </c>
-      <c r="F58" s="8">
+      <c r="G58" s="8">
         <v>100014</v>
       </c>
-      <c r="G58" s="8">
+      <c r="H58" s="8">
         <v>1</v>
       </c>
-      <c r="H58" s="10">
-        <v>0</v>
-      </c>
-      <c r="I58" s="8">
+      <c r="I58" s="10">
+        <v>0</v>
+      </c>
+      <c r="J58" s="8">
         <v>1</v>
       </c>
-      <c r="J58" s="8">
-        <v>0</v>
-      </c>
       <c r="K58" s="8">
         <v>0</v>
       </c>
-      <c r="L58" s="12">
-        <v>0</v>
-      </c>
-      <c r="M58" s="24" t="s">
+      <c r="L58" s="8">
+        <v>0</v>
+      </c>
+      <c r="M58" s="12">
+        <v>0</v>
+      </c>
+      <c r="N58" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N58" s="26" t="s">
+      <c r="O58" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O58" s="22" t="s">
+      <c r="P58" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="P58" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q58" s="22" t="s">
+      <c r="Q58" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="R58" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R58" s="27" t="s">
-        <v>242</v>
+      <c r="S58" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="T58" s="26" t="s">
+        <v>365</v>
       </c>
     </row>
-    <row r="59" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="8">
         <v>600111</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="F59" s="8">
         <v>6</v>
       </c>
-      <c r="F59" s="8">
+      <c r="G59" s="8">
         <v>100014</v>
       </c>
-      <c r="G59" s="8">
+      <c r="H59" s="8">
         <v>1</v>
       </c>
-      <c r="H59" s="10">
-        <v>0</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="I59" s="10">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8">
         <v>1</v>
       </c>
-      <c r="J59" s="8">
-        <v>0</v>
-      </c>
       <c r="K59" s="8">
         <v>0</v>
       </c>
-      <c r="L59" s="12">
-        <v>0</v>
-      </c>
-      <c r="M59" s="24" t="s">
+      <c r="L59" s="8">
+        <v>0</v>
+      </c>
+      <c r="M59" s="12">
+        <v>0</v>
+      </c>
+      <c r="N59" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N59" s="26" t="s">
+      <c r="O59" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O59" s="22" t="s">
+      <c r="P59" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="P59" s="22" t="s">
+      <c r="Q59" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q59" s="22" t="s">
+      <c r="R59" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R59" s="27" t="s">
+      <c r="S59" s="26" t="s">
         <v>214</v>
       </c>
+      <c r="T59" s="26" t="s">
+        <v>366</v>
+      </c>
     </row>
-    <row r="60" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="8">
         <v>600112</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="F60" s="8">
         <v>6</v>
       </c>
-      <c r="F60" s="8">
+      <c r="G60" s="8">
         <v>100014</v>
       </c>
-      <c r="G60" s="8">
+      <c r="H60" s="8">
         <v>1</v>
       </c>
-      <c r="H60" s="10">
-        <v>0</v>
-      </c>
-      <c r="I60" s="8">
+      <c r="I60" s="10">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8">
         <v>1</v>
       </c>
-      <c r="J60" s="8">
-        <v>0</v>
-      </c>
       <c r="K60" s="8">
         <v>0</v>
       </c>
-      <c r="L60" s="12">
-        <v>0</v>
-      </c>
-      <c r="M60" s="24" t="s">
+      <c r="L60" s="8">
+        <v>0</v>
+      </c>
+      <c r="M60" s="12">
+        <v>0</v>
+      </c>
+      <c r="N60" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N60" s="26" t="s">
+      <c r="O60" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O60" s="22" t="s">
+      <c r="P60" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="P60" s="22" t="s">
+      <c r="Q60" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q60" s="22" t="s">
+      <c r="R60" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R60" s="27" t="s">
+      <c r="S60" s="26" t="s">
         <v>215</v>
       </c>
+      <c r="T60" s="26" t="s">
+        <v>367</v>
+      </c>
     </row>
-    <row r="61" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="8">
         <v>600113</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="F61" s="8">
         <v>6</v>
       </c>
-      <c r="F61" s="8">
+      <c r="G61" s="8">
         <v>100014</v>
       </c>
-      <c r="G61" s="8">
+      <c r="H61" s="8">
         <v>1</v>
       </c>
-      <c r="H61" s="10">
-        <v>0</v>
-      </c>
-      <c r="I61" s="8">
+      <c r="I61" s="10">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8">
         <v>1</v>
       </c>
-      <c r="J61" s="8">
-        <v>0</v>
-      </c>
       <c r="K61" s="8">
         <v>0</v>
       </c>
-      <c r="L61" s="12">
-        <v>0</v>
-      </c>
-      <c r="M61" s="24" t="s">
+      <c r="L61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="12">
+        <v>0</v>
+      </c>
+      <c r="N61" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N61" s="26" t="s">
+      <c r="O61" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O61" s="22" t="s">
+      <c r="P61" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="P61" s="22" t="s">
+      <c r="Q61" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q61" s="22" t="s">
+      <c r="R61" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R61" s="27" t="s">
+      <c r="S61" s="26" t="s">
         <v>216</v>
       </c>
+      <c r="T61" s="26" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="62" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="8">
         <v>600114</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="F62" s="8">
         <v>6</v>
       </c>
-      <c r="F62" s="8">
+      <c r="G62" s="8">
         <v>100014</v>
       </c>
-      <c r="G62" s="8">
+      <c r="H62" s="8">
         <v>1</v>
       </c>
-      <c r="H62" s="10">
-        <v>0</v>
-      </c>
-      <c r="I62" s="8">
+      <c r="I62" s="10">
+        <v>0</v>
+      </c>
+      <c r="J62" s="8">
         <v>1</v>
       </c>
-      <c r="J62" s="8">
-        <v>0</v>
-      </c>
       <c r="K62" s="8">
         <v>0</v>
       </c>
-      <c r="L62" s="12">
-        <v>0</v>
-      </c>
-      <c r="M62" s="24" t="s">
+      <c r="L62" s="8">
+        <v>0</v>
+      </c>
+      <c r="M62" s="12">
+        <v>0</v>
+      </c>
+      <c r="N62" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N62" s="26" t="s">
+      <c r="O62" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O62" s="22" t="s">
+      <c r="P62" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="P62" s="22" t="s">
+      <c r="Q62" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q62" s="22" t="s">
+      <c r="R62" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R62" s="27" t="s">
+      <c r="S62" s="26" t="s">
         <v>217</v>
       </c>
+      <c r="T62" s="26" t="s">
+        <v>369</v>
+      </c>
     </row>
-    <row r="63" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="8">
         <v>600115</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="F63" s="8">
         <v>6</v>
       </c>
-      <c r="F63" s="8">
+      <c r="G63" s="8">
         <v>100014</v>
       </c>
-      <c r="G63" s="8">
+      <c r="H63" s="8">
         <v>1</v>
       </c>
-      <c r="H63" s="10">
-        <v>0</v>
-      </c>
-      <c r="I63" s="8">
+      <c r="I63" s="10">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
         <v>1</v>
       </c>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
       <c r="K63" s="8">
         <v>0</v>
       </c>
-      <c r="L63" s="12">
-        <v>0</v>
-      </c>
-      <c r="M63" s="24" t="s">
+      <c r="L63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="12">
+        <v>0</v>
+      </c>
+      <c r="N63" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="N63" s="26" t="s">
+      <c r="O63" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="O63" s="22" t="s">
+      <c r="P63" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="P63" s="22" t="s">
+      <c r="Q63" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q63" s="22" t="s">
+      <c r="R63" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R63" s="27" t="s">
+      <c r="S63" s="26" t="s">
         <v>218</v>
       </c>
+      <c r="T63" s="26" t="s">
+        <v>370</v>
+      </c>
     </row>
-    <row r="64" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="8">
         <v>600201</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="F64" s="8">
         <v>6</v>
       </c>
-      <c r="F64" s="8">
+      <c r="G64" s="8">
         <v>100014</v>
       </c>
-      <c r="G64" s="8">
+      <c r="H64" s="8">
         <v>1</v>
       </c>
-      <c r="H64" s="10">
-        <v>0</v>
-      </c>
-      <c r="I64" s="8">
+      <c r="I64" s="10">
+        <v>0</v>
+      </c>
+      <c r="J64" s="8">
         <v>1</v>
       </c>
-      <c r="J64" s="8">
-        <v>0</v>
-      </c>
       <c r="K64" s="8">
         <v>0</v>
       </c>
-      <c r="L64" s="12">
-        <v>0</v>
-      </c>
-      <c r="M64" s="24" t="s">
+      <c r="L64" s="8">
+        <v>0</v>
+      </c>
+      <c r="M64" s="12">
+        <v>0</v>
+      </c>
+      <c r="N64" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N64" s="26" t="s">
+      <c r="O64" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O64" s="22" t="s">
+      <c r="P64" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="P64" s="22" t="s">
+      <c r="Q64" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q64" s="22" t="s">
+      <c r="R64" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="R64" s="27" t="s">
+      <c r="S64" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="T64" s="29" t="s">
-        <v>240</v>
-      </c>
+      <c r="T64" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="U64" s="28"/>
     </row>
-    <row r="65" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="8">
         <v>600202</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="F65" s="8">
         <v>6</v>
       </c>
-      <c r="F65" s="8">
+      <c r="G65" s="8">
         <v>100014</v>
       </c>
-      <c r="G65" s="8">
+      <c r="H65" s="8">
         <v>1</v>
       </c>
-      <c r="H65" s="10">
-        <v>0</v>
-      </c>
-      <c r="I65" s="8">
+      <c r="I65" s="10">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8">
         <v>1</v>
       </c>
-      <c r="J65" s="8">
-        <v>0</v>
-      </c>
       <c r="K65" s="8">
         <v>0</v>
       </c>
-      <c r="L65" s="12">
-        <v>0</v>
-      </c>
-      <c r="M65" s="24" t="s">
+      <c r="L65" s="8">
+        <v>0</v>
+      </c>
+      <c r="M65" s="12">
+        <v>0</v>
+      </c>
+      <c r="N65" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N65" s="26" t="s">
+      <c r="O65" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O65" s="22" t="s">
+      <c r="P65" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="P65" s="22" t="s">
+      <c r="Q65" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q65" s="22" t="s">
+      <c r="R65" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="R65" s="27" t="s">
+      <c r="S65" s="26" t="s">
         <v>220</v>
       </c>
+      <c r="T65" s="26" t="s">
+        <v>372</v>
+      </c>
     </row>
-    <row r="66" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="8">
         <v>600203</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="F66" s="8">
         <v>6</v>
       </c>
-      <c r="F66" s="8">
+      <c r="G66" s="8">
         <v>100014</v>
       </c>
-      <c r="G66" s="8">
+      <c r="H66" s="8">
         <v>1</v>
       </c>
-      <c r="H66" s="10">
-        <v>0</v>
-      </c>
-      <c r="I66" s="8">
+      <c r="I66" s="10">
+        <v>0</v>
+      </c>
+      <c r="J66" s="8">
         <v>1</v>
       </c>
-      <c r="J66" s="8">
-        <v>0</v>
-      </c>
       <c r="K66" s="8">
         <v>0</v>
       </c>
-      <c r="L66" s="12">
-        <v>0</v>
-      </c>
-      <c r="M66" s="24" t="s">
+      <c r="L66" s="8">
+        <v>0</v>
+      </c>
+      <c r="M66" s="12">
+        <v>0</v>
+      </c>
+      <c r="N66" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N66" s="26" t="s">
+      <c r="O66" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O66" s="22" t="s">
+      <c r="P66" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="P66" s="22" t="s">
+      <c r="Q66" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="Q66" s="22" t="s">
+      <c r="R66" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R66" s="27" t="s">
+      <c r="S66" s="26" t="s">
         <v>213</v>
       </c>
+      <c r="T66" s="26" t="s">
+        <v>373</v>
+      </c>
     </row>
-    <row r="67" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="8">
         <v>600204</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="8">
         <v>6</v>
       </c>
-      <c r="F67" s="8">
+      <c r="G67" s="8">
         <v>100014</v>
       </c>
-      <c r="G67" s="8">
+      <c r="H67" s="8">
         <v>1</v>
       </c>
-      <c r="H67" s="10">
-        <v>0</v>
-      </c>
-      <c r="I67" s="8">
+      <c r="I67" s="10">
+        <v>0</v>
+      </c>
+      <c r="J67" s="8">
         <v>1</v>
       </c>
-      <c r="J67" s="8">
-        <v>0</v>
-      </c>
       <c r="K67" s="8">
         <v>0</v>
       </c>
-      <c r="L67" s="12">
-        <v>0</v>
-      </c>
-      <c r="M67" s="24" t="s">
+      <c r="L67" s="8">
+        <v>0</v>
+      </c>
+      <c r="M67" s="12">
+        <v>0</v>
+      </c>
+      <c r="N67" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N67" s="26" t="s">
+      <c r="O67" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O67" s="22" t="s">
+      <c r="P67" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="P67" s="22" t="s">
+      <c r="Q67" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="Q67" s="22" t="s">
+      <c r="R67" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="R67" s="27" t="s">
+      <c r="S67" s="26" t="s">
         <v>221</v>
       </c>
+      <c r="T67" s="26" t="s">
+        <v>374</v>
+      </c>
     </row>
-    <row r="68" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="8">
         <v>600205</v>
       </c>
-      <c r="D68" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E68" s="8">
+      <c r="D68" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="F68" s="8">
         <v>6</v>
       </c>
-      <c r="F68" s="8">
+      <c r="G68" s="8">
         <v>100014</v>
       </c>
-      <c r="G68" s="8">
+      <c r="H68" s="8">
         <v>1</v>
       </c>
-      <c r="H68" s="10">
-        <v>0</v>
-      </c>
-      <c r="I68" s="8">
+      <c r="I68" s="10">
+        <v>0</v>
+      </c>
+      <c r="J68" s="8">
         <v>1</v>
       </c>
-      <c r="J68" s="8">
-        <v>0</v>
-      </c>
       <c r="K68" s="8">
         <v>0</v>
       </c>
-      <c r="L68" s="12">
-        <v>0</v>
-      </c>
-      <c r="M68" s="24" t="s">
+      <c r="L68" s="8">
+        <v>0</v>
+      </c>
+      <c r="M68" s="12">
+        <v>0</v>
+      </c>
+      <c r="N68" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N68" s="26" t="s">
+      <c r="O68" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O68" s="22" t="s">
+      <c r="P68" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="P68" s="22" t="s">
+      <c r="Q68" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q68" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="R68" s="27" t="s">
-        <v>245</v>
+      <c r="R68" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="S68" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="T68" s="26" t="s">
+        <v>375</v>
       </c>
     </row>
-    <row r="69" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="8">
         <v>600206</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F69" s="8">
         <v>6</v>
       </c>
-      <c r="F69" s="8">
+      <c r="G69" s="8">
         <v>100014</v>
       </c>
-      <c r="G69" s="8">
+      <c r="H69" s="8">
         <v>1</v>
       </c>
-      <c r="H69" s="10">
-        <v>0</v>
-      </c>
-      <c r="I69" s="8">
+      <c r="I69" s="10">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8">
         <v>1</v>
       </c>
-      <c r="J69" s="8">
-        <v>0</v>
-      </c>
       <c r="K69" s="8">
         <v>0</v>
       </c>
-      <c r="L69" s="12">
-        <v>0</v>
-      </c>
-      <c r="M69" s="25" t="s">
+      <c r="L69" s="8">
+        <v>0</v>
+      </c>
+      <c r="M69" s="12">
+        <v>0</v>
+      </c>
+      <c r="N69" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="N69" s="26" t="s">
+      <c r="O69" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O69" s="23" t="s">
+      <c r="P69" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="P69" s="23" t="s">
+      <c r="Q69" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="Q69" s="23" t="s">
+      <c r="R69" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="R69" s="28" t="s">
+      <c r="S69" s="27" t="s">
         <v>222</v>
       </c>
+      <c r="T69" s="27" t="s">
+        <v>376</v>
+      </c>
     </row>
-    <row r="70" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="8">
         <v>600207</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="F70" s="8">
         <v>6</v>
       </c>
-      <c r="F70" s="8">
+      <c r="G70" s="8">
         <v>100014</v>
       </c>
-      <c r="G70" s="8">
+      <c r="H70" s="8">
         <v>1</v>
       </c>
-      <c r="H70" s="10">
-        <v>0</v>
-      </c>
-      <c r="I70" s="8">
+      <c r="I70" s="10">
+        <v>0</v>
+      </c>
+      <c r="J70" s="8">
         <v>1</v>
       </c>
-      <c r="J70" s="8">
-        <v>0</v>
-      </c>
       <c r="K70" s="8">
         <v>0</v>
       </c>
-      <c r="L70" s="12">
-        <v>0</v>
-      </c>
-      <c r="M70" s="24" t="s">
+      <c r="L70" s="8">
+        <v>0</v>
+      </c>
+      <c r="M70" s="12">
+        <v>0</v>
+      </c>
+      <c r="N70" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N70" s="26" t="s">
+      <c r="O70" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O70" s="22" t="s">
+      <c r="P70" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="P70" s="22" t="s">
+      <c r="Q70" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="Q70" s="22" t="s">
+      <c r="R70" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R70" s="27" t="s">
+      <c r="S70" s="26" t="s">
         <v>223</v>
       </c>
+      <c r="T70" s="26" t="s">
+        <v>377</v>
+      </c>
     </row>
-    <row r="71" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="8">
         <v>600208</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="F71" s="8">
         <v>6</v>
       </c>
-      <c r="F71" s="8">
+      <c r="G71" s="8">
         <v>100014</v>
       </c>
-      <c r="G71" s="8">
+      <c r="H71" s="8">
         <v>1</v>
       </c>
-      <c r="H71" s="10">
-        <v>0</v>
-      </c>
-      <c r="I71" s="8">
+      <c r="I71" s="10">
+        <v>0</v>
+      </c>
+      <c r="J71" s="8">
         <v>1</v>
       </c>
-      <c r="J71" s="8">
-        <v>0</v>
-      </c>
       <c r="K71" s="8">
         <v>0</v>
       </c>
-      <c r="L71" s="12">
-        <v>0</v>
-      </c>
-      <c r="M71" s="24" t="s">
+      <c r="L71" s="8">
+        <v>0</v>
+      </c>
+      <c r="M71" s="12">
+        <v>0</v>
+      </c>
+      <c r="N71" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N71" s="26" t="s">
+      <c r="O71" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O71" s="22" t="s">
+      <c r="P71" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="P71" s="22" t="s">
+      <c r="Q71" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q71" s="22" t="s">
+      <c r="R71" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="R71" s="27" t="s">
+      <c r="S71" s="26" t="s">
         <v>224</v>
       </c>
+      <c r="T71" s="26" t="s">
+        <v>378</v>
+      </c>
     </row>
-    <row r="72" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="8">
         <v>600209</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="F72" s="8">
         <v>6</v>
       </c>
-      <c r="F72" s="8">
+      <c r="G72" s="8">
         <v>100014</v>
       </c>
-      <c r="G72" s="8">
+      <c r="H72" s="8">
         <v>1</v>
       </c>
-      <c r="H72" s="10">
-        <v>0</v>
-      </c>
-      <c r="I72" s="8">
+      <c r="I72" s="10">
+        <v>0</v>
+      </c>
+      <c r="J72" s="8">
         <v>1</v>
       </c>
-      <c r="J72" s="8">
-        <v>0</v>
-      </c>
       <c r="K72" s="8">
         <v>0</v>
       </c>
-      <c r="L72" s="12">
-        <v>0</v>
-      </c>
-      <c r="M72" s="24" t="s">
+      <c r="L72" s="8">
+        <v>0</v>
+      </c>
+      <c r="M72" s="12">
+        <v>0</v>
+      </c>
+      <c r="N72" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="N72" s="26" t="s">
+      <c r="O72" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="O72" s="22" t="s">
+      <c r="P72" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="P72" s="22" t="s">
+      <c r="Q72" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="Q72" s="22" t="s">
+      <c r="R72" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="R72" s="27" t="s">
+      <c r="S72" s="26" t="s">
         <v>225</v>
       </c>
+      <c r="T72" s="26" t="s">
+        <v>379</v>
+      </c>
     </row>
-    <row r="73" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="8">
         <v>600301</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F73" s="8">
         <v>6</v>
       </c>
-      <c r="F73" s="8">
+      <c r="G73" s="8">
         <v>100014</v>
       </c>
-      <c r="G73" s="8">
+      <c r="H73" s="8">
         <v>1</v>
       </c>
-      <c r="H73" s="10">
-        <v>0</v>
-      </c>
-      <c r="I73" s="8">
+      <c r="I73" s="10">
+        <v>0</v>
+      </c>
+      <c r="J73" s="8">
         <v>1</v>
       </c>
-      <c r="J73" s="8">
-        <v>0</v>
-      </c>
       <c r="K73" s="8">
         <v>0</v>
       </c>
-      <c r="L73" s="12">
-        <v>0</v>
-      </c>
-      <c r="M73" s="24" t="s">
+      <c r="L73" s="8">
+        <v>0</v>
+      </c>
+      <c r="M73" s="12">
+        <v>0</v>
+      </c>
+      <c r="N73" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N73" s="26" t="s">
+      <c r="O73" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O73" s="22" t="s">
+      <c r="P73" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="P73" s="22" t="s">
+      <c r="Q73" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="Q73" s="22" t="s">
+      <c r="R73" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R73" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="T73" s="29" t="s">
-        <v>239</v>
-      </c>
+      <c r="S73" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="T73" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="U73" s="28"/>
     </row>
-    <row r="74" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="8">
         <v>600302</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F74" s="8">
         <v>6</v>
       </c>
-      <c r="F74" s="8">
+      <c r="G74" s="8">
         <v>100014</v>
       </c>
-      <c r="G74" s="8">
+      <c r="H74" s="8">
         <v>1</v>
       </c>
-      <c r="H74" s="10">
-        <v>0</v>
-      </c>
-      <c r="I74" s="8">
+      <c r="I74" s="10">
+        <v>0</v>
+      </c>
+      <c r="J74" s="8">
         <v>1</v>
       </c>
-      <c r="J74" s="8">
-        <v>0</v>
-      </c>
       <c r="K74" s="8">
         <v>0</v>
       </c>
-      <c r="L74" s="12">
-        <v>0</v>
-      </c>
-      <c r="M74" s="24" t="s">
+      <c r="L74" s="8">
+        <v>0</v>
+      </c>
+      <c r="M74" s="12">
+        <v>0</v>
+      </c>
+      <c r="N74" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N74" s="26" t="s">
+      <c r="O74" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O74" s="22" t="s">
+      <c r="P74" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="P74" s="22" t="s">
+      <c r="Q74" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="Q74" s="22" t="s">
+      <c r="R74" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R74" s="27" t="s">
+      <c r="S74" s="26" t="s">
         <v>226</v>
       </c>
+      <c r="T74" s="26" t="s">
+        <v>381</v>
+      </c>
     </row>
-    <row r="75" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="8">
         <v>600303</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="F75" s="8">
         <v>6</v>
       </c>
-      <c r="F75" s="8">
+      <c r="G75" s="8">
         <v>100014</v>
       </c>
-      <c r="G75" s="8">
+      <c r="H75" s="8">
         <v>1</v>
       </c>
-      <c r="H75" s="10">
-        <v>0</v>
-      </c>
-      <c r="I75" s="8">
+      <c r="I75" s="10">
+        <v>0</v>
+      </c>
+      <c r="J75" s="8">
         <v>1</v>
       </c>
-      <c r="J75" s="8">
-        <v>0</v>
-      </c>
       <c r="K75" s="8">
         <v>0</v>
       </c>
-      <c r="L75" s="12">
-        <v>0</v>
-      </c>
-      <c r="M75" s="24" t="s">
+      <c r="L75" s="8">
+        <v>0</v>
+      </c>
+      <c r="M75" s="12">
+        <v>0</v>
+      </c>
+      <c r="N75" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N75" s="26" t="s">
+      <c r="O75" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O75" s="22" t="s">
+      <c r="P75" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="P75" s="22" t="s">
+      <c r="Q75" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="Q75" s="22" t="s">
+      <c r="R75" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R75" s="27" t="s">
+      <c r="S75" s="26" t="s">
         <v>227</v>
       </c>
+      <c r="T75" s="26" t="s">
+        <v>382</v>
+      </c>
     </row>
-    <row r="76" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="8">
         <v>600304</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D76" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="F76" s="8">
         <v>6</v>
       </c>
-      <c r="F76" s="8">
+      <c r="G76" s="8">
         <v>100014</v>
       </c>
-      <c r="G76" s="8">
+      <c r="H76" s="8">
         <v>1</v>
       </c>
-      <c r="H76" s="10">
-        <v>0</v>
-      </c>
-      <c r="I76" s="8">
+      <c r="I76" s="10">
+        <v>0</v>
+      </c>
+      <c r="J76" s="8">
         <v>1</v>
       </c>
-      <c r="J76" s="8">
-        <v>0</v>
-      </c>
       <c r="K76" s="8">
         <v>0</v>
       </c>
-      <c r="L76" s="12">
-        <v>0</v>
-      </c>
-      <c r="M76" s="24" t="s">
+      <c r="L76" s="8">
+        <v>0</v>
+      </c>
+      <c r="M76" s="12">
+        <v>0</v>
+      </c>
+      <c r="N76" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N76" s="26" t="s">
+      <c r="O76" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O76" s="22" t="s">
+      <c r="P76" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="P76" s="22" t="s">
+      <c r="Q76" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="Q76" s="22" t="s">
+      <c r="R76" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R76" s="27" t="s">
+      <c r="S76" s="26" t="s">
         <v>228</v>
       </c>
+      <c r="T76" s="26" t="s">
+        <v>383</v>
+      </c>
     </row>
-    <row r="77" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="8">
         <v>600305</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="F77" s="8">
         <v>6</v>
       </c>
-      <c r="F77" s="8">
+      <c r="G77" s="8">
         <v>100014</v>
       </c>
-      <c r="G77" s="8">
+      <c r="H77" s="8">
         <v>1</v>
       </c>
-      <c r="H77" s="10">
-        <v>0</v>
-      </c>
-      <c r="I77" s="8">
+      <c r="I77" s="10">
+        <v>0</v>
+      </c>
+      <c r="J77" s="8">
         <v>1</v>
       </c>
-      <c r="J77" s="8">
-        <v>0</v>
-      </c>
       <c r="K77" s="8">
         <v>0</v>
       </c>
-      <c r="L77" s="12">
-        <v>0</v>
-      </c>
-      <c r="M77" s="24" t="s">
+      <c r="L77" s="8">
+        <v>0</v>
+      </c>
+      <c r="M77" s="12">
+        <v>0</v>
+      </c>
+      <c r="N77" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N77" s="26" t="s">
+      <c r="O77" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O77" s="22" t="s">
+      <c r="P77" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="P77" s="22" t="s">
+      <c r="Q77" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q77" s="22" t="s">
+      <c r="R77" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R77" s="27" t="s">
+      <c r="S77" s="26" t="s">
         <v>229</v>
       </c>
+      <c r="T77" s="26" t="s">
+        <v>384</v>
+      </c>
     </row>
-    <row r="78" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="8">
         <v>600306</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="F78" s="8">
         <v>6</v>
       </c>
-      <c r="F78" s="8">
+      <c r="G78" s="8">
         <v>100014</v>
       </c>
-      <c r="G78" s="8">
+      <c r="H78" s="8">
         <v>1</v>
       </c>
-      <c r="H78" s="10">
-        <v>0</v>
-      </c>
-      <c r="I78" s="8">
+      <c r="I78" s="10">
+        <v>0</v>
+      </c>
+      <c r="J78" s="8">
         <v>1</v>
       </c>
-      <c r="J78" s="8">
-        <v>0</v>
-      </c>
       <c r="K78" s="8">
         <v>0</v>
       </c>
-      <c r="L78" s="12">
-        <v>0</v>
-      </c>
-      <c r="M78" s="24" t="s">
+      <c r="L78" s="8">
+        <v>0</v>
+      </c>
+      <c r="M78" s="12">
+        <v>0</v>
+      </c>
+      <c r="N78" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N78" s="26" t="s">
+      <c r="O78" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O78" s="22" t="s">
+      <c r="P78" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="P78" s="22" t="s">
+      <c r="Q78" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="Q78" s="22" t="s">
+      <c r="R78" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="R78" s="27" t="s">
+      <c r="S78" s="26" t="s">
         <v>230</v>
       </c>
+      <c r="T78" s="26" t="s">
+        <v>385</v>
+      </c>
     </row>
-    <row r="79" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="8">
         <v>600307</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="F79" s="8">
         <v>6</v>
       </c>
-      <c r="F79" s="8">
+      <c r="G79" s="8">
         <v>100014</v>
       </c>
-      <c r="G79" s="8">
+      <c r="H79" s="8">
         <v>1</v>
       </c>
-      <c r="H79" s="10">
-        <v>0</v>
-      </c>
-      <c r="I79" s="8">
+      <c r="I79" s="10">
+        <v>0</v>
+      </c>
+      <c r="J79" s="8">
         <v>1</v>
       </c>
-      <c r="J79" s="8">
-        <v>0</v>
-      </c>
       <c r="K79" s="8">
         <v>0</v>
       </c>
-      <c r="L79" s="12">
-        <v>0</v>
-      </c>
-      <c r="M79" s="24" t="s">
+      <c r="L79" s="8">
+        <v>0</v>
+      </c>
+      <c r="M79" s="12">
+        <v>0</v>
+      </c>
+      <c r="N79" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N79" s="26" t="s">
+      <c r="O79" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O79" s="22" t="s">
+      <c r="P79" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="P79" s="22" t="s">
+      <c r="Q79" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="Q79" s="22" t="s">
+      <c r="R79" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="R79" s="27" t="s">
+      <c r="S79" s="26" t="s">
         <v>231</v>
       </c>
+      <c r="T79" s="26" t="s">
+        <v>386</v>
+      </c>
     </row>
-    <row r="80" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="8">
         <v>600308</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="F80" s="8">
         <v>6</v>
       </c>
-      <c r="F80" s="8">
+      <c r="G80" s="8">
         <v>100014</v>
       </c>
-      <c r="G80" s="8">
+      <c r="H80" s="8">
         <v>1</v>
       </c>
-      <c r="H80" s="10">
-        <v>0</v>
-      </c>
-      <c r="I80" s="8">
+      <c r="I80" s="10">
+        <v>0</v>
+      </c>
+      <c r="J80" s="8">
         <v>1</v>
       </c>
-      <c r="J80" s="8">
-        <v>0</v>
-      </c>
       <c r="K80" s="8">
         <v>0</v>
       </c>
-      <c r="L80" s="12">
-        <v>0</v>
-      </c>
-      <c r="M80" s="24" t="s">
+      <c r="L80" s="8">
+        <v>0</v>
+      </c>
+      <c r="M80" s="12">
+        <v>0</v>
+      </c>
+      <c r="N80" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N80" s="26" t="s">
+      <c r="O80" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="O80" s="22" t="s">
+      <c r="P80" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="P80" s="22" t="s">
+      <c r="Q80" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="Q80" s="22" t="s">
+      <c r="R80" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="R80" s="27" t="s">
+      <c r="S80" s="26" t="s">
         <v>232</v>
       </c>
+      <c r="T80" s="26" t="s">
+        <v>387</v>
+      </c>
     </row>
-    <row r="81" spans="3:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="8">
         <v>700011</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F81" s="8">
         <v>7</v>
       </c>
-      <c r="F81" s="8">
+      <c r="G81" s="8">
         <v>100001</v>
       </c>
-      <c r="G81" s="8">
+      <c r="H81" s="8">
         <v>1</v>
       </c>
-      <c r="H81" s="10">
-        <v>0</v>
-      </c>
-      <c r="I81" s="8">
+      <c r="I81" s="10">
+        <v>0</v>
+      </c>
+      <c r="J81" s="8">
         <v>1</v>
       </c>
-      <c r="J81" s="8">
-        <v>0</v>
-      </c>
       <c r="K81" s="8">
         <v>0</v>
       </c>
-      <c r="L81" s="12">
+      <c r="L81" s="8">
+        <v>0</v>
+      </c>
+      <c r="M81" s="12">
         <v>5</v>
       </c>
-      <c r="M81" s="2">
+      <c r="N81" s="2">
         <v>3000</v>
       </c>
-      <c r="N81" s="13" t="s">
+      <c r="O81" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O81" s="14">
+      <c r="P81" s="14">
         <v>1001</v>
       </c>
-      <c r="P81" s="14">
-        <v>0</v>
-      </c>
       <c r="Q81" s="14">
+        <v>0</v>
+      </c>
+      <c r="R81" s="14">
         <v>1</v>
       </c>
-      <c r="R81" s="19" t="s">
+      <c r="S81" s="19" t="s">
         <v>36</v>
       </c>
+      <c r="T81" s="19" t="s">
+        <v>313</v>
+      </c>
     </row>
-    <row r="82" spans="3:18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C82" s="8">
         <v>700021</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F82" s="8">
         <v>7</v>
       </c>
-      <c r="F82" s="8">
+      <c r="G82" s="8">
         <v>100002</v>
       </c>
-      <c r="G82" s="8">
+      <c r="H82" s="8">
         <v>1</v>
       </c>
-      <c r="H82" s="10">
-        <v>0</v>
-      </c>
-      <c r="I82" s="8">
+      <c r="I82" s="10">
+        <v>0</v>
+      </c>
+      <c r="J82" s="8">
         <v>1</v>
       </c>
-      <c r="J82" s="8">
-        <v>0</v>
-      </c>
       <c r="K82" s="8">
         <v>0</v>
       </c>
-      <c r="L82" s="12">
+      <c r="L82" s="8">
+        <v>0</v>
+      </c>
+      <c r="M82" s="12">
         <v>10</v>
       </c>
-      <c r="M82" s="2">
+      <c r="N82" s="2">
         <v>4500</v>
       </c>
-      <c r="N82" s="13" t="s">
+      <c r="O82" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O82" s="14">
+      <c r="P82" s="14">
         <v>1002</v>
       </c>
-      <c r="P82" s="14">
-        <v>0</v>
-      </c>
       <c r="Q82" s="14">
+        <v>0</v>
+      </c>
+      <c r="R82" s="14">
         <v>30</v>
       </c>
-      <c r="R82" s="19" t="s">
+      <c r="S82" s="19" t="s">
         <v>38</v>
       </c>
+      <c r="T82" s="19" t="s">
+        <v>314</v>
+      </c>
     </row>
-    <row r="83" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C83" s="8">
         <v>700031</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F83" s="8">
         <v>7</v>
       </c>
-      <c r="F83" s="8">
+      <c r="G83" s="8">
         <v>100003</v>
       </c>
-      <c r="G83" s="8">
+      <c r="H83" s="8">
         <v>1</v>
       </c>
-      <c r="H83" s="10">
-        <v>0</v>
-      </c>
-      <c r="I83" s="8">
+      <c r="I83" s="10">
+        <v>0</v>
+      </c>
+      <c r="J83" s="8">
         <v>1</v>
       </c>
-      <c r="J83" s="8">
-        <v>0</v>
-      </c>
       <c r="K83" s="8">
         <v>0</v>
       </c>
-      <c r="L83" s="12">
+      <c r="L83" s="8">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12">
         <v>10</v>
       </c>
-      <c r="M83" s="2">
+      <c r="N83" s="2">
         <v>15000</v>
       </c>
-      <c r="N83" s="13" t="s">
+      <c r="O83" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O83" s="15">
+      <c r="P83" s="15">
         <v>1003</v>
       </c>
-      <c r="P83" s="15">
-        <v>0</v>
-      </c>
       <c r="Q83" s="15">
+        <v>0</v>
+      </c>
+      <c r="R83" s="15">
         <v>3</v>
       </c>
-      <c r="R83" s="19" t="s">
+      <c r="S83" s="19" t="s">
         <v>40</v>
       </c>
+      <c r="T83" s="19" t="s">
+        <v>315</v>
+      </c>
     </row>
-    <row r="84" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C84" s="8">
         <v>700041</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F84" s="8">
         <v>7</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="G84" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G84" s="8">
+      <c r="H84" s="8">
         <v>1</v>
       </c>
-      <c r="H84" s="10">
-        <v>0</v>
-      </c>
-      <c r="I84" s="8">
+      <c r="I84" s="10">
+        <v>0</v>
+      </c>
+      <c r="J84" s="8">
         <v>1</v>
       </c>
-      <c r="J84" s="8">
-        <v>0</v>
-      </c>
       <c r="K84" s="8">
         <v>0</v>
       </c>
-      <c r="L84" s="12">
+      <c r="L84" s="8">
+        <v>0</v>
+      </c>
+      <c r="M84" s="12">
         <v>10</v>
       </c>
-      <c r="M84" s="2">
+      <c r="N84" s="2">
         <v>15000</v>
       </c>
-      <c r="N84" s="13" t="s">
+      <c r="O84" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O84" s="15">
+      <c r="P84" s="15">
         <v>1004</v>
       </c>
-      <c r="P84" s="15">
-        <v>0</v>
-      </c>
       <c r="Q84" s="15">
+        <v>0</v>
+      </c>
+      <c r="R84" s="15">
         <v>1</v>
       </c>
-      <c r="R84" s="19" t="s">
+      <c r="S84" s="19" t="s">
         <v>43</v>
       </c>
+      <c r="T84" s="19" t="s">
+        <v>316</v>
+      </c>
     </row>
-    <row r="85" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="8">
         <v>700051</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F85" s="8">
         <v>7</v>
       </c>
-      <c r="F85" s="8">
+      <c r="G85" s="8">
         <v>100005</v>
       </c>
-      <c r="G85" s="8">
+      <c r="H85" s="8">
         <v>1</v>
       </c>
-      <c r="H85" s="8">
+      <c r="I85" s="8">
         <v>100052</v>
       </c>
-      <c r="I85" s="8">
+      <c r="J85" s="8">
         <v>0.5</v>
       </c>
-      <c r="J85" s="8">
-        <v>0</v>
-      </c>
       <c r="K85" s="8">
         <v>0</v>
       </c>
-      <c r="L85" s="12">
+      <c r="L85" s="8">
+        <v>0</v>
+      </c>
+      <c r="M85" s="12">
         <v>10</v>
       </c>
-      <c r="M85" s="2">
+      <c r="N85" s="2">
         <v>6000</v>
       </c>
-      <c r="N85" s="13" t="s">
+      <c r="O85" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O85" s="14">
+      <c r="P85" s="14">
         <v>1005</v>
       </c>
-      <c r="P85" s="14">
-        <v>0</v>
-      </c>
       <c r="Q85" s="14">
+        <v>0</v>
+      </c>
+      <c r="R85" s="14">
         <v>100000</v>
       </c>
-      <c r="R85" s="19" t="s">
+      <c r="S85" s="19" t="s">
         <v>45</v>
       </c>
+      <c r="T85" s="19" t="s">
+        <v>317</v>
+      </c>
     </row>
-    <row r="86" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="8">
         <v>700052</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F86" s="8">
         <v>7</v>
       </c>
-      <c r="F86" s="8">
+      <c r="G86" s="8">
         <v>100052</v>
       </c>
-      <c r="G86" s="8">
+      <c r="H86" s="8">
         <v>1</v>
       </c>
-      <c r="H86" s="10">
-        <v>0</v>
-      </c>
-      <c r="I86" s="8">
+      <c r="I86" s="10">
+        <v>0</v>
+      </c>
+      <c r="J86" s="8">
         <v>1</v>
       </c>
-      <c r="J86" s="8">
-        <v>0</v>
-      </c>
       <c r="K86" s="8">
         <v>0</v>
       </c>
-      <c r="L86" s="12">
+      <c r="L86" s="8">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12">
         <v>10</v>
       </c>
-      <c r="M86" s="2">
+      <c r="N86" s="2">
         <v>6000</v>
       </c>
-      <c r="N86" s="13" t="s">
+      <c r="O86" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O86" s="14">
+      <c r="P86" s="14">
         <v>1014</v>
       </c>
-      <c r="P86" s="14">
-        <v>0</v>
-      </c>
       <c r="Q86" s="14">
+        <v>0</v>
+      </c>
+      <c r="R86" s="14">
         <v>3</v>
       </c>
-      <c r="R86" s="19" t="s">
+      <c r="S86" s="19" t="s">
         <v>47</v>
       </c>
+      <c r="T86" s="19" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="87" spans="3:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="8">
         <v>700061</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F87" s="8">
         <v>7</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="G87" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G87" s="8">
+      <c r="H87" s="8">
         <v>1</v>
       </c>
-      <c r="H87" s="8">
+      <c r="I87" s="8">
         <v>100062</v>
       </c>
-      <c r="I87" s="8">
+      <c r="J87" s="8">
         <v>0.7</v>
       </c>
-      <c r="J87" s="8">
-        <v>0</v>
-      </c>
       <c r="K87" s="8">
         <v>0</v>
       </c>
-      <c r="L87" s="12">
+      <c r="L87" s="8">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12">
         <v>10</v>
       </c>
-      <c r="M87" s="2">
+      <c r="N87" s="2">
         <v>6000</v>
       </c>
-      <c r="N87" s="13" t="s">
+      <c r="O87" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O87" s="15">
+      <c r="P87" s="15">
         <v>1006</v>
       </c>
-      <c r="P87" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="15">
+      <c r="Q87" s="16">
+        <v>0</v>
+      </c>
+      <c r="R87" s="15">
         <v>1</v>
       </c>
-      <c r="R87" s="19" t="s">
+      <c r="S87" s="19" t="s">
         <v>50</v>
+      </c>
+      <c r="T87" s="19" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/TaskCountryConfig.xlsx
+++ b/Excel/TaskCountryConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FDD28C-44C2-419F-ACFE-883AE595C126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA716584-9E24-4E44-A4C9-116F8EE50A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="515">
   <si>
     <t>Id</t>
   </si>
@@ -673,112 +673,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>十连击破</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>探险家</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>探险专家</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>领主试炼</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>封印挑战</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物获取</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备附魔</t>
-  </si>
-  <si>
-    <t>鉴定家</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物融合</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物小成</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物洗礼</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物之战</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备洗练</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活制造</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物孵化</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>深渊挑战</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物初成</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>鉴定者</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>献上宝物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>抢占矿场</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备洗练</t>
-  </si>
-  <si>
-    <t>珍宠孵化</t>
-  </si>
-  <si>
-    <t>宠物达成</t>
-  </si>
-  <si>
-    <t>实力代表</t>
-  </si>
-  <si>
-    <t>宠物挑战</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>战力挑战</t>
-  </si>
-  <si>
-    <t>献上神宠</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸运者</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>100000</t>
   </si>
   <si>
@@ -938,122 +832,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>在野外击败10个敌方玩家，奖励5个经验盒</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用普通藏宝图10次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用高级藏宝图3次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>击败10个地狱级领主怪物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>封印之塔挑战10次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得3只全新的宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用附魔道具给自己的装备附魔5次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用鉴定道具给自己的装备鉴定5次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物合成5次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>合成1只战力达到7000点的宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物使用宠之晶洗炼达到5次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物天梯战斗获胜次数达到10次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备洗炼达到10次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活技能制造出20个道具</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功孵化5次宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑战5次深渊类型的副本</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物合成10次,</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用90点及以上的鉴定符去鉴定2次装备</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>上交一个橙色的装备</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>占领1个黄金矿</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备洗炼达到30次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用珍贵的宠物蛋成功孵化两次宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>试炼之地输出进入排行前10</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宠物天梯进入排行榜前10</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>战力排行榜进入前10</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>占领1个核心矿</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>上交一只6技能以上的宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>洗练出1个带有隐藏技能的装备</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>上交一个50级以上鉴定3属性的装备一件</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>int[]</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1066,39 +844,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>1;100000@31;20@10000159;5</t>
-  </si>
-  <si>
-    <t>1;150000@31;30@10000159;5</t>
-  </si>
-  <si>
-    <t>1;200000@31;40@10000159;10</t>
-  </si>
-  <si>
-    <t>合成1只战力达到6000点的宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>合成一只战力达到8000点的宠物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>6000</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>装备洗炼达到20次</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>20</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>大师洗练</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>TaskName_EN</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1440,135 +1193,805 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>c</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>深渊挑战</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Challenge a dungeon of abyssal type once.</t>
+  </si>
+  <si>
+    <t>传承打造</t>
+  </si>
+  <si>
+    <t>Inheritance Crafting</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>洗练大师</t>
+  </si>
+  <si>
+    <t>Refining Master</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>洗炼装备30次</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴定家</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鉴定出一个3条属性的装备</t>
+  </si>
+  <si>
+    <t>Identifies a 3-attribute piece of equipment</t>
+  </si>
+  <si>
+    <t>怪物猎手</t>
+  </si>
+  <si>
+    <t>Monster Hunter</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>击败3000只怪物</t>
+  </si>
+  <si>
+    <t>Defeat 3000 monsters.</t>
+  </si>
+  <si>
+    <t>荣获新宠</t>
+  </si>
+  <si>
+    <t>Gained new popularity</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>获得5只全新的宠物</t>
+  </si>
+  <si>
+    <t>Get 5 brand new pets</t>
+  </si>
+  <si>
+    <t>封印挑战</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>使用鉴定道具给自己的装备鉴定15次</t>
+  </si>
+  <si>
+    <t>Use the identification item to identify one's equipment 15 times.</t>
+  </si>
+  <si>
+    <t>宠物合成</t>
+  </si>
+  <si>
+    <t>Pet combination</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>合成1只战力达到7000点的宠物</t>
+  </si>
+  <si>
+    <t>Synthesize a pet with a combat power of 7000 points.</t>
+  </si>
+  <si>
+    <t>寻找宝物</t>
+  </si>
+  <si>
+    <t>Search for treasures</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>藏宝大师</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Treasure Master</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>开启1次高级藏宝图</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Activate the advanced treasure map once</t>
+  </si>
+  <si>
+    <t>领主之敌</t>
+  </si>
+  <si>
+    <t>Lord's Enemy</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>击败30个领主级怪物</t>
+  </si>
+  <si>
+    <t>Defeat 30 lord-level monsters</t>
+  </si>
+  <si>
+    <t>五连击破</t>
+  </si>
+  <si>
+    <t>Five Consecutive Kills</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>在野外地区击败5名玩家</t>
+  </si>
+  <si>
+    <t>Defeat 5 players in the wild area</t>
+  </si>
+  <si>
+    <t>技能替换</t>
+  </si>
+  <si>
+    <t>Skill Replacement</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>附魔初成</t>
+  </si>
+  <si>
+    <t>Enchantment Completion</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>幸运洗练</t>
+  </si>
+  <si>
+    <t>Lucky Refinement</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>洗练出1个带有隐藏技能的装备</t>
+  </si>
+  <si>
+    <t>Craft a piece of equipment with hidden skills</t>
+  </si>
+  <si>
+    <t>宠物融合</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>宠物合成10次</t>
+  </si>
+  <si>
+    <t>Synthesize pets 10 times</t>
+  </si>
+  <si>
+    <t>献上神宠</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>挑战有1次深渊类型的副本</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>打造1件传承的装备</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑战有3次深渊类型的副本</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗炼装备10次</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3只全新的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>封印之塔挑战10次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成1只战力达到9000点的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启10次普通藏宝图</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物使用技能书替换自身技能3次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用附魔道具给自己的装备附魔5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物合成5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上交一只4技能以上的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上交一只5技能以上的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>击败1000只怪物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 1000 monsters.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refine equipment 10 times each</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Challenge a dungeon of abyssal type three times.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refine equipment 30 times each</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get 3 brand new pets</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synthesize pets 5 times</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Challenge the Seal Tower 10 times</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submit a pet with more than 4 skills.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Submit a pet with more than 5 skills.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synthesize a pet with a combat power of 7000 points.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Open 10 ordinary treasure maps.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet uses skill books to replace its own skills 3 times.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use enchanting items to enchant your equipment 5 times</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forge an inherited equipment.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10000132;2</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010039;1</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010083;5</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010041;2</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010086;1</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010083;2</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10000132;5</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010042;2</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010034;1</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010041;5</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010083;5</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010083;10</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10000158;1</t>
+  </si>
+  <si>
+    <t>10000184;10@1;100000@10010039;1</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010028;1</t>
+  </si>
+  <si>
+    <t>10000184;20@1;150000@10010028;2</t>
+  </si>
+  <si>
+    <t>1;100000@31;20@10000159;5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;150000@31;30@10000159;5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;200000@31;40@10000159;10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在野外击败10个敌方玩家，奖励5个经验盒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Defeat 10 enemy players in the wild and receive 5 experience boxes as a reward</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用普通藏宝图10次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Use the ordinary treasure map 10 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用高级藏宝图3次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Use the advanced treasure map 3 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>击败10个地狱级领主怪物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Defeat 10 hell-level lord monsters</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>封印之塔挑战10次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Completed the Tower of Sealing 10 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3只全新的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Gained 3 brand new pets</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用附魔道具给自己的装备附魔5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Use enchanting items to enchant one's equipment 5 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用鉴定道具给自己的装备鉴定5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Use the identification item to appraise the equipment 5 times.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物合成5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Pet Synthesis 5 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成1只战力达到6000点的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Combine with 1 pet with a combat power of 6000 points</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物使用宠之晶洗炼达到5次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>The pet has used the Pet Crystal to refine 5 times.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物天梯战斗获胜次数达到10次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>The pet has won 10 times in the ladder battle</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备洗炼达到10次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Equip refinement reaches 10 times.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活技能制造出20个道具</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Life skill: Produces 20 items</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功孵化5次宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Successfully hatched 5 pets</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑战5次深渊类型的副本</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Challenge 5 abyss-type dungeons</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物合成10次,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Pet synthesis 10 times,</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成1只战力达到7000点的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Synthesize a pet with a combat power of 7000 points.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用90点及以上的鉴定符去鉴定2次装备</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Use 90 or more runes to identify 2 pieces of equipment</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备洗炼达到20次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Equipment Refining reaches 20 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上交一个橙色的装备</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Submit an orange piece of equipment</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>占领1个黄金矿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Capture 1 gold mine</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备洗炼达到30次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Equip refinement completed 30 times</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用珍贵的宠物蛋成功孵化两次宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Successfully hatch two pets using a precious pet egg.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成一只战力达到8000点的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Synthesize a pet with a combat power of 8000 points</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>试炼之地输出进入排行前10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>The trial land's output has entered the top 10 of the ranking.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物天梯进入排行榜前10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>The pet ladder has entered the top 10 of the ranking list.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>战力排行榜进入前10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Enter the top 10 of the battle ranking</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>占领1个核心矿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Capture 1 core mine</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上交一只6技能以上的宠物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Submit a pet with more than 6 skills.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗练出1个带有隐藏技能的装备</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Craft a piece of equipment with hidden skills</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上交一个50级以上鉴定3属性的装备一件</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Submit a piece of equipment with a level above 5 and 3 attributes</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>十连击破</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>探险家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>探险专家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>领主试炼</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>封印挑战</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物获取</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备附魔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴定家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物融合</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物小成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物洗礼</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物之战</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备洗练</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活制造</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物孵化</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>深渊挑战</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物初成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴定者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大师洗练</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>献上宝物</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抢占矿场</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>珍宠孵化</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物达成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>实力代表</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物挑战</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>战力挑战</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>献上神宠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸运者</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1576,7 +1999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1736,13 +2159,6 @@
       <sz val="9"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="52">
@@ -11728,7 +12144,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -11791,36 +12207,25 @@
     <xf numFmtId="49" fontId="1" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="51" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="51" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="51" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="51" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3226">
@@ -15415,7 +15820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:U87"/>
+  <dimension ref="C2:T105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="6" width="12.625" customWidth="1"/>
@@ -15434,11 +15839,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:20" x14ac:dyDescent="0.15">
-      <c r="E2" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="T2" s="32" t="s">
-        <v>388</v>
+      <c r="E2" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15505,7 +15910,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>17</v>
@@ -15550,7 +15955,7 @@
         <v>30</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>312</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15594,13 +15999,13 @@
         <v>32</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="S5" s="17" t="s">
         <v>32</v>
@@ -15617,7 +16022,7 @@
         <v>34</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -15643,7 +16048,7 @@
       <c r="M6" s="12">
         <v>5</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="12">
         <v>3000</v>
       </c>
       <c r="O6" s="13" t="s">
@@ -15662,7 +16067,7 @@
         <v>36</v>
       </c>
       <c r="T6" s="19" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15673,7 +16078,7 @@
         <v>37</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -15699,7 +16104,7 @@
       <c r="M7" s="12">
         <v>10</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="12">
         <v>4500</v>
       </c>
       <c r="O7" s="13" t="s">
@@ -15718,7 +16123,7 @@
         <v>38</v>
       </c>
       <c r="T7" s="19" t="s">
-        <v>314</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15729,7 +16134,7 @@
         <v>39</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
@@ -15755,7 +16160,7 @@
       <c r="M8" s="12">
         <v>10</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="12">
         <v>15000</v>
       </c>
       <c r="O8" s="13" t="s">
@@ -15774,7 +16179,7 @@
         <v>40</v>
       </c>
       <c r="T8" s="19" t="s">
-        <v>315</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15785,7 +16190,7 @@
         <v>41</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
@@ -15811,7 +16216,7 @@
       <c r="M9" s="12">
         <v>10</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="12">
         <v>15000</v>
       </c>
       <c r="O9" s="13" t="s">
@@ -15830,7 +16235,7 @@
         <v>43</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>316</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15841,7 +16246,7 @@
         <v>44</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="F10" s="8">
         <v>1</v>
@@ -15867,7 +16272,7 @@
       <c r="M10" s="12">
         <v>10</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="12">
         <v>6000</v>
       </c>
       <c r="O10" s="13" t="s">
@@ -15886,7 +16291,7 @@
         <v>45</v>
       </c>
       <c r="T10" s="19" t="s">
-        <v>317</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15897,7 +16302,7 @@
         <v>46</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="F11" s="8">
         <v>1</v>
@@ -15923,7 +16328,7 @@
       <c r="M11" s="12">
         <v>10</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="12">
         <v>6000</v>
       </c>
       <c r="O11" s="13" t="s">
@@ -15942,7 +16347,7 @@
         <v>47</v>
       </c>
       <c r="T11" s="19" t="s">
-        <v>318</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15953,7 +16358,7 @@
         <v>48</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="F12" s="8">
         <v>1</v>
@@ -15979,7 +16384,7 @@
       <c r="M12" s="12">
         <v>10</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="12">
         <v>6000</v>
       </c>
       <c r="O12" s="13" t="s">
@@ -15998,7 +16403,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="19" t="s">
-        <v>319</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16009,7 +16414,7 @@
         <v>51</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="F13" s="8">
         <v>1</v>
@@ -16035,7 +16440,7 @@
       <c r="M13" s="12">
         <v>10</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="12">
         <v>6000</v>
       </c>
       <c r="O13" s="13" t="s">
@@ -16054,7 +16459,7 @@
         <v>52</v>
       </c>
       <c r="T13" s="19" t="s">
-        <v>320</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16065,7 +16470,7 @@
         <v>53</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="F14" s="8">
         <v>1</v>
@@ -16091,7 +16496,7 @@
       <c r="M14" s="12">
         <v>10</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="12">
         <v>6000</v>
       </c>
       <c r="O14" s="13" t="s">
@@ -16110,7 +16515,7 @@
         <v>55</v>
       </c>
       <c r="T14" s="19" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16121,7 +16526,7 @@
         <v>56</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="F15" s="8">
         <v>1</v>
@@ -16147,7 +16552,7 @@
       <c r="M15" s="12">
         <v>10</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="12">
         <v>6000</v>
       </c>
       <c r="O15" s="13" t="s">
@@ -16166,7 +16571,7 @@
         <v>57</v>
       </c>
       <c r="T15" s="19" t="s">
-        <v>322</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16177,7 +16582,7 @@
         <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="F16" s="8">
         <v>1</v>
@@ -16203,7 +16608,7 @@
       <c r="M16" s="12">
         <v>10</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="12">
         <v>6000</v>
       </c>
       <c r="O16" s="13" t="s">
@@ -16222,7 +16627,7 @@
         <v>60</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16233,7 +16638,7 @@
         <v>61</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
@@ -16259,7 +16664,7 @@
       <c r="M17" s="12">
         <v>10</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="12">
         <v>30000</v>
       </c>
       <c r="O17" s="13" t="s">
@@ -16278,7 +16683,7 @@
         <v>63</v>
       </c>
       <c r="T17" s="19" t="s">
-        <v>324</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16289,7 +16694,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -16315,7 +16720,7 @@
       <c r="M18" s="12">
         <v>10</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="12">
         <v>30000</v>
       </c>
       <c r="O18" s="13" t="s">
@@ -16334,7 +16739,7 @@
         <v>64</v>
       </c>
       <c r="T18" s="19" t="s">
-        <v>325</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16345,7 +16750,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -16371,7 +16776,7 @@
       <c r="M19" s="12">
         <v>10</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="12">
         <v>15000</v>
       </c>
       <c r="O19" s="13" t="s">
@@ -16390,7 +16795,7 @@
         <v>66</v>
       </c>
       <c r="T19" s="19" t="s">
-        <v>326</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16401,7 +16806,7 @@
         <v>67</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="F20" s="8">
         <v>1</v>
@@ -16427,7 +16832,7 @@
       <c r="M20" s="12">
         <v>10</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="12">
         <v>15000</v>
       </c>
       <c r="O20" s="13" t="s">
@@ -16446,7 +16851,7 @@
         <v>68</v>
       </c>
       <c r="T20" s="19" t="s">
-        <v>327</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16457,7 +16862,7 @@
         <v>69</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="F21" s="8">
         <v>1</v>
@@ -16483,7 +16888,7 @@
       <c r="M21" s="12">
         <v>10</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="12">
         <v>15000</v>
       </c>
       <c r="O21" s="13" t="s">
@@ -16502,7 +16907,7 @@
         <v>70</v>
       </c>
       <c r="T21" s="19" t="s">
-        <v>328</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16513,7 +16918,7 @@
         <v>71</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="F22" s="8">
         <v>1</v>
@@ -16539,7 +16944,7 @@
       <c r="M22" s="12">
         <v>5</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="12">
         <v>15000</v>
       </c>
       <c r="O22" s="13" t="s">
@@ -16558,7 +16963,7 @@
         <v>72</v>
       </c>
       <c r="T22" s="19" t="s">
-        <v>329</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16569,7 +16974,7 @@
         <v>73</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="F23" s="8">
         <v>1</v>
@@ -16595,7 +17000,7 @@
       <c r="M23" s="12">
         <v>5</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="12">
         <v>15000</v>
       </c>
       <c r="O23" s="13" t="s">
@@ -16614,7 +17019,7 @@
         <v>74</v>
       </c>
       <c r="T23" s="19" t="s">
-        <v>330</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16625,7 +17030,7 @@
         <v>75</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="F24" s="8">
         <v>2</v>
@@ -16651,7 +17056,7 @@
       <c r="M24" s="12">
         <v>0</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="12">
         <v>30000</v>
       </c>
       <c r="O24" s="13" t="s">
@@ -16670,7 +17075,7 @@
         <v>77</v>
       </c>
       <c r="T24" s="19" t="s">
-        <v>331</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16681,7 +17086,7 @@
         <v>78</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="F25" s="8">
         <v>2</v>
@@ -16707,7 +17112,7 @@
       <c r="M25" s="12">
         <v>0</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="12">
         <v>30000</v>
       </c>
       <c r="O25" s="13" t="s">
@@ -16726,7 +17131,7 @@
         <v>80</v>
       </c>
       <c r="T25" s="19" t="s">
-        <v>332</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16737,7 +17142,7 @@
         <v>81</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>265</v>
+        <v>201</v>
       </c>
       <c r="F26" s="8">
         <v>2</v>
@@ -16763,7 +17168,7 @@
       <c r="M26" s="12">
         <v>0</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="12">
         <v>30000</v>
       </c>
       <c r="O26" s="13" t="s">
@@ -16782,7 +17187,7 @@
         <v>82</v>
       </c>
       <c r="T26" s="19" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16793,7 +17198,7 @@
         <v>83</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="F27" s="8">
         <v>2</v>
@@ -16819,7 +17224,7 @@
       <c r="M27" s="12">
         <v>0</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="12">
         <v>30000</v>
       </c>
       <c r="O27" s="13" t="s">
@@ -16838,7 +17243,7 @@
         <v>84</v>
       </c>
       <c r="T27" s="19" t="s">
-        <v>334</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16849,7 +17254,7 @@
         <v>85</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="F28" s="8">
         <v>2</v>
@@ -16875,7 +17280,7 @@
       <c r="M28" s="12">
         <v>0</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="12">
         <v>30000</v>
       </c>
       <c r="O28" s="13" t="s">
@@ -16894,7 +17299,7 @@
         <v>86</v>
       </c>
       <c r="T28" s="19" t="s">
-        <v>335</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16905,7 +17310,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="F29" s="8">
         <v>2</v>
@@ -16931,7 +17336,7 @@
       <c r="M29" s="12">
         <v>0</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" s="12">
         <v>30000</v>
       </c>
       <c r="O29" s="13" t="s">
@@ -16950,7 +17355,7 @@
         <v>88</v>
       </c>
       <c r="T29" s="19" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -16961,7 +17366,7 @@
         <v>89</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="F30" s="8">
         <v>2</v>
@@ -16987,7 +17392,7 @@
       <c r="M30" s="12">
         <v>0</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="12">
         <v>30000</v>
       </c>
       <c r="O30" s="13" t="s">
@@ -17006,7 +17411,7 @@
         <v>90</v>
       </c>
       <c r="T30" s="19" t="s">
-        <v>337</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17017,7 +17422,7 @@
         <v>91</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="F31" s="8">
         <v>2</v>
@@ -17043,7 +17448,7 @@
       <c r="M31" s="12">
         <v>0</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="12">
         <v>30000</v>
       </c>
       <c r="O31" s="13" t="s">
@@ -17062,7 +17467,7 @@
         <v>93</v>
       </c>
       <c r="T31" s="19" t="s">
-        <v>338</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17073,7 +17478,7 @@
         <v>94</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>270</v>
+        <v>206</v>
       </c>
       <c r="F32" s="8">
         <v>2</v>
@@ -17099,7 +17504,7 @@
       <c r="M32" s="12">
         <v>0</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" s="12">
         <v>30000</v>
       </c>
       <c r="O32" s="13" t="s">
@@ -17118,7 +17523,7 @@
         <v>95</v>
       </c>
       <c r="T32" s="19" t="s">
-        <v>339</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17129,7 +17534,7 @@
         <v>96</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="F33" s="8">
         <v>2</v>
@@ -17155,7 +17560,7 @@
       <c r="M33" s="12">
         <v>0</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="12">
         <v>30000</v>
       </c>
       <c r="O33" s="13" t="s">
@@ -17174,7 +17579,7 @@
         <v>97</v>
       </c>
       <c r="T33" s="19" t="s">
-        <v>340</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="3:20" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -17185,7 +17590,7 @@
         <v>98</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>272</v>
+        <v>208</v>
       </c>
       <c r="F34" s="8">
         <v>2</v>
@@ -17211,7 +17616,7 @@
       <c r="M34" s="12">
         <v>0</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34" s="12">
         <v>50000</v>
       </c>
       <c r="O34" s="13" t="s">
@@ -17230,7 +17635,7 @@
         <v>99</v>
       </c>
       <c r="T34" s="19" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17241,7 +17646,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>273</v>
+        <v>209</v>
       </c>
       <c r="F35" s="8">
         <v>3</v>
@@ -17267,7 +17672,7 @@
       <c r="M35" s="12">
         <v>0</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="12">
         <v>50000</v>
       </c>
       <c r="O35" s="13" t="s">
@@ -17286,7 +17691,7 @@
         <v>102</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17297,7 +17702,7 @@
         <v>103</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="F36" s="8">
         <v>3</v>
@@ -17323,7 +17728,7 @@
       <c r="M36" s="12">
         <v>0</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36" s="12">
         <v>50000</v>
       </c>
       <c r="O36" s="13" t="s">
@@ -17342,7 +17747,7 @@
         <v>104</v>
       </c>
       <c r="T36" s="19" t="s">
-        <v>343</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17353,7 +17758,7 @@
         <v>105</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="F37" s="8">
         <v>3</v>
@@ -17379,7 +17784,7 @@
       <c r="M37" s="12">
         <v>0</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="12">
         <v>100000</v>
       </c>
       <c r="O37" s="13" t="s">
@@ -17398,7 +17803,7 @@
         <v>106</v>
       </c>
       <c r="T37" s="19" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17409,7 +17814,7 @@
         <v>107</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="F38" s="8">
         <v>3</v>
@@ -17435,7 +17840,7 @@
       <c r="M38" s="12">
         <v>0</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38" s="12">
         <v>100000</v>
       </c>
       <c r="O38" s="13" t="s">
@@ -17454,7 +17859,7 @@
         <v>108</v>
       </c>
       <c r="T38" s="19" t="s">
-        <v>345</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17465,7 +17870,7 @@
         <v>109</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>277</v>
+        <v>213</v>
       </c>
       <c r="F39" s="8">
         <v>4</v>
@@ -17491,7 +17896,7 @@
       <c r="M39" s="12">
         <v>0</v>
       </c>
-      <c r="N39" s="2">
+      <c r="N39" s="12">
         <v>30000</v>
       </c>
       <c r="O39" s="13" t="s">
@@ -17510,7 +17915,7 @@
         <v>111</v>
       </c>
       <c r="T39" s="19" t="s">
-        <v>346</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17521,7 +17926,7 @@
         <v>112</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="F40" s="8">
         <v>4</v>
@@ -17547,7 +17952,7 @@
       <c r="M40" s="12">
         <v>0</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N40" s="12">
         <v>50000</v>
       </c>
       <c r="O40" s="13" t="s">
@@ -17566,7 +17971,7 @@
         <v>113</v>
       </c>
       <c r="T40" s="19" t="s">
-        <v>347</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17577,7 +17982,7 @@
         <v>114</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="F41" s="8">
         <v>4</v>
@@ -17603,7 +18008,7 @@
       <c r="M41" s="12">
         <v>0</v>
       </c>
-      <c r="N41" s="2">
+      <c r="N41" s="12">
         <v>50000</v>
       </c>
       <c r="O41" s="13" t="s">
@@ -17622,7 +18027,7 @@
         <v>116</v>
       </c>
       <c r="T41" s="19" t="s">
-        <v>348</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17633,7 +18038,7 @@
         <v>117</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="F42" s="8">
         <v>4</v>
@@ -17659,7 +18064,7 @@
       <c r="M42" s="12">
         <v>0</v>
       </c>
-      <c r="N42" s="2">
+      <c r="N42" s="12">
         <v>100000</v>
       </c>
       <c r="O42" s="13" t="s">
@@ -17678,7 +18083,7 @@
         <v>119</v>
       </c>
       <c r="T42" s="19" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17689,7 +18094,7 @@
         <v>120</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>281</v>
+        <v>217</v>
       </c>
       <c r="F43" s="8">
         <v>4</v>
@@ -17715,7 +18120,7 @@
       <c r="M43" s="12">
         <v>0</v>
       </c>
-      <c r="N43" s="2">
+      <c r="N43" s="12">
         <v>100000</v>
       </c>
       <c r="O43" s="13" t="s">
@@ -17734,7 +18139,7 @@
         <v>122</v>
       </c>
       <c r="T43" s="19" t="s">
-        <v>350</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17745,7 +18150,7 @@
         <v>123</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="F44" s="8">
         <v>5</v>
@@ -17771,7 +18176,7 @@
       <c r="M44" s="12">
         <v>0</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="12">
         <v>0</v>
       </c>
       <c r="O44" s="13" t="s">
@@ -17790,7 +18195,7 @@
         <v>130</v>
       </c>
       <c r="T44" s="19" t="s">
-        <v>351</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17801,7 +18206,7 @@
         <v>124</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>283</v>
+        <v>219</v>
       </c>
       <c r="F45" s="8">
         <v>5</v>
@@ -17827,7 +18232,7 @@
       <c r="M45" s="12">
         <v>0</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="12">
         <v>0</v>
       </c>
       <c r="O45" s="13" t="s">
@@ -17846,7 +18251,7 @@
         <v>131</v>
       </c>
       <c r="T45" s="19" t="s">
-        <v>352</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17857,7 +18262,7 @@
         <v>125</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="F46" s="8">
         <v>5</v>
@@ -17883,7 +18288,7 @@
       <c r="M46" s="12">
         <v>0</v>
       </c>
-      <c r="N46" s="2">
+      <c r="N46" s="12">
         <v>0</v>
       </c>
       <c r="O46" s="13" t="s">
@@ -17902,7 +18307,7 @@
         <v>132</v>
       </c>
       <c r="T46" s="19" t="s">
-        <v>353</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17913,7 +18318,7 @@
         <v>125</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="F47" s="8">
         <v>5</v>
@@ -17939,7 +18344,7 @@
       <c r="M47" s="12">
         <v>0</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="12">
         <v>0</v>
       </c>
       <c r="O47" s="13" t="s">
@@ -17958,7 +18363,7 @@
         <v>133</v>
       </c>
       <c r="T47" s="19" t="s">
-        <v>354</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -17969,7 +18374,7 @@
         <v>126</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="F48" s="8">
         <v>5</v>
@@ -17995,7 +18400,7 @@
       <c r="M48" s="12">
         <v>0</v>
       </c>
-      <c r="N48" s="2">
+      <c r="N48" s="12">
         <v>0</v>
       </c>
       <c r="O48" s="13" t="s">
@@ -18014,18 +18419,18 @@
         <v>134</v>
       </c>
       <c r="T48" s="19" t="s">
-        <v>355</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="49" spans="3:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="8">
         <v>600101</v>
       </c>
-      <c r="D49" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>286</v>
+      <c r="D49" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>222</v>
       </c>
       <c r="F49" s="8">
         <v>6</v>
@@ -18051,38 +18456,37 @@
       <c r="M49" s="12">
         <v>0</v>
       </c>
-      <c r="N49" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O49" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P49" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q49" s="21" t="s">
+      <c r="N49" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P49" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q49" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="R49" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S49" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="T49" s="26" t="s">
-        <v>356</v>
-      </c>
-      <c r="U49" s="28"/>
+      <c r="R49" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S49" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="T49" s="19" t="s">
+        <v>424</v>
+      </c>
     </row>
-    <row r="50" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="8">
         <v>600102</v>
       </c>
-      <c r="D50" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>287</v>
+      <c r="D50" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>223</v>
       </c>
       <c r="F50" s="8">
         <v>6</v>
@@ -18108,37 +18512,37 @@
       <c r="M50" s="12">
         <v>0</v>
       </c>
-      <c r="N50" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O50" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P50" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q50" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R50" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S50" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="T50" s="26" t="s">
-        <v>357</v>
+      <c r="N50" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q50" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R50" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S50" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="T50" s="19" t="s">
+        <v>426</v>
       </c>
     </row>
-    <row r="51" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="8">
         <v>600103</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="29" t="s">
-        <v>288</v>
+      <c r="D51" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>224</v>
       </c>
       <c r="F51" s="8">
         <v>6</v>
@@ -18164,37 +18568,37 @@
       <c r="M51" s="12">
         <v>0</v>
       </c>
-      <c r="N51" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O51" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P51" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q51" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R51" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="S51" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="T51" s="26" t="s">
-        <v>358</v>
+      <c r="N51" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q51" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R51" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="S51" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="T51" s="19" t="s">
+        <v>428</v>
       </c>
     </row>
-    <row r="52" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="8">
         <v>600104</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>248</v>
+      <c r="D52" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>184</v>
       </c>
       <c r="F52" s="8">
         <v>6</v>
@@ -18220,37 +18624,37 @@
       <c r="M52" s="12">
         <v>0</v>
       </c>
-      <c r="N52" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O52" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P52" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q52" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R52" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S52" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="T52" s="26" t="s">
-        <v>359</v>
+      <c r="N52" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O52" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P52" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q52" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R52" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S52" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="T52" s="19" t="s">
+        <v>430</v>
       </c>
     </row>
-    <row r="53" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="8">
         <v>600105</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" s="29" t="s">
-        <v>289</v>
+      <c r="D53" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>225</v>
       </c>
       <c r="F53" s="8">
         <v>6</v>
@@ -18276,37 +18680,37 @@
       <c r="M53" s="12">
         <v>0</v>
       </c>
-      <c r="N53" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O53" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P53" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q53" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R53" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S53" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="T53" s="26" t="s">
-        <v>360</v>
+      <c r="N53" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O53" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q53" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R53" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S53" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="T53" s="19" t="s">
+        <v>432</v>
       </c>
     </row>
-    <row r="54" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="8">
         <v>600106</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E54" s="29" t="s">
-        <v>290</v>
+      <c r="D54" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>226</v>
       </c>
       <c r="F54" s="8">
         <v>6</v>
@@ -18332,37 +18736,37 @@
       <c r="M54" s="12">
         <v>0</v>
       </c>
-      <c r="N54" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O54" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P54" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q54" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R54" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="S54" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="T54" s="26" t="s">
-        <v>361</v>
+      <c r="N54" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O54" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q54" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R54" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="S54" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="T54" s="19" t="s">
+        <v>434</v>
       </c>
     </row>
-    <row r="55" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="8">
         <v>600107</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E55" s="29" t="s">
-        <v>291</v>
+      <c r="D55" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>227</v>
       </c>
       <c r="F55" s="8">
         <v>6</v>
@@ -18388,37 +18792,37 @@
       <c r="M55" s="12">
         <v>0</v>
       </c>
-      <c r="N55" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O55" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P55" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q55" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="R55" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S55" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="T55" s="26" t="s">
-        <v>362</v>
+      <c r="N55" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O55" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q55" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="R55" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S55" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="T55" s="19" t="s">
+        <v>436</v>
       </c>
     </row>
-    <row r="56" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="8">
         <v>600108</v>
       </c>
-      <c r="D56" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>292</v>
+      <c r="D56" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="F56" s="8">
         <v>6</v>
@@ -18444,37 +18848,37 @@
       <c r="M56" s="12">
         <v>0</v>
       </c>
-      <c r="N56" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O56" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P56" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q56" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="R56" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S56" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="T56" s="26" t="s">
-        <v>363</v>
+      <c r="N56" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O56" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P56" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q56" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="R56" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S56" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="T56" s="19" t="s">
+        <v>438</v>
       </c>
     </row>
-    <row r="57" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="8">
         <v>600109</v>
       </c>
-      <c r="D57" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>293</v>
+      <c r="D57" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>229</v>
       </c>
       <c r="F57" s="8">
         <v>6</v>
@@ -18500,37 +18904,37 @@
       <c r="M57" s="12">
         <v>0</v>
       </c>
-      <c r="N57" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O57" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P57" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q57" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R57" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S57" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="T57" s="26" t="s">
-        <v>364</v>
+      <c r="N57" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O57" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P57" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q57" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R57" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S57" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="T57" s="19" t="s">
+        <v>440</v>
       </c>
     </row>
-    <row r="58" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="8">
         <v>600110</v>
       </c>
-      <c r="D58" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>294</v>
+      <c r="D58" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="F58" s="8">
         <v>6</v>
@@ -18556,37 +18960,37 @@
       <c r="M58" s="12">
         <v>0</v>
       </c>
-      <c r="N58" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O58" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P58" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q58" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="R58" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S58" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="T58" s="26" t="s">
-        <v>365</v>
+      <c r="N58" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O58" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P58" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q58" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="R58" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S58" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="T58" s="19" t="s">
+        <v>442</v>
       </c>
     </row>
-    <row r="59" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="8">
         <v>600111</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E59" s="29" t="s">
-        <v>295</v>
+      <c r="D59" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="F59" s="8">
         <v>6</v>
@@ -18612,37 +19016,37 @@
       <c r="M59" s="12">
         <v>0</v>
       </c>
-      <c r="N59" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O59" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P59" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q59" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R59" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S59" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="T59" s="26" t="s">
-        <v>366</v>
+      <c r="N59" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O59" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P59" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q59" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R59" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S59" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="T59" s="19" t="s">
+        <v>444</v>
       </c>
     </row>
-    <row r="60" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="8">
         <v>600112</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E60" s="29" t="s">
-        <v>296</v>
+      <c r="D60" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="F60" s="8">
         <v>6</v>
@@ -18668,37 +19072,37 @@
       <c r="M60" s="12">
         <v>0</v>
       </c>
-      <c r="N60" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O60" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P60" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q60" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R60" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S60" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="T60" s="26" t="s">
-        <v>367</v>
+      <c r="N60" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O60" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P60" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q60" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R60" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S60" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="T60" s="19" t="s">
+        <v>446</v>
       </c>
     </row>
-    <row r="61" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="8">
         <v>600113</v>
       </c>
-      <c r="D61" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E61" s="29" t="s">
-        <v>256</v>
+      <c r="D61" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>192</v>
       </c>
       <c r="F61" s="8">
         <v>6</v>
@@ -18724,37 +19128,37 @@
       <c r="M61" s="12">
         <v>0</v>
       </c>
-      <c r="N61" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O61" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P61" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q61" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R61" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S61" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="T61" s="26" t="s">
-        <v>368</v>
+      <c r="N61" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O61" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P61" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q61" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R61" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S61" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="T61" s="19" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="62" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="8">
         <v>600114</v>
       </c>
-      <c r="D62" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E62" s="29" t="s">
-        <v>297</v>
+      <c r="D62" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>233</v>
       </c>
       <c r="F62" s="8">
         <v>6</v>
@@ -18780,37 +19184,37 @@
       <c r="M62" s="12">
         <v>0</v>
       </c>
-      <c r="N62" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O62" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P62" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q62" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R62" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S62" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="T62" s="26" t="s">
-        <v>369</v>
+      <c r="N62" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O62" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q62" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R62" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S62" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="T62" s="19" t="s">
+        <v>450</v>
       </c>
     </row>
-    <row r="63" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="8">
         <v>600115</v>
       </c>
-      <c r="D63" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="E63" s="29" t="s">
-        <v>298</v>
+      <c r="D63" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>234</v>
       </c>
       <c r="F63" s="8">
         <v>6</v>
@@ -18836,37 +19240,37 @@
       <c r="M63" s="12">
         <v>0</v>
       </c>
-      <c r="N63" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="O63" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="P63" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q63" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R63" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S63" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="T63" s="26" t="s">
-        <v>370</v>
+      <c r="N63" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O63" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="P63" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q63" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R63" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S63" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="T63" s="19" t="s">
+        <v>452</v>
       </c>
     </row>
-    <row r="64" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="8">
         <v>600201</v>
       </c>
-      <c r="D64" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E64" s="29" t="s">
-        <v>299</v>
+      <c r="D64" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>235</v>
       </c>
       <c r="F64" s="8">
         <v>6</v>
@@ -18892,38 +19296,37 @@
       <c r="M64" s="12">
         <v>0</v>
       </c>
-      <c r="N64" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O64" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P64" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q64" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R64" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="S64" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="T64" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="U64" s="28"/>
+      <c r="N64" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O64" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P64" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q64" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R64" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S64" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="T64" s="19" t="s">
+        <v>454</v>
+      </c>
     </row>
-    <row r="65" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="8">
         <v>600202</v>
       </c>
-      <c r="D65" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E65" s="29" t="s">
-        <v>293</v>
+      <c r="D65" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>229</v>
       </c>
       <c r="F65" s="8">
         <v>6</v>
@@ -18949,37 +19352,37 @@
       <c r="M65" s="12">
         <v>0</v>
       </c>
-      <c r="N65" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O65" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P65" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q65" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R65" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="S65" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="T65" s="26" t="s">
-        <v>372</v>
+      <c r="N65" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O65" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q65" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R65" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="S65" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="T65" s="19" t="s">
+        <v>456</v>
       </c>
     </row>
-    <row r="66" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="8">
         <v>600203</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E66" s="29" t="s">
-        <v>300</v>
+      <c r="D66" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>236</v>
       </c>
       <c r="F66" s="8">
         <v>6</v>
@@ -19005,37 +19408,37 @@
       <c r="M66" s="12">
         <v>0</v>
       </c>
-      <c r="N66" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O66" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P66" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q66" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="R66" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S66" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="T66" s="26" t="s">
-        <v>373</v>
+      <c r="N66" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O66" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P66" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q66" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="R66" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S66" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="T66" s="19" t="s">
+        <v>458</v>
       </c>
     </row>
-    <row r="67" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="8">
         <v>600204</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E67" s="29" t="s">
-        <v>292</v>
+      <c r="D67" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="F67" s="8">
         <v>6</v>
@@ -19061,37 +19464,37 @@
       <c r="M67" s="12">
         <v>0</v>
       </c>
-      <c r="N67" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O67" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P67" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q67" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="R67" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="S67" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="T67" s="26" t="s">
-        <v>374</v>
+      <c r="N67" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O67" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P67" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q67" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="R67" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="S67" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="T67" s="19" t="s">
+        <v>460</v>
       </c>
     </row>
-    <row r="68" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="8">
         <v>600205</v>
       </c>
-      <c r="D68" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E68" s="29" t="s">
-        <v>301</v>
+      <c r="D68" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>237</v>
       </c>
       <c r="F68" s="8">
         <v>6</v>
@@ -19117,37 +19520,37 @@
       <c r="M68" s="12">
         <v>0</v>
       </c>
-      <c r="N68" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O68" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P68" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q68" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R68" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="S68" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="T68" s="26" t="s">
-        <v>375</v>
+      <c r="N68" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O68" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P68" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q68" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R68" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="S68" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="T68" s="19" t="s">
+        <v>462</v>
       </c>
     </row>
-    <row r="69" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="8">
         <v>600206</v>
       </c>
-      <c r="D69" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="30" t="s">
-        <v>302</v>
+      <c r="D69" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>238</v>
       </c>
       <c r="F69" s="8">
         <v>6</v>
@@ -19173,37 +19576,37 @@
       <c r="M69" s="12">
         <v>0</v>
       </c>
-      <c r="N69" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="O69" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P69" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q69" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="R69" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="S69" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="T69" s="27" t="s">
-        <v>376</v>
+      <c r="N69" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O69" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P69" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q69" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="R69" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="S69" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="T69" s="19" t="s">
+        <v>464</v>
       </c>
     </row>
-    <row r="70" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="8">
         <v>600207</v>
       </c>
-      <c r="D70" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>303</v>
+      <c r="D70" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>239</v>
       </c>
       <c r="F70" s="8">
         <v>6</v>
@@ -19229,37 +19632,37 @@
       <c r="M70" s="12">
         <v>0</v>
       </c>
-      <c r="N70" s="23" t="s">
+      <c r="N70" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O70" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P70" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q70" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="O70" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P70" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q70" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="R70" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S70" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="T70" s="26" t="s">
-        <v>377</v>
+      <c r="R70" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S70" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="T70" s="19" t="s">
+        <v>466</v>
       </c>
     </row>
-    <row r="71" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="8">
         <v>600208</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" s="29" t="s">
-        <v>256</v>
+      <c r="D71" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>192</v>
       </c>
       <c r="F71" s="8">
         <v>6</v>
@@ -19285,37 +19688,37 @@
       <c r="M71" s="12">
         <v>0</v>
       </c>
-      <c r="N71" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O71" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P71" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q71" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R71" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="S71" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="T71" s="26" t="s">
-        <v>378</v>
+      <c r="N71" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O71" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P71" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q71" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R71" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="S71" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="T71" s="19" t="s">
+        <v>468</v>
       </c>
     </row>
-    <row r="72" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="8">
         <v>600209</v>
       </c>
-      <c r="D72" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E72" s="29" t="s">
-        <v>304</v>
+      <c r="D72" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>240</v>
       </c>
       <c r="F72" s="8">
         <v>6</v>
@@ -19341,37 +19744,37 @@
       <c r="M72" s="12">
         <v>0</v>
       </c>
-      <c r="N72" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="O72" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="P72" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q72" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="R72" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="S72" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="T72" s="26" t="s">
-        <v>379</v>
+      <c r="N72" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O72" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="P72" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q72" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="R72" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="S72" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="T72" s="19" t="s">
+        <v>470</v>
       </c>
     </row>
-    <row r="73" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="8">
         <v>600301</v>
       </c>
-      <c r="D73" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="29" t="s">
-        <v>305</v>
+      <c r="D73" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>241</v>
       </c>
       <c r="F73" s="8">
         <v>6</v>
@@ -19397,38 +19800,37 @@
       <c r="M73" s="12">
         <v>0</v>
       </c>
-      <c r="N73" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O73" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P73" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q73" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="R73" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S73" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="T73" s="26" t="s">
-        <v>380</v>
-      </c>
-      <c r="U73" s="28"/>
+      <c r="N73" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O73" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P73" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q73" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="R73" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S73" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="T73" s="19" t="s">
+        <v>472</v>
+      </c>
     </row>
-    <row r="74" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="8">
         <v>600302</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" s="29" t="s">
-        <v>306</v>
+      <c r="D74" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>242</v>
       </c>
       <c r="F74" s="8">
         <v>6</v>
@@ -19454,37 +19856,37 @@
       <c r="M74" s="12">
         <v>0</v>
       </c>
-      <c r="N74" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O74" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P74" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q74" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="R74" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S74" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="T74" s="26" t="s">
-        <v>381</v>
+      <c r="N74" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O74" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P74" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q74" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="R74" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S74" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="T74" s="19" t="s">
+        <v>474</v>
       </c>
     </row>
-    <row r="75" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="8">
         <v>600303</v>
       </c>
-      <c r="D75" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E75" s="29" t="s">
-        <v>307</v>
+      <c r="D75" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>243</v>
       </c>
       <c r="F75" s="8">
         <v>6</v>
@@ -19510,37 +19912,37 @@
       <c r="M75" s="12">
         <v>0</v>
       </c>
-      <c r="N75" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O75" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P75" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q75" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="R75" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S75" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="T75" s="26" t="s">
-        <v>382</v>
+      <c r="N75" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O75" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P75" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q75" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="R75" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S75" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="T75" s="19" t="s">
+        <v>476</v>
       </c>
     </row>
-    <row r="76" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="8">
         <v>600304</v>
       </c>
-      <c r="D76" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="29" t="s">
-        <v>308</v>
+      <c r="D76" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="F76" s="8">
         <v>6</v>
@@ -19566,37 +19968,37 @@
       <c r="M76" s="12">
         <v>0</v>
       </c>
-      <c r="N76" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O76" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P76" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q76" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="R76" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S76" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="T76" s="26" t="s">
-        <v>383</v>
+      <c r="N76" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O76" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P76" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q76" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="R76" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S76" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="T76" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
-    <row r="77" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="8">
         <v>600305</v>
       </c>
-      <c r="D77" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>303</v>
+      <c r="D77" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>239</v>
       </c>
       <c r="F77" s="8">
         <v>6</v>
@@ -19622,37 +20024,37 @@
       <c r="M77" s="12">
         <v>0</v>
       </c>
-      <c r="N77" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O77" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P77" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q77" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R77" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S77" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="T77" s="26" t="s">
-        <v>384</v>
+      <c r="N77" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O77" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P77" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q77" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R77" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S77" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="T77" s="19" t="s">
+        <v>480</v>
       </c>
     </row>
-    <row r="78" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="8">
         <v>600306</v>
       </c>
-      <c r="D78" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E78" s="29" t="s">
-        <v>309</v>
+      <c r="D78" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>245</v>
       </c>
       <c r="F78" s="8">
         <v>6</v>
@@ -19678,37 +20080,37 @@
       <c r="M78" s="12">
         <v>0</v>
       </c>
-      <c r="N78" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O78" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P78" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q78" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="R78" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="S78" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="T78" s="26" t="s">
-        <v>385</v>
+      <c r="N78" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O78" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P78" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q78" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="R78" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="S78" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="T78" s="19" t="s">
+        <v>482</v>
       </c>
     </row>
-    <row r="79" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="8">
         <v>600307</v>
       </c>
-      <c r="D79" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E79" s="29" t="s">
-        <v>310</v>
+      <c r="D79" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="F79" s="8">
         <v>6</v>
@@ -19734,37 +20136,37 @@
       <c r="M79" s="12">
         <v>0</v>
       </c>
-      <c r="N79" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O79" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P79" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q79" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="R79" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S79" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="T79" s="26" t="s">
-        <v>386</v>
+      <c r="N79" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O79" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P79" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q79" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="R79" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S79" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="T79" s="19" t="s">
+        <v>484</v>
       </c>
     </row>
-    <row r="80" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="8">
         <v>600308</v>
       </c>
-      <c r="D80" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E80" s="29" t="s">
-        <v>302</v>
+      <c r="D80" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>238</v>
       </c>
       <c r="F80" s="8">
         <v>6</v>
@@ -19790,418 +20192,1426 @@
       <c r="M80" s="12">
         <v>0</v>
       </c>
-      <c r="N80" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="O80" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P80" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q80" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="R80" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="S80" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="T80" s="26" t="s">
+      <c r="N80" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="O80" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P80" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q80" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="R80" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="S80" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="T80" s="19" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C81" s="28">
+        <v>700101</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" s="28">
+        <v>7</v>
+      </c>
+      <c r="G81" s="28">
+        <v>100001</v>
+      </c>
+      <c r="H81" s="28">
+        <v>1</v>
+      </c>
+      <c r="I81" s="28">
+        <v>700102</v>
+      </c>
+      <c r="J81" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="K81" s="28">
+        <v>0</v>
+      </c>
+      <c r="L81" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M81" s="23">
+        <v>0</v>
+      </c>
+      <c r="N81" s="23">
+        <v>0</v>
+      </c>
+      <c r="O81" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="P81" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q81" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S81" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="T81" s="24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C82" s="28">
+        <v>700102</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="E82" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F82" s="28">
+        <v>7</v>
+      </c>
+      <c r="G82" s="28">
+        <v>100001</v>
+      </c>
+      <c r="H82" s="28">
+        <v>1</v>
+      </c>
+      <c r="I82" s="28">
+        <v>700103</v>
+      </c>
+      <c r="J82" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K82" s="28">
+        <v>0</v>
+      </c>
+      <c r="L82" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M82" s="23">
+        <v>0</v>
+      </c>
+      <c r="N82" s="23">
+        <v>0</v>
+      </c>
+      <c r="O82" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="P82" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q82" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="S82" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="T82" s="24" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="83" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C83" s="28">
+        <v>700103</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="F83" s="28">
+        <v>7</v>
+      </c>
+      <c r="G83" s="28">
+        <v>100002</v>
+      </c>
+      <c r="H83" s="28">
+        <v>1</v>
+      </c>
+      <c r="I83" s="28">
+        <v>0</v>
+      </c>
+      <c r="J83" s="28">
+        <v>1</v>
+      </c>
+      <c r="K83" s="28">
+        <v>0</v>
+      </c>
+      <c r="L83" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M83" s="23">
+        <v>0</v>
+      </c>
+      <c r="N83" s="23">
+        <v>0</v>
+      </c>
+      <c r="O83" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="P83" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q83" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="R83" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S83" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="T83" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C84" s="28">
+        <v>700201</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="E84" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="F84" s="28">
+        <v>7</v>
+      </c>
+      <c r="G84" s="28">
+        <v>100003</v>
+      </c>
+      <c r="H84" s="28">
+        <v>1</v>
+      </c>
+      <c r="I84" s="28">
+        <v>700202</v>
+      </c>
+      <c r="J84" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="K84" s="28">
+        <v>0</v>
+      </c>
+      <c r="L84" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M84" s="23">
+        <v>0</v>
+      </c>
+      <c r="N84" s="23">
+        <v>0</v>
+      </c>
+      <c r="O84" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="P84" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q84" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="S84" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="T84" s="24" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C85" s="28">
+        <v>700202</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="F85" s="28">
+        <v>7</v>
+      </c>
+      <c r="G85" s="28">
+        <v>100003</v>
+      </c>
+      <c r="H85" s="28">
+        <v>1</v>
+      </c>
+      <c r="I85" s="28">
+        <v>700203</v>
+      </c>
+      <c r="J85" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K85" s="28">
+        <v>0</v>
+      </c>
+      <c r="L85" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M85" s="23">
+        <v>0</v>
+      </c>
+      <c r="N85" s="23">
+        <v>0</v>
+      </c>
+      <c r="O85" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="P85" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q85" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="S85" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="T85" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C86" s="28">
+        <v>700203</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F86" s="28">
+        <v>7</v>
+      </c>
+      <c r="G86" s="29">
+        <v>100004</v>
+      </c>
+      <c r="H86" s="28">
+        <v>1</v>
+      </c>
+      <c r="I86" s="28">
+        <v>0</v>
+      </c>
+      <c r="J86" s="28">
+        <v>1</v>
+      </c>
+      <c r="K86" s="28">
+        <v>0</v>
+      </c>
+      <c r="L86" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M86" s="23">
+        <v>0</v>
+      </c>
+      <c r="N86" s="23">
+        <v>0</v>
+      </c>
+      <c r="O86" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="P86" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q86" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="R86" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S86" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="T86" s="24" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C87" s="28">
+        <v>700301</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="F87" s="28">
+        <v>7</v>
+      </c>
+      <c r="G87" s="28">
+        <v>100005</v>
+      </c>
+      <c r="H87" s="28">
+        <v>1</v>
+      </c>
+      <c r="I87" s="28">
+        <v>700302</v>
+      </c>
+      <c r="J87" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="K87" s="28">
+        <v>0</v>
+      </c>
+      <c r="L87" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M87" s="23">
+        <v>0</v>
+      </c>
+      <c r="N87" s="23">
+        <v>0</v>
+      </c>
+      <c r="O87" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="P87" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q87" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="S87" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="T87" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C88" s="28">
+        <v>700302</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E88" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="F88" s="28">
+        <v>7</v>
+      </c>
+      <c r="G88" s="28">
+        <v>100005</v>
+      </c>
+      <c r="H88" s="28">
+        <v>1</v>
+      </c>
+      <c r="I88" s="28">
+        <v>700303</v>
+      </c>
+      <c r="J88" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K88" s="28">
+        <v>0</v>
+      </c>
+      <c r="L88" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M88" s="23">
+        <v>0</v>
+      </c>
+      <c r="N88" s="23">
+        <v>0</v>
+      </c>
+      <c r="O88" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="P88" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q88" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="S88" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="T88" s="24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C89" s="28">
+        <v>700303</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F89" s="28">
+        <v>7</v>
+      </c>
+      <c r="G89" s="28">
+        <v>100052</v>
+      </c>
+      <c r="H89" s="28">
+        <v>1</v>
+      </c>
+      <c r="I89" s="28">
+        <v>700304</v>
+      </c>
+      <c r="J89" s="28">
+        <v>0.75</v>
+      </c>
+      <c r="K89" s="28">
+        <v>0</v>
+      </c>
+      <c r="L89" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M89" s="23">
+        <v>0</v>
+      </c>
+      <c r="N89" s="23">
+        <v>0</v>
+      </c>
+      <c r="O89" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="P89" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q89" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="S89" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="T89" s="24" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C90" s="28">
+        <v>700304</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F90" s="28">
+        <v>7</v>
+      </c>
+      <c r="G90" s="28">
+        <v>100052</v>
+      </c>
+      <c r="H90" s="28">
+        <v>1</v>
+      </c>
+      <c r="I90" s="28">
+        <v>0</v>
+      </c>
+      <c r="J90" s="28">
+        <v>1</v>
+      </c>
+      <c r="K90" s="28">
+        <v>0</v>
+      </c>
+      <c r="L90" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M90" s="23">
+        <v>0</v>
+      </c>
+      <c r="N90" s="23">
+        <v>0</v>
+      </c>
+      <c r="O90" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="P90" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q90" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="S90" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="T90" s="24" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C91" s="28">
+        <v>701501</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F91" s="28">
+        <v>7</v>
+      </c>
+      <c r="G91" s="28">
+        <v>100005</v>
+      </c>
+      <c r="H91" s="28">
+        <v>1</v>
+      </c>
+      <c r="I91" s="28">
+        <v>701502</v>
+      </c>
+      <c r="J91" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="K91" s="28">
+        <v>0</v>
+      </c>
+      <c r="L91" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M91" s="23">
+        <v>0</v>
+      </c>
+      <c r="N91" s="23">
+        <v>0</v>
+      </c>
+      <c r="O91" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="P91" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q91" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="S91" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="T91" s="24" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C92" s="28">
+        <v>701502</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F92" s="28">
+        <v>7</v>
+      </c>
+      <c r="G92" s="28">
+        <v>100005</v>
+      </c>
+      <c r="H92" s="28">
+        <v>1</v>
+      </c>
+      <c r="I92" s="28">
+        <v>701503</v>
+      </c>
+      <c r="J92" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K92" s="28">
+        <v>0</v>
+      </c>
+      <c r="L92" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M92" s="23">
+        <v>0</v>
+      </c>
+      <c r="N92" s="23">
+        <v>0</v>
+      </c>
+      <c r="O92" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="P92" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q92" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="S92" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="T92" s="24" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C93" s="28">
+        <v>701503</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="F93" s="28">
+        <v>7</v>
+      </c>
+      <c r="G93" s="29">
+        <v>100006</v>
+      </c>
+      <c r="H93" s="28">
+        <v>1</v>
+      </c>
+      <c r="I93" s="28">
+        <v>0</v>
+      </c>
+      <c r="J93" s="28">
+        <v>1</v>
+      </c>
+      <c r="K93" s="28">
+        <v>0</v>
+      </c>
+      <c r="L93" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M93" s="23">
+        <v>0</v>
+      </c>
+      <c r="N93" s="23">
+        <v>0</v>
+      </c>
+      <c r="O93" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="P93" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q93" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="S93" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="T93" s="24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C94" s="28">
+        <v>700601</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" s="28">
+        <v>7</v>
+      </c>
+      <c r="G94" s="28">
+        <v>100001</v>
+      </c>
+      <c r="H94" s="28">
+        <v>1</v>
+      </c>
+      <c r="I94" s="28">
+        <v>700602</v>
+      </c>
+      <c r="J94" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K94" s="28">
+        <v>0</v>
+      </c>
+      <c r="L94" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M94" s="23">
+        <v>0</v>
+      </c>
+      <c r="N94" s="23">
+        <v>0</v>
+      </c>
+      <c r="O94" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="P94" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q94" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="R94" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="S94" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="T94" s="24" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C95" s="28">
+        <v>700602</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F95" s="28">
+        <v>7</v>
+      </c>
+      <c r="G95" s="28">
+        <v>100052</v>
+      </c>
+      <c r="H95" s="28">
+        <v>1</v>
+      </c>
+      <c r="I95" s="28">
+        <v>700603</v>
+      </c>
+      <c r="J95" s="28">
+        <v>0.75</v>
+      </c>
+      <c r="K95" s="28">
+        <v>0</v>
+      </c>
+      <c r="L95" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M95" s="23">
+        <v>0</v>
+      </c>
+      <c r="N95" s="23">
+        <v>0</v>
+      </c>
+      <c r="O95" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="P95" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q95" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="R95" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="S95" s="24" t="s">
         <v>387</v>
       </c>
+      <c r="T95" s="24" t="s">
+        <v>397</v>
+      </c>
     </row>
-    <row r="81" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="8">
-        <v>700011</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F81" s="8">
+    <row r="96" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="28">
+        <v>700603</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F96" s="28">
         <v>7</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G96" s="28">
+        <v>100052</v>
+      </c>
+      <c r="H96" s="28">
+        <v>1</v>
+      </c>
+      <c r="I96" s="28">
+        <v>0</v>
+      </c>
+      <c r="J96" s="28">
+        <v>1</v>
+      </c>
+      <c r="K96" s="28">
+        <v>0</v>
+      </c>
+      <c r="L96" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M96" s="23">
+        <v>0</v>
+      </c>
+      <c r="N96" s="23">
+        <v>0</v>
+      </c>
+      <c r="O96" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="P96" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q96" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="R96" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="S96" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="T96" s="24" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C97" s="28">
+        <v>700701</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F97" s="28">
+        <v>7</v>
+      </c>
+      <c r="G97" s="28">
+        <v>100003</v>
+      </c>
+      <c r="H97" s="28">
+        <v>1</v>
+      </c>
+      <c r="I97" s="28">
+        <v>700702</v>
+      </c>
+      <c r="J97" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="K97" s="28">
+        <v>0</v>
+      </c>
+      <c r="L97" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M97" s="23">
+        <v>0</v>
+      </c>
+      <c r="N97" s="23">
+        <v>0</v>
+      </c>
+      <c r="O97" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="P97" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q97" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="R97" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S97" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="T97" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C98" s="28">
+        <v>700702</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E98" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F98" s="28">
+        <v>7</v>
+      </c>
+      <c r="G98" s="28">
+        <v>100003</v>
+      </c>
+      <c r="H98" s="28">
+        <v>1</v>
+      </c>
+      <c r="I98" s="28">
+        <v>700703</v>
+      </c>
+      <c r="J98" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K98" s="28">
+        <v>0</v>
+      </c>
+      <c r="L98" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M98" s="23">
+        <v>0</v>
+      </c>
+      <c r="N98" s="23">
+        <v>0</v>
+      </c>
+      <c r="O98" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="P98" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q98" s="28">
+        <v>9000</v>
+      </c>
+      <c r="R98" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S98" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="T98" s="24" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C99" s="28">
+        <v>700703</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="F99" s="28">
+        <v>7</v>
+      </c>
+      <c r="G99" s="29">
+        <v>100004</v>
+      </c>
+      <c r="H99" s="28">
+        <v>1</v>
+      </c>
+      <c r="I99" s="28">
+        <v>0</v>
+      </c>
+      <c r="J99" s="28">
+        <v>1</v>
+      </c>
+      <c r="K99" s="28">
+        <v>0</v>
+      </c>
+      <c r="L99" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M99" s="23">
+        <v>0</v>
+      </c>
+      <c r="N99" s="23">
+        <v>0</v>
+      </c>
+      <c r="O99" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="P99" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q99" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="S99" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="T99" s="24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C100" s="28">
+        <v>700801</v>
+      </c>
+      <c r="D100" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="F100" s="28">
+        <v>7</v>
+      </c>
+      <c r="G100" s="28">
+        <v>100005</v>
+      </c>
+      <c r="H100" s="28">
+        <v>1</v>
+      </c>
+      <c r="I100" s="28">
+        <v>700802</v>
+      </c>
+      <c r="J100" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K100" s="28">
+        <v>0</v>
+      </c>
+      <c r="L100" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M100" s="23">
+        <v>0</v>
+      </c>
+      <c r="N100" s="23">
+        <v>0</v>
+      </c>
+      <c r="O100" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="P100" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q100" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S100" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="T100" s="24" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C101" s="28">
+        <v>700802</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="E101" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F101" s="28">
+        <v>7</v>
+      </c>
+      <c r="G101" s="28">
+        <v>100052</v>
+      </c>
+      <c r="H101" s="28">
+        <v>1</v>
+      </c>
+      <c r="I101" s="28">
+        <v>0</v>
+      </c>
+      <c r="J101" s="28">
+        <v>1</v>
+      </c>
+      <c r="K101" s="28">
+        <v>0</v>
+      </c>
+      <c r="L101" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M101" s="23">
+        <v>0</v>
+      </c>
+      <c r="N101" s="23">
+        <v>0</v>
+      </c>
+      <c r="O101" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="P101" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q101" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="S101" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="T101" s="24" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C102" s="28">
+        <v>700901</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="F102" s="28">
+        <v>7</v>
+      </c>
+      <c r="G102" s="28">
         <v>100001</v>
       </c>
-      <c r="H81" s="8">
-        <v>1</v>
-      </c>
-      <c r="I81" s="10">
-        <v>0</v>
-      </c>
-      <c r="J81" s="8">
-        <v>1</v>
-      </c>
-      <c r="K81" s="8">
-        <v>0</v>
-      </c>
-      <c r="L81" s="8">
-        <v>0</v>
-      </c>
-      <c r="M81" s="12">
-        <v>5</v>
-      </c>
-      <c r="N81" s="2">
-        <v>3000</v>
-      </c>
-      <c r="O81" s="13" t="s">
+      <c r="H102" s="28">
+        <v>1</v>
+      </c>
+      <c r="I102" s="28">
+        <v>700902</v>
+      </c>
+      <c r="J102" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K102" s="28">
+        <v>0</v>
+      </c>
+      <c r="L102" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="P81" s="14">
-        <v>1001</v>
-      </c>
-      <c r="Q81" s="14">
-        <v>0</v>
-      </c>
-      <c r="R81" s="14">
-        <v>1</v>
-      </c>
-      <c r="S81" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="T81" s="19" t="s">
-        <v>313</v>
+      <c r="M102" s="23">
+        <v>0</v>
+      </c>
+      <c r="N102" s="23">
+        <v>0</v>
+      </c>
+      <c r="O102" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="P102" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q102" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="S102" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="T102" s="24" t="s">
+        <v>350</v>
       </c>
     </row>
-    <row r="82" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C82" s="8">
-        <v>700021</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F82" s="8">
+    <row r="103" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C103" s="28">
+        <v>700902</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F103" s="28">
         <v>7</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G103" s="28">
         <v>100002</v>
       </c>
-      <c r="H82" s="8">
-        <v>1</v>
-      </c>
-      <c r="I82" s="10">
-        <v>0</v>
-      </c>
-      <c r="J82" s="8">
-        <v>1</v>
-      </c>
-      <c r="K82" s="8">
-        <v>0</v>
-      </c>
-      <c r="L82" s="8">
-        <v>0</v>
-      </c>
-      <c r="M82" s="12">
-        <v>10</v>
-      </c>
-      <c r="N82" s="2">
-        <v>4500</v>
-      </c>
-      <c r="O82" s="13" t="s">
+      <c r="H103" s="28">
+        <v>1</v>
+      </c>
+      <c r="I103" s="28">
+        <v>0</v>
+      </c>
+      <c r="J103" s="28">
+        <v>1</v>
+      </c>
+      <c r="K103" s="28">
+        <v>0</v>
+      </c>
+      <c r="L103" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="P82" s="14">
-        <v>1002</v>
-      </c>
-      <c r="Q82" s="14">
-        <v>0</v>
-      </c>
-      <c r="R82" s="14">
-        <v>30</v>
-      </c>
-      <c r="S82" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="T82" s="19" t="s">
-        <v>314</v>
+      <c r="M103" s="23">
+        <v>0</v>
+      </c>
+      <c r="N103" s="23">
+        <v>0</v>
+      </c>
+      <c r="O103" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="P103" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q103" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="S103" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="T103" s="24" t="s">
+        <v>401</v>
       </c>
     </row>
-    <row r="83" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C83" s="8">
-        <v>700031</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="F83" s="8">
+    <row r="104" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C104" s="28">
+        <v>701001</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="F104" s="28">
         <v>7</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G104" s="28">
         <v>100003</v>
       </c>
-      <c r="H83" s="8">
-        <v>1</v>
-      </c>
-      <c r="I83" s="10">
-        <v>0</v>
-      </c>
-      <c r="J83" s="8">
-        <v>1</v>
-      </c>
-      <c r="K83" s="8">
-        <v>0</v>
-      </c>
-      <c r="L83" s="8">
-        <v>0</v>
-      </c>
-      <c r="M83" s="12">
-        <v>10</v>
-      </c>
-      <c r="N83" s="2">
-        <v>15000</v>
-      </c>
-      <c r="O83" s="13" t="s">
+      <c r="H104" s="28">
+        <v>1</v>
+      </c>
+      <c r="I104" s="28">
+        <v>701002</v>
+      </c>
+      <c r="J104" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K104" s="28">
+        <v>0</v>
+      </c>
+      <c r="L104" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="P83" s="15">
-        <v>1003</v>
-      </c>
-      <c r="Q83" s="15">
-        <v>0</v>
-      </c>
-      <c r="R83" s="15">
-        <v>3</v>
-      </c>
-      <c r="S83" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="T83" s="19" t="s">
-        <v>315</v>
+      <c r="M104" s="23">
+        <v>0</v>
+      </c>
+      <c r="N104" s="23">
+        <v>0</v>
+      </c>
+      <c r="O104" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="P104" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q104" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="R104" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="S104" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="T104" s="24" t="s">
+        <v>402</v>
       </c>
     </row>
-    <row r="84" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C84" s="8">
-        <v>700041</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F84" s="8">
+    <row r="105" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C105" s="28">
+        <v>701002</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="E105" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F105" s="28">
         <v>7</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H84" s="8">
-        <v>1</v>
-      </c>
-      <c r="I84" s="10">
-        <v>0</v>
-      </c>
-      <c r="J84" s="8">
-        <v>1</v>
-      </c>
-      <c r="K84" s="8">
-        <v>0</v>
-      </c>
-      <c r="L84" s="8">
-        <v>0</v>
-      </c>
-      <c r="M84" s="12">
-        <v>10</v>
-      </c>
-      <c r="N84" s="2">
-        <v>15000</v>
-      </c>
-      <c r="O84" s="13" t="s">
+      <c r="G105" s="29">
+        <v>100004</v>
+      </c>
+      <c r="H105" s="28">
+        <v>1</v>
+      </c>
+      <c r="I105" s="28">
+        <v>0</v>
+      </c>
+      <c r="J105" s="28">
+        <v>1</v>
+      </c>
+      <c r="K105" s="28">
+        <v>0</v>
+      </c>
+      <c r="L105" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="P84" s="15">
-        <v>1004</v>
-      </c>
-      <c r="Q84" s="15">
-        <v>0</v>
-      </c>
-      <c r="R84" s="15">
-        <v>1</v>
-      </c>
-      <c r="S84" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="T84" s="19" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="85" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C85" s="8">
-        <v>700051</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F85" s="8">
-        <v>7</v>
-      </c>
-      <c r="G85" s="8">
-        <v>100005</v>
-      </c>
-      <c r="H85" s="8">
-        <v>1</v>
-      </c>
-      <c r="I85" s="8">
-        <v>100052</v>
-      </c>
-      <c r="J85" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="K85" s="8">
-        <v>0</v>
-      </c>
-      <c r="L85" s="8">
-        <v>0</v>
-      </c>
-      <c r="M85" s="12">
-        <v>10</v>
-      </c>
-      <c r="N85" s="2">
-        <v>6000</v>
-      </c>
-      <c r="O85" s="13" t="s">
+      <c r="M105" s="23">
+        <v>0</v>
+      </c>
+      <c r="N105" s="23">
+        <v>0</v>
+      </c>
+      <c r="O105" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="P105" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q105" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="P85" s="14">
-        <v>1005</v>
-      </c>
-      <c r="Q85" s="14">
-        <v>0</v>
-      </c>
-      <c r="R85" s="14">
-        <v>100000</v>
-      </c>
-      <c r="S85" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="T85" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="86" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C86" s="8">
-        <v>700052</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F86" s="8">
-        <v>7</v>
-      </c>
-      <c r="G86" s="8">
-        <v>100052</v>
-      </c>
-      <c r="H86" s="8">
-        <v>1</v>
-      </c>
-      <c r="I86" s="10">
-        <v>0</v>
-      </c>
-      <c r="J86" s="8">
-        <v>1</v>
-      </c>
-      <c r="K86" s="8">
-        <v>0</v>
-      </c>
-      <c r="L86" s="8">
-        <v>0</v>
-      </c>
-      <c r="M86" s="12">
-        <v>10</v>
-      </c>
-      <c r="N86" s="2">
-        <v>6000</v>
-      </c>
-      <c r="O86" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="P86" s="14">
-        <v>1014</v>
-      </c>
-      <c r="Q86" s="14">
-        <v>0</v>
-      </c>
-      <c r="R86" s="14">
-        <v>3</v>
-      </c>
-      <c r="S86" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="T86" s="19" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="87" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C87" s="8">
-        <v>700061</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F87" s="8">
-        <v>7</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H87" s="8">
-        <v>1</v>
-      </c>
-      <c r="I87" s="8">
-        <v>100062</v>
-      </c>
-      <c r="J87" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="K87" s="8">
-        <v>0</v>
-      </c>
-      <c r="L87" s="8">
-        <v>0</v>
-      </c>
-      <c r="M87" s="12">
-        <v>10</v>
-      </c>
-      <c r="N87" s="2">
-        <v>6000</v>
-      </c>
-      <c r="O87" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="P87" s="15">
-        <v>1006</v>
-      </c>
-      <c r="Q87" s="16">
-        <v>0</v>
-      </c>
-      <c r="R87" s="15">
-        <v>1</v>
-      </c>
-      <c r="S87" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="T87" s="19" t="s">
-        <v>319</v>
+      <c r="R105" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="S105" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="T105" s="24" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/TaskCountryConfig.xlsx
+++ b/Excel/TaskCountryConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA716584-9E24-4E44-A4C9-116F8EE50A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19A7325-22E7-49B7-B097-95D6DF5917AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12144,7 +12144,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -12222,9 +12222,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="51" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="51" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -20507,7 +20504,7 @@
       <c r="F86" s="28">
         <v>7</v>
       </c>
-      <c r="G86" s="29">
+      <c r="G86" s="28">
         <v>100004</v>
       </c>
       <c r="H86" s="28">
@@ -20899,7 +20896,7 @@
       <c r="F93" s="28">
         <v>7</v>
       </c>
-      <c r="G93" s="29">
+      <c r="G93" s="28">
         <v>100006</v>
       </c>
       <c r="H93" s="28">
@@ -21235,7 +21232,7 @@
       <c r="F99" s="28">
         <v>7</v>
       </c>
-      <c r="G99" s="29">
+      <c r="G99" s="28">
         <v>100004</v>
       </c>
       <c r="H99" s="28">
@@ -21571,7 +21568,7 @@
       <c r="F105" s="28">
         <v>7</v>
       </c>
-      <c r="G105" s="29">
+      <c r="G105" s="28">
         <v>100004</v>
       </c>
       <c r="H105" s="28">

--- a/Excel/TaskCountryConfig.xlsx
+++ b/Excel/TaskCountryConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19A7325-22E7-49B7-B097-95D6DF5917AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6863851F-688D-4D66-BA0D-2ADAA394EAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="91" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="28">
-        <v>701501</v>
+        <v>701401</v>
       </c>
       <c r="D91" s="21" t="s">
         <v>363</v>
@@ -20794,7 +20794,7 @@
         <v>701502</v>
       </c>
       <c r="J91" s="28">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K91" s="28">
         <v>0</v>
@@ -20829,7 +20829,7 @@
     </row>
     <row r="92" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="28">
-        <v>701502</v>
+        <v>701402</v>
       </c>
       <c r="D92" s="21" t="s">
         <v>363</v>
@@ -20847,10 +20847,10 @@
         <v>1</v>
       </c>
       <c r="I92" s="28">
-        <v>701503</v>
+        <v>0</v>
       </c>
       <c r="J92" s="28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K92" s="28">
         <v>0</v>
@@ -20885,7 +20885,7 @@
     </row>
     <row r="93" spans="3:20" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C93" s="28">
-        <v>701503</v>
+        <v>701501</v>
       </c>
       <c r="D93" s="21" t="s">
         <v>321</v>

--- a/Excel/TaskCountryConfig.xlsx
+++ b/Excel/TaskCountryConfig.xlsx
@@ -1,39 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB287E-94DE-4F4C-9976-2C6590ABC781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="TaskCountryProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Admin</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -42,7 +48,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,14 +62,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -73,7 +77,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -81,14 +84,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">作者:
@@ -98,7 +100,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0：忽略此字段
@@ -106,14 +107,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="P4" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">作者:
@@ -189,7 +189,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -226,18 +225,18 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Task" type="4" refreshedVersion="2" background="1" saveData="1">
-    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="C:\Users\Administrator\Desktop\Task.xml" htmlTables="1" htmlFormat="all"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="Task" type="4" background="1" refreshedVersion="2" saveData="1">
+    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="C:\Users\Administrator\Desktop\Task.xml" htmlFormat="all" htmlTables="1"/>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="Task_Template" type="4" refreshedVersion="2" background="1" saveData="1">
-    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Task_Template.xml" htmlTables="1" htmlFormat="all"/>
+  <connection id="2" name="Task_Template" type="4" background="1" refreshedVersion="2" saveData="1">
+    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Task_Template.xml" htmlFormat="all" htmlTables="1"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="488">
   <si>
     <t>c</t>
   </si>
@@ -1650,90 +1649,70 @@
   </si>
   <si>
     <t>击败500只怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 500 monsters.</t>
   </si>
   <si>
     <t>击败2000只怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>击败3000只怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 2000 monsters.</t>
   </si>
   <si>
     <t>击败4000只怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 4000 monsters.</t>
+  </si>
+  <si>
+    <t>10000184;15@1;150000@10000132;3</t>
   </si>
   <si>
     <t>击败10个领主级怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 10 lord-level monsters</t>
+  </si>
+  <si>
+    <t>10000184;15@1;150000@10010034;2</t>
   </si>
   <si>
     <t>击败20个领主级怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>击败30个领主级怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 20 lord-level monsters</t>
+  </si>
+  <si>
+    <t>10000184;15@1;150000@10010083;5</t>
   </si>
   <si>
     <t>击败40个领主级怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defeat 40 lord-level monsters</t>
+  </si>
+  <si>
+    <t>10000184;15@1;150000@10010086;1</t>
   </si>
   <si>
     <t>击败50个领主级怪物</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 500 monsters.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 2000 monsters.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 3000 monsters.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 4000 monsters.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 10 lord-level monsters</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 20 lord-level monsters</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defeat 40 lord-level monsters</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Defeat 50 lord-level monsters</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000184;15@1;150000@10000132;3</t>
-  </si>
-  <si>
-    <t>10000184;15@1;150000@10010034;2</t>
-  </si>
-  <si>
-    <t>10000184;15@1;150000@10010083;5</t>
-  </si>
-  <si>
-    <t>10000184;15@1;150000@10010086;1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1745,7 +1724,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1753,7 +1731,6 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1761,7 +1738,61 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1770,7 +1801,94 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1778,7 +1896,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1787,7 +1912,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
@@ -1795,7 +1919,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1803,20 +1926,18 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1825,7 +1946,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1833,7 +1953,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1841,7 +1960,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1849,7 +1967,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1857,32 +1974,15 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="52">
+  <fills count="83">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1903,19 +2003,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14981536301767021"/>
+        <fgColor theme="0" tint="-0.14981536301767"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14978484450819421"/>
+        <fgColor theme="0" tint="-0.149784844508194"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1945,7 +2063,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1957,7 +2087,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1969,7 +2111,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1981,7 +2135,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1993,7 +2159,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2005,192 +2183,300 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79976805932798245"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79979857783745845"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79973754081850645"/>
+        <fgColor theme="4" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79976805932798245"/>
+        <fgColor theme="4" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79979857783745845"/>
+        <fgColor theme="4" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79973754081850645"/>
+        <fgColor theme="5" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79976805932798245"/>
+        <fgColor theme="5" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79979857783745845"/>
+        <fgColor theme="5" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79973754081850645"/>
+        <fgColor theme="6" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79976805932798245"/>
+        <fgColor theme="6" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79979857783745845"/>
+        <fgColor theme="6" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79973754081850645"/>
+        <fgColor theme="7" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79976805932798245"/>
+        <fgColor theme="7" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79979857783745845"/>
+        <fgColor theme="7" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79973754081850645"/>
+        <fgColor theme="8" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79976805932798245"/>
+        <fgColor theme="8" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79979857783745845"/>
+        <fgColor theme="8" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79973754081850645"/>
+        <fgColor theme="9" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39976195562608724"/>
+        <fgColor theme="9" tint="0.799798577837458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39973143711661124"/>
+        <fgColor theme="9" tint="0.799737540818506"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39976195562608724"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39973143711661124"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39976195562608724"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39973143711661124"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39976195562608724"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39973143711661124"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39976195562608724"/>
+        <fgColor theme="4" tint="0.399761955626087"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39973143711661124"/>
+        <fgColor theme="4" tint="0.399731437116611"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39976195562608724"/>
+        <fgColor theme="5" tint="0.399761955626087"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39973143711661124"/>
+        <fgColor theme="5" tint="0.399731437116611"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399761955626087"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399731437116611"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399761955626087"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399731437116611"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399761955626087"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399731437116611"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399761955626087"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399731437116611"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2243,7 +2529,7 @@
         <color theme="1" tint="0.499984740745262"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39979247413556324"/>
+        <color theme="4" tint="0.399792474135563"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -2304,170 +2590,397 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="58">
+  <cellStyleXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="68" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="69" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="70" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="73" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="74" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="75" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="76" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="77" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="78" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="79" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="80" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="81" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="82" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="82" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2484,22 +2997,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="93" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="90" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="93" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="93" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2517,16 +3030,16 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="90" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="90" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="93" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2548,70 +3061,118 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="58">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 2 2 7" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 2 2 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 2 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 2 2 7" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 2 2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 2 2 7" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 2 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 2 2 7" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 2 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 2 2 7" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="60% - 强调文字颜色 1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="60% - 强调文字颜色 1 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="60% - 强调文字颜色 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="60% - 强调文字颜色 2 2 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="60% - 强调文字颜色 3 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="60% - 强调文字颜色 3 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="60% - 强调文字颜色 4 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="60% - 强调文字颜色 4 2 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="60% - 强调文字颜色 5 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="60% - 强调文字颜色 5 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="60% - 强调文字颜色 6 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="60% - 强调文字颜色 6 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="百分比 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="标题 4 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="标题 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="差 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+  <cellStyles count="106">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="常规 11" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="常规 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="常规 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="常规 6 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="好 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="解释性文本 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="警告文本 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="强调文字颜色 1 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="强调文字颜色 2 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="强调文字颜色 3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="强调文字颜色 4 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="强调文字颜色 5 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="强调文字颜色 6 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="适中 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="注释 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="注释 2 2 2 2 3" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 2 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 2 2 7" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 2 2 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 2 2 7" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 2 2 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 2 2 7" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 2 2 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 2 2 7" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 2 2 2" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 2 2 7" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 2 2 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 2 2 7" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="69"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="72"/>
+    <cellStyle name="60% - 强调文字颜色 1 2" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 1 2 2" xfId="74"/>
+    <cellStyle name="60% - 强调文字颜色 2 2" xfId="75"/>
+    <cellStyle name="60% - 强调文字颜色 2 2 2" xfId="76"/>
+    <cellStyle name="60% - 强调文字颜色 3 2" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 3 2 2" xfId="78"/>
+    <cellStyle name="60% - 强调文字颜色 4 2" xfId="79"/>
+    <cellStyle name="60% - 强调文字颜色 4 2 2" xfId="80"/>
+    <cellStyle name="60% - 强调文字颜色 5 2" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 5 2 2" xfId="82"/>
+    <cellStyle name="60% - 强调文字颜色 6 2" xfId="83"/>
+    <cellStyle name="60% - 强调文字颜色 6 2 2" xfId="84"/>
+    <cellStyle name="百分比 2" xfId="85"/>
+    <cellStyle name="标题 4 2" xfId="86"/>
+    <cellStyle name="标题 5" xfId="87"/>
+    <cellStyle name="差 2" xfId="88"/>
+    <cellStyle name="常规 10" xfId="89"/>
+    <cellStyle name="常规 11" xfId="90"/>
+    <cellStyle name="常规 2 3" xfId="91"/>
+    <cellStyle name="常规 3" xfId="92"/>
+    <cellStyle name="常规 6 2" xfId="93"/>
+    <cellStyle name="好 2" xfId="94"/>
+    <cellStyle name="解释性文本 2" xfId="95"/>
+    <cellStyle name="警告文本 2" xfId="96"/>
+    <cellStyle name="强调文字颜色 1 2" xfId="97"/>
+    <cellStyle name="强调文字颜色 2 2" xfId="98"/>
+    <cellStyle name="强调文字颜色 3 2" xfId="99"/>
+    <cellStyle name="强调文字颜色 4 2" xfId="100"/>
+    <cellStyle name="强调文字颜色 5 2" xfId="101"/>
+    <cellStyle name="强调文字颜色 6 2" xfId="102"/>
+    <cellStyle name="适中 2" xfId="103"/>
+    <cellStyle name="注释 2" xfId="104"/>
+    <cellStyle name="注释 2 2 2 2 3" xfId="105"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <i val="0"/>
       </font>
       <fill>
@@ -2631,7 +3192,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{92C971F3-7F4A-4A6A-B530-8589AD5A9A41}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{6C9CB150-DA15-4A25-BDF4-600A05C018B3}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2639,9 +3200,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2680,7 +3238,7 @@
     </xsd:schema>
   </Schema>
   <Map ID="2" Name="DateArea_映射1" RootElement="DateArea" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
-    <DataBinding FileBinding="true" ConnectionID="2" DataBindingLoadMode="1"/>
+    <DataBinding ConnectionID="2" FileBinding="true" DataBindingLoadMode="1"/>
   </Map>
 </MapInfo>
 </file>
@@ -2966,14 +3524,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C2:T117"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="16.375" customWidth="1"/>
@@ -2992,7 +3550,7 @@
     <col min="20" max="20" width="76.75" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:20" x14ac:dyDescent="0.15">
+    <row r="2" spans="3:20">
       <c r="E2" t="s">
         <v>0</v>
       </c>
@@ -3000,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
@@ -3056,7 +3614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
@@ -3112,7 +3670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C5" s="6" t="s">
         <v>34</v>
       </c>
@@ -3168,7 +3726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C6" s="12">
         <v>100011</v>
       </c>
@@ -3224,7 +3782,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="3:20" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C7" s="12">
         <v>100021</v>
       </c>
@@ -3280,7 +3838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C8" s="12">
         <v>100031</v>
       </c>
@@ -3336,7 +3894,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C9" s="12">
         <v>100041</v>
       </c>
@@ -3392,7 +3950,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C10" s="12">
         <v>100051</v>
       </c>
@@ -3448,7 +4006,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C11" s="12">
         <v>100052</v>
       </c>
@@ -3504,7 +4062,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C12" s="12">
         <v>100061</v>
       </c>
@@ -3560,7 +4118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C13" s="12">
         <v>100062</v>
       </c>
@@ -3616,7 +4174,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C14" s="12">
         <v>100071</v>
       </c>
@@ -3672,7 +4230,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C15" s="12">
         <v>100072</v>
       </c>
@@ -3728,7 +4286,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C16" s="12">
         <v>100081</v>
       </c>
@@ -3784,7 +4342,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C17" s="12">
         <v>100091</v>
       </c>
@@ -3840,7 +4398,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C18" s="12">
         <v>100092</v>
       </c>
@@ -3896,7 +4454,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C19" s="12">
         <v>100101</v>
       </c>
@@ -3952,7 +4510,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C20" s="12">
         <v>100102</v>
       </c>
@@ -4008,7 +4566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C21" s="12">
         <v>100103</v>
       </c>
@@ -4064,7 +4622,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C22" s="12">
         <v>100111</v>
       </c>
@@ -4120,7 +4678,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C23" s="12">
         <v>100121</v>
       </c>
@@ -4176,7 +4734,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C24" s="12">
         <v>200001</v>
       </c>
@@ -4232,7 +4790,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C25" s="12">
         <v>200002</v>
       </c>
@@ -4288,7 +4846,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C26" s="12">
         <v>200003</v>
       </c>
@@ -4344,7 +4902,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C27" s="12">
         <v>200004</v>
       </c>
@@ -4400,7 +4958,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C28" s="12">
         <v>200005</v>
       </c>
@@ -4456,7 +5014,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C29" s="12">
         <v>200006</v>
       </c>
@@ -4512,7 +5070,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C30" s="12">
         <v>200007</v>
       </c>
@@ -4568,7 +5126,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C31" s="12">
         <v>200008</v>
       </c>
@@ -4624,7 +5182,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C32" s="12">
         <v>200009</v>
       </c>
@@ -4680,7 +5238,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C33" s="12">
         <v>200010</v>
       </c>
@@ -4736,7 +5294,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="3:20" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" s="3" customFormat="1" ht="20.25" customHeight="1" spans="3:20">
       <c r="C34" s="12">
         <v>200011</v>
       </c>
@@ -4792,7 +5350,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C35" s="12">
         <v>300001</v>
       </c>
@@ -4848,7 +5406,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C36" s="12">
         <v>300002</v>
       </c>
@@ -4904,7 +5462,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C37" s="12">
         <v>300003</v>
       </c>
@@ -4960,7 +5518,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C38" s="12">
         <v>300004</v>
       </c>
@@ -5016,7 +5574,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C39" s="12">
         <v>400001</v>
       </c>
@@ -5072,7 +5630,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C40" s="12">
         <v>400002</v>
       </c>
@@ -5128,7 +5686,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="41" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C41" s="12">
         <v>400003</v>
       </c>
@@ -5184,7 +5742,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C42" s="12">
         <v>400004</v>
       </c>
@@ -5240,7 +5798,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C43" s="12">
         <v>400005</v>
       </c>
@@ -5296,7 +5854,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C44" s="12">
         <v>500001</v>
       </c>
@@ -5352,7 +5910,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C45" s="12">
         <v>500002</v>
       </c>
@@ -5408,7 +5966,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="46" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C46" s="12">
         <v>500003</v>
       </c>
@@ -5464,7 +6022,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C47" s="12">
         <v>500004</v>
       </c>
@@ -5520,7 +6078,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="48" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C48" s="12">
         <v>500005</v>
       </c>
@@ -5576,7 +6134,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="3:20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C49" s="12">
         <v>600101</v>
       </c>
@@ -5632,7 +6190,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" ht="20.1" customHeight="1" spans="3:20">
       <c r="C50" s="12">
         <v>600102</v>
       </c>
@@ -5688,7 +6246,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="51" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" ht="20.1" customHeight="1" spans="3:20">
       <c r="C51" s="12">
         <v>600103</v>
       </c>
@@ -5744,7 +6302,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="52" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" ht="20.1" customHeight="1" spans="3:20">
       <c r="C52" s="12">
         <v>600104</v>
       </c>
@@ -5800,7 +6358,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" ht="20.1" customHeight="1" spans="3:20">
       <c r="C53" s="12">
         <v>600105</v>
       </c>
@@ -5856,7 +6414,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="54" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" ht="20.1" customHeight="1" spans="3:20">
       <c r="C54" s="12">
         <v>600106</v>
       </c>
@@ -5912,7 +6470,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" ht="20.1" customHeight="1" spans="3:20">
       <c r="C55" s="12">
         <v>600107</v>
       </c>
@@ -5968,7 +6526,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="56" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" ht="20.1" customHeight="1" spans="3:20">
       <c r="C56" s="12">
         <v>600108</v>
       </c>
@@ -6024,7 +6582,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" ht="20.1" customHeight="1" spans="3:20">
       <c r="C57" s="12">
         <v>600109</v>
       </c>
@@ -6080,7 +6638,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="58" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" ht="20.1" customHeight="1" spans="3:20">
       <c r="C58" s="12">
         <v>600110</v>
       </c>
@@ -6136,7 +6694,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="59" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" ht="20.1" customHeight="1" spans="3:20">
       <c r="C59" s="12">
         <v>600111</v>
       </c>
@@ -6192,7 +6750,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" ht="20.1" customHeight="1" spans="3:20">
       <c r="C60" s="12">
         <v>600112</v>
       </c>
@@ -6248,7 +6806,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="61" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" ht="20.1" customHeight="1" spans="3:20">
       <c r="C61" s="12">
         <v>600113</v>
       </c>
@@ -6304,7 +6862,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="62" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" ht="20.1" customHeight="1" spans="3:20">
       <c r="C62" s="12">
         <v>600114</v>
       </c>
@@ -6360,7 +6918,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" ht="20.1" customHeight="1" spans="3:20">
       <c r="C63" s="12">
         <v>600115</v>
       </c>
@@ -6416,7 +6974,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" ht="20.1" customHeight="1" spans="3:20">
       <c r="C64" s="12">
         <v>600201</v>
       </c>
@@ -6472,7 +7030,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="65" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" ht="20.1" customHeight="1" spans="3:20">
       <c r="C65" s="12">
         <v>600202</v>
       </c>
@@ -6528,7 +7086,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="66" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" ht="20.1" customHeight="1" spans="3:20">
       <c r="C66" s="12">
         <v>600203</v>
       </c>
@@ -6584,7 +7142,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="67" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" ht="20.1" customHeight="1" spans="3:20">
       <c r="C67" s="12">
         <v>600204</v>
       </c>
@@ -6640,7 +7198,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="68" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" ht="20.1" customHeight="1" spans="3:20">
       <c r="C68" s="12">
         <v>600205</v>
       </c>
@@ -6696,7 +7254,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" ht="20.1" customHeight="1" spans="3:20">
       <c r="C69" s="12">
         <v>600206</v>
       </c>
@@ -6752,7 +7310,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" ht="20.1" customHeight="1" spans="3:20">
       <c r="C70" s="12">
         <v>600207</v>
       </c>
@@ -6808,7 +7366,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" ht="20.1" customHeight="1" spans="3:20">
       <c r="C71" s="12">
         <v>600208</v>
       </c>
@@ -6864,7 +7422,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="72" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" ht="20.1" customHeight="1" spans="3:20">
       <c r="C72" s="12">
         <v>600209</v>
       </c>
@@ -6920,7 +7478,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="73" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" ht="20.1" customHeight="1" spans="3:20">
       <c r="C73" s="12">
         <v>600301</v>
       </c>
@@ -6976,7 +7534,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="74" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" ht="20.1" customHeight="1" spans="3:20">
       <c r="C74" s="12">
         <v>600302</v>
       </c>
@@ -7032,7 +7590,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="75" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" ht="20.1" customHeight="1" spans="3:20">
       <c r="C75" s="12">
         <v>600303</v>
       </c>
@@ -7088,7 +7646,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="76" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" ht="20.1" customHeight="1" spans="3:20">
       <c r="C76" s="12">
         <v>600304</v>
       </c>
@@ -7144,7 +7702,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="77" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" ht="20.1" customHeight="1" spans="3:20">
       <c r="C77" s="12">
         <v>600305</v>
       </c>
@@ -7200,7 +7758,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="78" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" ht="20.1" customHeight="1" spans="3:20">
       <c r="C78" s="12">
         <v>600306</v>
       </c>
@@ -7256,7 +7814,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="79" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" ht="20.1" customHeight="1" spans="3:20">
       <c r="C79" s="12">
         <v>600307</v>
       </c>
@@ -7312,7 +7870,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="80" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" ht="20.1" customHeight="1" spans="3:20">
       <c r="C80" s="12">
         <v>600308</v>
       </c>
@@ -7368,7 +7926,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C81" s="21">
         <v>700101</v>
       </c>
@@ -7424,7 +7982,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="82" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C82" s="21">
         <v>700102</v>
       </c>
@@ -7480,7 +8038,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="83" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C83" s="21">
         <v>700103</v>
       </c>
@@ -7536,7 +8094,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="84" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C84" s="21">
         <v>700201</v>
       </c>
@@ -7592,7 +8150,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="85" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C85" s="21">
         <v>700202</v>
       </c>
@@ -7648,7 +8206,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="86" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C86" s="21">
         <v>700203</v>
       </c>
@@ -7704,7 +8262,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="87" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C87" s="21">
         <v>700301</v>
       </c>
@@ -7760,7 +8318,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="88" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C88" s="21">
         <v>700302</v>
       </c>
@@ -7816,7 +8374,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="89" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C89" s="21">
         <v>700303</v>
       </c>
@@ -7872,7 +8430,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="90" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C90" s="21">
         <v>700304</v>
       </c>
@@ -7928,7 +8486,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C91" s="21">
         <v>700401</v>
       </c>
@@ -7984,7 +8542,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="92" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C92" s="21">
         <v>700402</v>
       </c>
@@ -8040,7 +8598,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="93" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C93" s="21">
         <v>700501</v>
       </c>
@@ -8096,7 +8654,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="94" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C94" s="21">
         <v>700601</v>
       </c>
@@ -8152,7 +8710,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="95" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C95" s="21">
         <v>700602</v>
       </c>
@@ -8208,7 +8766,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="96" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C96" s="21">
         <v>700603</v>
       </c>
@@ -8264,7 +8822,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="97" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C97" s="21">
         <v>700701</v>
       </c>
@@ -8320,7 +8878,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="98" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C98" s="21">
         <v>700702</v>
       </c>
@@ -8376,7 +8934,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="99" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C99" s="21">
         <v>700703</v>
       </c>
@@ -8432,7 +8990,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="100" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C100" s="21">
         <v>700801</v>
       </c>
@@ -8488,7 +9046,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="101" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C101" s="21">
         <v>700802</v>
       </c>
@@ -8544,7 +9102,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="102" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C102" s="21">
         <v>700901</v>
       </c>
@@ -8600,7 +9158,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="103" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C103" s="21">
         <v>700902</v>
       </c>
@@ -8656,7 +9214,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="104" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C104" s="21">
         <v>701001</v>
       </c>
@@ -8712,7 +9270,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="105" spans="3:20" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" s="4" customFormat="1" ht="19.5" customHeight="1" spans="3:20">
       <c r="C105" s="21">
         <v>701002</v>
       </c>
@@ -8768,7 +9326,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="106" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C106" s="21">
         <v>800101</v>
       </c>
@@ -8779,7 +9337,7 @@
         <v>405</v>
       </c>
       <c r="F106" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G106" s="21">
         <v>100005</v>
@@ -8821,10 +9379,10 @@
         <v>470</v>
       </c>
       <c r="T106" s="25" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="107" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="107" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C107" s="21">
         <v>800201</v>
       </c>
@@ -8835,7 +9393,7 @@
         <v>405</v>
       </c>
       <c r="F107" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G107" s="21">
         <v>100005</v>
@@ -8880,7 +9438,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="108" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C108" s="21">
         <v>800301</v>
       </c>
@@ -8891,7 +9449,7 @@
         <v>405</v>
       </c>
       <c r="F108" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G108" s="21">
         <v>100005</v>
@@ -8930,13 +9488,13 @@
         <v>2000</v>
       </c>
       <c r="S108" s="25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="T108" s="25" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="109" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="109" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C109" s="21">
         <v>800401</v>
       </c>
@@ -8947,7 +9505,7 @@
         <v>405</v>
       </c>
       <c r="F109" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G109" s="21">
         <v>100005</v>
@@ -8986,13 +9544,13 @@
         <v>3000</v>
       </c>
       <c r="S109" s="25" t="s">
-        <v>472</v>
+        <v>412</v>
       </c>
       <c r="T109" s="25" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="110" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="110" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C110" s="21">
         <v>800501</v>
       </c>
@@ -9003,7 +9561,7 @@
         <v>405</v>
       </c>
       <c r="F110" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G110" s="21">
         <v>100005</v>
@@ -9042,13 +9600,13 @@
         <v>4000</v>
       </c>
       <c r="S110" s="25" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="T110" s="25" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="111" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="111" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C111" s="21">
         <v>800601</v>
       </c>
@@ -9059,7 +9617,7 @@
         <v>449</v>
       </c>
       <c r="F111" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G111" s="21">
         <v>100052</v>
@@ -9086,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="24" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="P111" s="23" t="s">
         <v>451</v>
@@ -9098,13 +9656,13 @@
         <v>10</v>
       </c>
       <c r="S111" s="25" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="T111" s="25" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="112" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="112" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C112" s="21">
         <v>800701</v>
       </c>
@@ -9115,7 +9673,7 @@
         <v>449</v>
       </c>
       <c r="F112" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G112" s="21">
         <v>100052</v>
@@ -9142,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="24" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="P112" s="23" t="s">
         <v>451</v>
@@ -9154,13 +9712,13 @@
         <v>20</v>
       </c>
       <c r="S112" s="25" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="T112" s="25" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="113" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="113" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C113" s="21">
         <v>800801</v>
       </c>
@@ -9171,7 +9729,7 @@
         <v>449</v>
       </c>
       <c r="F113" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G113" s="21">
         <v>100052</v>
@@ -9198,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="O113" s="24" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="P113" s="23" t="s">
         <v>451</v>
@@ -9210,13 +9768,13 @@
         <v>30</v>
       </c>
       <c r="S113" s="25" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="T113" s="25" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="114" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C114" s="21">
         <v>800901</v>
       </c>
@@ -9227,7 +9785,7 @@
         <v>449</v>
       </c>
       <c r="F114" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G114" s="21">
         <v>100052</v>
@@ -9254,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="24" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="P114" s="23" t="s">
         <v>451</v>
@@ -9266,13 +9824,13 @@
         <v>40</v>
       </c>
       <c r="S114" s="25" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="T114" s="25" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="115" spans="3:20" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="115" s="4" customFormat="1" ht="20.1" customHeight="1" spans="3:20">
       <c r="C115" s="21">
         <v>801001</v>
       </c>
@@ -9283,7 +9841,7 @@
         <v>449</v>
       </c>
       <c r="F115" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G115" s="21">
         <v>100052</v>
@@ -9310,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="24" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="P115" s="23" t="s">
         <v>451</v>
@@ -9322,18 +9880,18 @@
         <v>50</v>
       </c>
       <c r="S115" s="25" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="T115" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="116" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="116" ht="20.1" customHeight="1"/>
+    <row r="117" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>